--- a/Figure S1.xlsx
+++ b/Figure S1.xlsx
@@ -1,20 +1,23 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
-  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29127"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DELL\Desktop\iMetaOmics原始数据\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1712EB22-137D-4DC3-AD29-25BAC14A619A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView windowWidth="17750" windowHeight="7000" firstSheet="1" activeTab="3"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" firstSheet="1" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="organ index" sheetId="1" r:id="rId1"/>
     <sheet name="Duodenum morphology  " sheetId="2" r:id="rId2"/>
-    <sheet name="Jejunum morphology" sheetId="3" r:id="rId3"/>
+    <sheet name="Jejunum morphology  " sheetId="5" r:id="rId3"/>
     <sheet name="Ileum morphology  " sheetId="4" r:id="rId4"/>
   </sheets>
-  <externalReferences>
-    <externalReference r:id="rId5"/>
-  </externalReferences>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
@@ -295,7 +298,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="Times New Roman"/>
-        <charset val="134"/>
+        <family val="1"/>
       </rPr>
       <t>Vills surface area,µm</t>
     </r>
@@ -305,7 +308,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="Times New Roman"/>
-        <charset val="134"/>
+        <family val="1"/>
       </rPr>
       <t>2</t>
     </r>
@@ -314,19 +317,15 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
-  <numFmts count="9">
-    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="176" formatCode="0.00_ "/>
-    <numFmt numFmtId="177" formatCode="0.000_ "/>
-    <numFmt numFmtId="178" formatCode="0.00_);[Red]\(0.00\)"/>
-    <numFmt numFmtId="179" formatCode="0.0000_ "/>
-    <numFmt numFmtId="180" formatCode="0_);[Red]\(0\)"/>
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="x14ac x16r2 xr xr9">
+  <numFmts count="5">
+    <numFmt numFmtId="178" formatCode="0.00_ "/>
+    <numFmt numFmtId="179" formatCode="0.000_ "/>
+    <numFmt numFmtId="180" formatCode="0.00_);[Red]\(0.00\)"/>
+    <numFmt numFmtId="181" formatCode="0.0000_ "/>
+    <numFmt numFmtId="182" formatCode="0_);[Red]\(0\)"/>
   </numFmts>
-  <fonts count="22">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -338,355 +337,31 @@
       <sz val="11"/>
       <color theme="1"/>
       <name val="Times New Roman"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
+      <family val="1"/>
     </font>
     <font>
       <vertAlign val="superscript"/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <name val="宋体"/>
       <charset val="134"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="33">
+  <fills count="2">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="11">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -722,388 +397,212 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
-  <cellStyleXfs count="49">
+  <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="178" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="1" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="178" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="179" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="1" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="178" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="180" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="179" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="181" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="180" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="182" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="2" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
-  <cellStyles count="49">
+  <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
-    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
-    <cellStyle name="货币" xfId="2" builtinId="4"/>
-    <cellStyle name="百分比" xfId="3" builtinId="5"/>
-    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
-    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
-    <cellStyle name="超链接" xfId="6" builtinId="8"/>
-    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
-    <cellStyle name="注释" xfId="8" builtinId="10"/>
-    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
-    <cellStyle name="标题" xfId="10" builtinId="15"/>
-    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
-    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
-    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
-    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
-    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
-    <cellStyle name="输入" xfId="16" builtinId="20"/>
-    <cellStyle name="输出" xfId="17" builtinId="21"/>
-    <cellStyle name="计算" xfId="18" builtinId="22"/>
-    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
-    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
-    <cellStyle name="汇总" xfId="21" builtinId="25"/>
-    <cellStyle name="好" xfId="22" builtinId="26"/>
-    <cellStyle name="差" xfId="23" builtinId="27"/>
-    <cellStyle name="适中" xfId="24" builtinId="28"/>
-    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
-    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
-    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
-    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
-    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
-    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
-    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
-    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
-    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
-    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
-    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
-    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
-    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
-    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
-    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
-    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
-    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
-    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
-    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
-    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
-    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
-    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
-    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
-    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
   <dxfs count="17">
     <dxf>
       <fill>
         <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.799981688894314"/>
-          <bgColor theme="4" tint="0.799981688894314"/>
+          <fgColor theme="4" tint="0.79995117038483843"/>
+          <bgColor theme="4" tint="0.79995117038483843"/>
+        </patternFill>
+      </fill>
+      <border>
+        <bottom style="thin">
+          <color theme="4" tint="0.39994506668294322"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.79995117038483843"/>
+          <bgColor theme="4" tint="0.79995117038483843"/>
+        </patternFill>
+      </fill>
+      <border>
+        <bottom style="thin">
+          <color theme="4" tint="0.39994506668294322"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+      <border>
+        <bottom style="thin">
+          <color theme="4" tint="0.39994506668294322"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color theme="1"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color theme="1"/>
+      </font>
+      <border>
+        <top style="thin">
+          <color theme="4"/>
+        </top>
+        <bottom style="thin">
+          <color theme="4"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.79995117038483843"/>
+          <bgColor theme="4" tint="0.79995117038483843"/>
         </patternFill>
       </fill>
     </dxf>
     <dxf>
       <fill>
         <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.799981688894314"/>
-          <bgColor theme="4" tint="0.799981688894314"/>
+          <fgColor theme="4" tint="0.79995117038483843"/>
+          <bgColor theme="4" tint="0.79995117038483843"/>
         </patternFill>
       </fill>
     </dxf>
     <dxf>
       <font>
-        <b val="1"/>
+        <b/>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.79995117038483843"/>
+          <bgColor theme="4" tint="0.79995117038483843"/>
+        </patternFill>
+      </fill>
+      <border>
+        <top style="thin">
+          <color theme="4" tint="0.39994506668294322"/>
+        </top>
+        <bottom style="thin">
+          <color theme="4" tint="0.39994506668294322"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.79995117038483843"/>
+          <bgColor theme="4" tint="0.79995117038483843"/>
+        </patternFill>
+      </fill>
+      <border>
+        <bottom style="thin">
+          <color theme="4" tint="0.39994506668294322"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.79995117038483843"/>
+          <bgColor theme="4" tint="0.79995117038483843"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.79995117038483843"/>
+          <bgColor theme="4" tint="0.79995117038483843"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
         <color theme="1"/>
       </font>
     </dxf>
     <dxf>
       <font>
-        <b val="1"/>
+        <b/>
         <color theme="1"/>
       </font>
     </dxf>
     <dxf>
       <font>
-        <b val="1"/>
+        <b/>
         <color theme="1"/>
       </font>
       <border>
@@ -1114,7 +613,7 @@
     </dxf>
     <dxf>
       <font>
-        <b val="1"/>
+        <b/>
         <color theme="0"/>
       </font>
       <fill>
@@ -1142,326 +641,43 @@
           <color theme="4"/>
         </bottom>
         <horizontal style="thin">
-          <color theme="4" tint="0.399975585192419"/>
+          <color theme="4" tint="0.39994506668294322"/>
         </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.799981688894314"/>
-          <bgColor theme="4" tint="0.799981688894314"/>
-        </patternFill>
-      </fill>
-      <border>
-        <bottom style="thin">
-          <color theme="4" tint="0.399975585192419"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="1"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.799981688894314"/>
-          <bgColor theme="4" tint="0.799981688894314"/>
-        </patternFill>
-      </fill>
-      <border>
-        <bottom style="thin">
-          <color theme="4" tint="0.399975585192419"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="1"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="1"/>
-      </font>
-      <border>
-        <bottom style="thin">
-          <color theme="4" tint="0.399975585192419"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="1"/>
-        <color theme="1"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="1"/>
-        <color theme="1"/>
-      </font>
-      <border>
-        <top style="thin">
-          <color theme="4"/>
-        </top>
-        <bottom style="thin">
-          <color theme="4"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.799981688894314"/>
-          <bgColor theme="4" tint="0.799981688894314"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.799981688894314"/>
-          <bgColor theme="4" tint="0.799981688894314"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="1"/>
-        <color theme="1"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.799981688894314"/>
-          <bgColor theme="4" tint="0.799981688894314"/>
-        </patternFill>
-      </fill>
-      <border>
-        <top style="thin">
-          <color theme="4" tint="0.399975585192419"/>
-        </top>
-        <bottom style="thin">
-          <color theme="4" tint="0.399975585192419"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="1"/>
-        <color theme="1"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.799981688894314"/>
-          <bgColor theme="4" tint="0.799981688894314"/>
-        </patternFill>
-      </fill>
-      <border>
-        <bottom style="thin">
-          <color theme="4" tint="0.399975585192419"/>
-        </bottom>
       </border>
     </dxf>
   </dxfs>
   <tableStyles count="2" defaultTableStyle="TableStylePreset3_Accent1" defaultPivotStyle="PivotStylePreset2_Accent1">
     <tableStyle name="TableStylePreset3_Accent1" pivot="0" count="7" xr9:uid="{59DB682C-5494-4EDE-A608-00C9E5F0F923}">
-      <tableStyleElement type="wholeTable" dxfId="6"/>
-      <tableStyleElement type="headerRow" dxfId="5"/>
-      <tableStyleElement type="totalRow" dxfId="4"/>
-      <tableStyleElement type="firstColumn" dxfId="3"/>
-      <tableStyleElement type="lastColumn" dxfId="2"/>
-      <tableStyleElement type="firstRowStripe" dxfId="1"/>
-      <tableStyleElement type="firstColumnStripe" dxfId="0"/>
+      <tableStyleElement type="wholeTable" dxfId="16"/>
+      <tableStyleElement type="headerRow" dxfId="15"/>
+      <tableStyleElement type="totalRow" dxfId="14"/>
+      <tableStyleElement type="firstColumn" dxfId="13"/>
+      <tableStyleElement type="lastColumn" dxfId="12"/>
+      <tableStyleElement type="firstRowStripe" dxfId="11"/>
+      <tableStyleElement type="firstColumnStripe" dxfId="10"/>
     </tableStyle>
     <tableStyle name="PivotStylePreset2_Accent1" table="0" count="10" xr9:uid="{267968C8-6FFD-4C36-ACC1-9EA1FD1885CA}">
-      <tableStyleElement type="headerRow" dxfId="16"/>
-      <tableStyleElement type="totalRow" dxfId="15"/>
-      <tableStyleElement type="firstRowStripe" dxfId="14"/>
-      <tableStyleElement type="firstColumnStripe" dxfId="13"/>
-      <tableStyleElement type="firstSubtotalRow" dxfId="12"/>
-      <tableStyleElement type="secondSubtotalRow" dxfId="11"/>
-      <tableStyleElement type="firstRowSubheading" dxfId="10"/>
-      <tableStyleElement type="secondRowSubheading" dxfId="9"/>
-      <tableStyleElement type="pageFieldLabels" dxfId="8"/>
-      <tableStyleElement type="pageFieldValues" dxfId="7"/>
+      <tableStyleElement type="headerRow" dxfId="9"/>
+      <tableStyleElement type="totalRow" dxfId="8"/>
+      <tableStyleElement type="firstRowStripe" dxfId="7"/>
+      <tableStyleElement type="firstColumnStripe" dxfId="6"/>
+      <tableStyleElement type="firstSubtotalRow" dxfId="5"/>
+      <tableStyleElement type="secondSubtotalRow" dxfId="4"/>
+      <tableStyleElement type="firstRowSubheading" dxfId="3"/>
+      <tableStyleElement type="secondRowSubheading" dxfId="2"/>
+      <tableStyleElement type="pageFieldLabels" dxfId="1"/>
+      <tableStyleElement type="pageFieldValues" dxfId="0"/>
     </tableStyle>
   </tableStyles>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
     </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <sheetNames>
-      <sheetName val="Sheet1"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0" refreshError="1">
-        <row r="33">
-          <cell r="G33">
-            <v>72.8866946601942</v>
-          </cell>
-        </row>
-        <row r="34">
-          <cell r="G34">
-            <v>78.5628310679612</v>
-          </cell>
-        </row>
-        <row r="35">
-          <cell r="G35">
-            <v>91.0139140776699</v>
-          </cell>
-        </row>
-        <row r="36">
-          <cell r="G36">
-            <v>93.2241048543689</v>
-          </cell>
-        </row>
-        <row r="37">
-          <cell r="G37">
-            <v>93.7282970873786</v>
-          </cell>
-        </row>
-        <row r="38">
-          <cell r="G38">
-            <v>97.7839126213592</v>
-          </cell>
-        </row>
-        <row r="39">
-          <cell r="G39">
-            <v>105.08783592233</v>
-          </cell>
-        </row>
-        <row r="40">
-          <cell r="G40">
-            <v>105.642492718447</v>
-          </cell>
-        </row>
-        <row r="41">
-          <cell r="G41">
-            <v>114.365468446602</v>
-          </cell>
-        </row>
-        <row r="42">
-          <cell r="G42">
-            <v>116.924811650485</v>
-          </cell>
-        </row>
-        <row r="43">
-          <cell r="G43">
-            <v>121.324268932039</v>
-          </cell>
-        </row>
-        <row r="44">
-          <cell r="G44">
-            <v>126.809648058252</v>
-          </cell>
-        </row>
-        <row r="45">
-          <cell r="G45">
-            <v>130.805199029126</v>
-          </cell>
-        </row>
-        <row r="46">
-          <cell r="G46">
-            <v>139.007968446602</v>
-          </cell>
-        </row>
-        <row r="47">
-          <cell r="G47">
-            <v>141.22792961165</v>
-          </cell>
-        </row>
-        <row r="48">
-          <cell r="G48">
-            <v>141.867213592233</v>
-          </cell>
-        </row>
-        <row r="49">
-          <cell r="G49">
-            <v>149.325309708738</v>
-          </cell>
-        </row>
-        <row r="50">
-          <cell r="G50">
-            <v>152.461198058252</v>
-          </cell>
-        </row>
-        <row r="51">
-          <cell r="G51">
-            <v>158.915162135922</v>
-          </cell>
-        </row>
-        <row r="52">
-          <cell r="G52">
-            <v>161.667255339806</v>
-          </cell>
-        </row>
-        <row r="53">
-          <cell r="G53">
-            <v>173.338362135922</v>
-          </cell>
-        </row>
-        <row r="54">
-          <cell r="G54">
-            <v>173.902982038835</v>
-          </cell>
-        </row>
-        <row r="55">
-          <cell r="G55">
-            <v>180.697320873786</v>
-          </cell>
-        </row>
-        <row r="56">
-          <cell r="G56">
-            <v>203.892739320388</v>
-          </cell>
-        </row>
-        <row r="57">
-          <cell r="G57">
-            <v>210.614724757282</v>
-          </cell>
-        </row>
-        <row r="58">
-          <cell r="G58">
-            <v>211.650485436893</v>
-          </cell>
-        </row>
-        <row r="59">
-          <cell r="G59">
-            <v>217.86546407767</v>
-          </cell>
-        </row>
-        <row r="60">
-          <cell r="G60">
-            <v>232.726369417476</v>
-          </cell>
-        </row>
-        <row r="61">
-          <cell r="G61">
-            <v>248.118561650485</v>
-          </cell>
-        </row>
-        <row r="62">
-          <cell r="G62">
-            <v>315.317335436893</v>
-          </cell>
-        </row>
-        <row r="63">
-          <cell r="G63">
-            <v>347.62161407767</v>
-          </cell>
-        </row>
-      </sheetData>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1708,27 +924,27 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
-  <dimension ref="A1:G73"/>
-  <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="14" outlineLevelCol="6"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:XEY73"/>
+  <sheetFormatPr defaultColWidth="8.7265625" defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="8.72727272727273" style="2"/>
-    <col min="2" max="2" width="10.6363636363636" style="2" customWidth="1"/>
-    <col min="3" max="3" width="8.72727272727273" style="2"/>
-    <col min="4" max="4" width="21.6363636363636" style="11" customWidth="1"/>
-    <col min="5" max="5" width="25.3636363636364" style="11" customWidth="1"/>
-    <col min="6" max="6" width="17.7272727272727" style="11" customWidth="1"/>
-    <col min="7" max="7" width="17.2727272727273" style="11" customWidth="1"/>
-    <col min="8" max="16379" width="8.72727272727273" style="10"/>
-    <col min="16380" max="16384" width="8.72727272727273" style="1"/>
+    <col min="1" max="1" width="8.7265625" style="2"/>
+    <col min="2" max="2" width="10.6328125" style="2" customWidth="1"/>
+    <col min="3" max="3" width="8.7265625" style="2"/>
+    <col min="4" max="4" width="21.6328125" style="10" customWidth="1"/>
+    <col min="5" max="5" width="25.36328125" style="10" customWidth="1"/>
+    <col min="6" max="6" width="17.7265625" style="10" customWidth="1"/>
+    <col min="7" max="7" width="17.26953125" style="10" customWidth="1"/>
+    <col min="8" max="16379" width="8.7265625" style="9"/>
+    <col min="16380" max="16384" width="8.7265625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" s="10" customFormat="1" ht="28" spans="1:7">
+    <row r="1" spans="1:7" s="9" customFormat="1" ht="28" x14ac:dyDescent="0.3">
       <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
@@ -1738,20 +954,20 @@
       <c r="C1" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="12" t="s">
+      <c r="D1" s="11" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="12" t="s">
+      <c r="E1" s="11" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="13" t="s">
+      <c r="F1" s="12" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="13" t="s">
+      <c r="G1" s="12" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="2" s="10" customFormat="1" spans="1:7">
+    <row r="2" spans="1:7" s="9" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A2" s="4" t="s">
         <v>7</v>
       </c>
@@ -1767,14 +983,14 @@
       <c r="E2" s="5">
         <v>0.219027484143763</v>
       </c>
-      <c r="F2" s="14">
-        <v>1.72666666666667</v>
-      </c>
-      <c r="G2" s="14">
-        <v>0.0365045806906272</v>
-      </c>
-    </row>
-    <row r="3" s="10" customFormat="1" spans="1:7">
+      <c r="F2" s="13">
+        <v>1.7266666666666699</v>
+      </c>
+      <c r="G2" s="13">
+        <v>3.6504580690627203E-2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" s="9" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A3" s="4" t="s">
         <v>9</v>
       </c>
@@ -1788,16 +1004,16 @@
         <v>580</v>
       </c>
       <c r="E3" s="5">
-        <v>0.169166666666667</v>
-      </c>
-      <c r="F3" s="14">
-        <v>0.966666666666667</v>
-      </c>
-      <c r="G3" s="14">
-        <v>0.0281944444444444</v>
-      </c>
-    </row>
-    <row r="4" s="10" customFormat="1" spans="1:7">
+        <v>0.16916666666666699</v>
+      </c>
+      <c r="F3" s="13">
+        <v>0.96666666666666701</v>
+      </c>
+      <c r="G3" s="13">
+        <v>2.81944444444444E-2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" s="9" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A4" s="4" t="s">
         <v>10</v>
       </c>
@@ -1813,14 +1029,14 @@
       <c r="E4" s="5">
         <v>0.225849056603774</v>
       </c>
-      <c r="F4" s="14">
+      <c r="F4" s="13">
         <v>0.9</v>
       </c>
-      <c r="G4" s="14">
-        <v>0.0322641509433962</v>
-      </c>
-    </row>
-    <row r="5" s="10" customFormat="1" spans="1:7">
+      <c r="G4" s="13">
+        <v>3.22641509433962E-2</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" s="9" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A5" s="4" t="s">
         <v>11</v>
       </c>
@@ -1834,16 +1050,16 @@
         <v>652</v>
       </c>
       <c r="E5" s="5">
-        <v>0.153550724637681</v>
-      </c>
-      <c r="F5" s="14">
+        <v>0.15355072463768099</v>
+      </c>
+      <c r="F5" s="13">
         <v>1.08666666666667</v>
       </c>
-      <c r="G5" s="14">
-        <v>0.0255917874396135</v>
-      </c>
-    </row>
-    <row r="6" s="10" customFormat="1" spans="1:7">
+      <c r="G5" s="13">
+        <v>2.55917874396135E-2</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" s="9" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A6" s="4" t="s">
         <v>12</v>
       </c>
@@ -1859,14 +1075,14 @@
       <c r="E6" s="5">
         <v>0.121551724137931</v>
       </c>
-      <c r="F6" s="14">
-        <v>1.128</v>
-      </c>
-      <c r="G6" s="14">
-        <v>0.0243103448275862</v>
-      </c>
-    </row>
-    <row r="7" s="10" customFormat="1" spans="1:7">
+      <c r="F6" s="13">
+        <v>1.1279999999999999</v>
+      </c>
+      <c r="G6" s="13">
+        <v>2.4310344827586199E-2</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" s="9" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A7" s="4" t="s">
         <v>13</v>
       </c>
@@ -1882,14 +1098,14 @@
       <c r="E7" s="5">
         <v>0.19901023890785</v>
       </c>
-      <c r="F7" s="14">
+      <c r="F7" s="13">
         <v>0.98</v>
       </c>
-      <c r="G7" s="14">
-        <v>0.0284300341296928</v>
-      </c>
-    </row>
-    <row r="8" s="10" customFormat="1" spans="1:7">
+      <c r="G7" s="13">
+        <v>2.8430034129692801E-2</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" s="9" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A8" s="4" t="s">
         <v>14</v>
       </c>
@@ -1903,16 +1119,16 @@
         <v>1244</v>
       </c>
       <c r="E8" s="5">
-        <v>0.619825174825175</v>
-      </c>
-      <c r="F8" s="14">
-        <v>0.829333333333333</v>
-      </c>
-      <c r="G8" s="14">
-        <v>0.0413216783216783</v>
-      </c>
-    </row>
-    <row r="9" s="10" customFormat="1" spans="1:7">
+        <v>0.61982517482517496</v>
+      </c>
+      <c r="F8" s="13">
+        <v>0.82933333333333303</v>
+      </c>
+      <c r="G8" s="13">
+        <v>4.1321678321678303E-2</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" s="9" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A9" s="4" t="s">
         <v>15</v>
       </c>
@@ -1926,16 +1142,16 @@
         <v>962</v>
       </c>
       <c r="E9" s="5">
-        <v>0.591484918793504</v>
-      </c>
-      <c r="F9" s="14">
-        <v>0.60125</v>
-      </c>
-      <c r="G9" s="14">
-        <v>0.036967807424594</v>
-      </c>
-    </row>
-    <row r="10" s="10" customFormat="1" spans="1:7">
+        <v>0.59148491879350396</v>
+      </c>
+      <c r="F9" s="13">
+        <v>0.60124999999999995</v>
+      </c>
+      <c r="G9" s="13">
+        <v>3.6967807424593997E-2</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" s="9" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A10" s="4" t="s">
         <v>16</v>
       </c>
@@ -1949,16 +1165,16 @@
         <v>1050</v>
       </c>
       <c r="E10" s="5">
-        <v>0.707368421052632</v>
-      </c>
-      <c r="F10" s="14">
-        <v>0.617647058823529</v>
-      </c>
-      <c r="G10" s="14">
-        <v>0.041609907120743</v>
-      </c>
-    </row>
-    <row r="11" s="10" customFormat="1" spans="1:7">
+        <v>0.70736842105263198</v>
+      </c>
+      <c r="F10" s="13">
+        <v>0.61764705882352899</v>
+      </c>
+      <c r="G10" s="13">
+        <v>4.1609907120743E-2</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" s="9" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A11" s="4" t="s">
         <v>17</v>
       </c>
@@ -1972,16 +1188,16 @@
         <v>1090</v>
       </c>
       <c r="E11" s="5">
-        <v>0.682626262626263</v>
-      </c>
-      <c r="F11" s="14">
-        <v>0.778571428571429</v>
-      </c>
-      <c r="G11" s="14">
-        <v>0.0487590187590188</v>
-      </c>
-    </row>
-    <row r="12" s="10" customFormat="1" spans="1:7">
+        <v>0.68262626262626303</v>
+      </c>
+      <c r="F11" s="13">
+        <v>0.77857142857142903</v>
+      </c>
+      <c r="G11" s="13">
+        <v>4.87590187590188E-2</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" s="9" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A12" s="4" t="s">
         <v>18</v>
       </c>
@@ -1997,14 +1213,14 @@
       <c r="E12" s="5">
         <v>0.65</v>
       </c>
-      <c r="F12" s="14">
-        <v>0.764705882352941</v>
-      </c>
-      <c r="G12" s="14">
-        <v>0.0382352941176471</v>
-      </c>
-    </row>
-    <row r="13" s="10" customFormat="1" spans="1:7">
+      <c r="F12" s="13">
+        <v>0.76470588235294101</v>
+      </c>
+      <c r="G12" s="13">
+        <v>3.8235294117647103E-2</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" s="9" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A13" s="4" t="s">
         <v>19</v>
       </c>
@@ -2014,20 +1230,20 @@
       <c r="C13" s="4">
         <v>60</v>
       </c>
-      <c r="D13" s="15">
+      <c r="D13" s="14">
         <v>1032</v>
       </c>
-      <c r="E13" s="12">
+      <c r="E13" s="11">
         <v>0.653304721030043</v>
       </c>
-      <c r="F13" s="14">
-        <v>0.543157894736842</v>
-      </c>
-      <c r="G13" s="14">
-        <v>0.0343844590015812</v>
-      </c>
-    </row>
-    <row r="14" s="10" customFormat="1" spans="1:7">
+      <c r="F13" s="13">
+        <v>0.54315789473684195</v>
+      </c>
+      <c r="G13" s="13">
+        <v>3.43844590015812E-2</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" s="9" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A14" s="4" t="s">
         <v>20</v>
       </c>
@@ -2041,16 +1257,16 @@
         <v>920</v>
       </c>
       <c r="E14" s="5">
-        <v>0.506</v>
-      </c>
-      <c r="F14" s="14">
-        <v>0.383333333333333</v>
-      </c>
-      <c r="G14" s="14">
-        <v>0.0210833333333333</v>
-      </c>
-    </row>
-    <row r="15" s="10" customFormat="1" spans="1:7">
+        <v>0.50600000000000001</v>
+      </c>
+      <c r="F14" s="13">
+        <v>0.38333333333333303</v>
+      </c>
+      <c r="G14" s="13">
+        <v>2.1083333333333301E-2</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" s="9" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A15" s="4" t="s">
         <v>21</v>
       </c>
@@ -2064,16 +1280,16 @@
         <v>710</v>
       </c>
       <c r="E15" s="5">
-        <v>0.49241935483871</v>
-      </c>
-      <c r="F15" s="14">
+        <v>0.49241935483871002</v>
+      </c>
+      <c r="F15" s="13">
         <v>0.338095238095238</v>
       </c>
-      <c r="G15" s="14">
-        <v>0.0234485407066052</v>
-      </c>
-    </row>
-    <row r="16" s="10" customFormat="1" spans="1:7">
+      <c r="G15" s="13">
+        <v>2.3448540706605198E-2</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" s="9" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A16" s="4" t="s">
         <v>22</v>
       </c>
@@ -2087,16 +1303,16 @@
         <v>790</v>
       </c>
       <c r="E16" s="5">
-        <v>0.632</v>
-      </c>
-      <c r="F16" s="14">
-        <v>0.359090909090909</v>
-      </c>
-      <c r="G16" s="14">
-        <v>0.0287272727272727</v>
-      </c>
-    </row>
-    <row r="17" s="10" customFormat="1" spans="1:7">
+        <v>0.63200000000000001</v>
+      </c>
+      <c r="F16" s="13">
+        <v>0.35909090909090902</v>
+      </c>
+      <c r="G16" s="13">
+        <v>2.8727272727272699E-2</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" s="9" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A17" s="4" t="s">
         <v>23</v>
       </c>
@@ -2110,16 +1326,16 @@
         <v>970</v>
       </c>
       <c r="E17" s="5">
-        <v>0.826704545454545</v>
-      </c>
-      <c r="F17" s="14">
-        <v>0.373076923076923</v>
-      </c>
-      <c r="G17" s="14">
-        <v>0.0317963286713287</v>
-      </c>
-    </row>
-    <row r="18" s="10" customFormat="1" spans="1:7">
+        <v>0.82670454545454497</v>
+      </c>
+      <c r="F17" s="13">
+        <v>0.37307692307692297</v>
+      </c>
+      <c r="G17" s="13">
+        <v>3.17963286713287E-2</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" s="9" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A18" s="4" t="s">
         <v>24</v>
       </c>
@@ -2133,16 +1349,16 @@
         <v>960</v>
       </c>
       <c r="E18" s="5">
-        <v>0.684137931034483</v>
-      </c>
-      <c r="F18" s="14">
-        <v>0.436363636363636</v>
-      </c>
-      <c r="G18" s="14">
-        <v>0.0310971786833856</v>
-      </c>
-    </row>
-    <row r="19" s="10" customFormat="1" spans="1:7">
+        <v>0.68413793103448295</v>
+      </c>
+      <c r="F18" s="13">
+        <v>0.43636363636363601</v>
+      </c>
+      <c r="G18" s="13">
+        <v>3.1097178683385601E-2</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" s="9" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A19" s="4" t="s">
         <v>25</v>
       </c>
@@ -2156,16 +1372,16 @@
         <v>970</v>
       </c>
       <c r="E19" s="5">
-        <v>0.672386363636364</v>
-      </c>
-      <c r="F19" s="14">
+        <v>0.67238636363636395</v>
+      </c>
+      <c r="F19" s="13">
         <v>0.359259259259259</v>
       </c>
-      <c r="G19" s="14">
-        <v>0.0249031986531987</v>
-      </c>
-    </row>
-    <row r="20" s="10" customFormat="1" spans="1:7">
+      <c r="G19" s="13">
+        <v>2.4903198653198701E-2</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" s="9" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A20" s="4" t="s">
         <v>26</v>
       </c>
@@ -2179,16 +1395,16 @@
         <v>1190</v>
       </c>
       <c r="E20" s="5">
-        <v>1.01690909090909</v>
-      </c>
-      <c r="F20" s="14">
-        <v>0.313157894736842</v>
-      </c>
-      <c r="G20" s="14">
-        <v>0.0267607655502392</v>
-      </c>
-    </row>
-    <row r="21" s="10" customFormat="1" spans="1:7">
+        <v>1.0169090909090901</v>
+      </c>
+      <c r="F20" s="13">
+        <v>0.31315789473684202</v>
+      </c>
+      <c r="G20" s="13">
+        <v>2.67607655502392E-2</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" s="9" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A21" s="4" t="s">
         <v>27</v>
       </c>
@@ -2202,16 +1418,16 @@
         <v>940</v>
       </c>
       <c r="E21" s="5">
-        <v>0.818352941176471</v>
-      </c>
-      <c r="F21" s="14">
-        <v>0.29375</v>
-      </c>
-      <c r="G21" s="14">
-        <v>0.0255735294117647</v>
-      </c>
-    </row>
-    <row r="22" s="10" customFormat="1" spans="1:7">
+        <v>0.81835294117647095</v>
+      </c>
+      <c r="F21" s="13">
+        <v>0.29375000000000001</v>
+      </c>
+      <c r="G21" s="13">
+        <v>2.55735294117647E-2</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" s="9" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A22" s="4" t="s">
         <v>28</v>
       </c>
@@ -2225,16 +1441,16 @@
         <v>1220</v>
       </c>
       <c r="E22" s="5">
-        <v>0.993274336283186</v>
-      </c>
-      <c r="F22" s="14">
-        <v>0.38125</v>
-      </c>
-      <c r="G22" s="14">
-        <v>0.0310398230088496</v>
-      </c>
-    </row>
-    <row r="23" s="10" customFormat="1" spans="1:7">
+        <v>0.99327433628318595</v>
+      </c>
+      <c r="F22" s="13">
+        <v>0.38124999999999998</v>
+      </c>
+      <c r="G22" s="13">
+        <v>3.1039823008849599E-2</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" s="9" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A23" s="4" t="s">
         <v>29</v>
       </c>
@@ -2248,16 +1464,16 @@
         <v>1240</v>
       </c>
       <c r="E23" s="5">
-        <v>0.970434782608696</v>
-      </c>
-      <c r="F23" s="14">
-        <v>0.354285714285714</v>
-      </c>
-      <c r="G23" s="14">
-        <v>0.0277267080745342</v>
-      </c>
-    </row>
-    <row r="24" s="10" customFormat="1" spans="1:7">
+        <v>0.97043478260869598</v>
+      </c>
+      <c r="F23" s="13">
+        <v>0.35428571428571398</v>
+      </c>
+      <c r="G23" s="13">
+        <v>2.7726708074534201E-2</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" s="9" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A24" s="4" t="s">
         <v>30</v>
       </c>
@@ -2271,16 +1487,16 @@
         <v>1115</v>
       </c>
       <c r="E24" s="5">
-        <v>1.0660487804878</v>
-      </c>
-      <c r="F24" s="14">
-        <v>0.318571428571429</v>
-      </c>
-      <c r="G24" s="14">
-        <v>0.0304585365853659</v>
-      </c>
-    </row>
-    <row r="25" s="10" customFormat="1" spans="1:7">
+        <v>1.0660487804878001</v>
+      </c>
+      <c r="F24" s="13">
+        <v>0.31857142857142901</v>
+      </c>
+      <c r="G24" s="13">
+        <v>3.0458536585365899E-2</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7" s="9" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A25" s="4" t="s">
         <v>31</v>
       </c>
@@ -2290,20 +1506,20 @@
       <c r="C25" s="4">
         <v>150</v>
       </c>
-      <c r="D25" s="15">
+      <c r="D25" s="14">
         <v>1150</v>
       </c>
-      <c r="E25" s="12">
-        <v>1.11745283018868</v>
-      </c>
-      <c r="F25" s="14">
-        <v>0.338235294117647</v>
-      </c>
-      <c r="G25" s="14">
-        <v>0.0328662597114317</v>
-      </c>
-    </row>
-    <row r="26" s="10" customFormat="1" spans="1:7">
+      <c r="E25" s="11">
+        <v>1.1174528301886799</v>
+      </c>
+      <c r="F25" s="13">
+        <v>0.33823529411764702</v>
+      </c>
+      <c r="G25" s="13">
+        <v>3.28662597114317E-2</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7" s="9" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A26" s="4" t="s">
         <v>32</v>
       </c>
@@ -2316,17 +1532,17 @@
       <c r="D26" s="4">
         <v>1320</v>
       </c>
-      <c r="E26" s="16">
-        <v>1.27672131147541</v>
-      </c>
-      <c r="F26" s="14">
-        <v>0.169230769230769</v>
-      </c>
-      <c r="G26" s="14">
-        <v>0.0163682219419924</v>
-      </c>
-    </row>
-    <row r="27" s="10" customFormat="1" spans="1:7">
+      <c r="E26" s="15">
+        <v>1.2767213114754099</v>
+      </c>
+      <c r="F26" s="13">
+        <v>0.16923076923076899</v>
+      </c>
+      <c r="G26" s="13">
+        <v>1.63682219419924E-2</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7" s="9" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A27" s="4" t="s">
         <v>33</v>
       </c>
@@ -2342,14 +1558,14 @@
       <c r="E27" s="5">
         <v>1.01908045977012</v>
       </c>
-      <c r="F27" s="14">
-        <v>0.131494252873563</v>
-      </c>
-      <c r="G27" s="14">
-        <v>0.0117135685031048</v>
-      </c>
-    </row>
-    <row r="28" s="10" customFormat="1" spans="1:7">
+      <c r="F27" s="13">
+        <v>0.13149425287356301</v>
+      </c>
+      <c r="G27" s="13">
+        <v>1.17135685031048E-2</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7" s="9" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A28" s="4" t="s">
         <v>34</v>
       </c>
@@ -2365,14 +1581,14 @@
       <c r="E28" s="5">
         <v>1.26915254237288</v>
       </c>
-      <c r="F28" s="14">
-        <v>0.150588235294118</v>
-      </c>
-      <c r="G28" s="14">
-        <v>0.0149312063808574</v>
-      </c>
-    </row>
-    <row r="29" s="10" customFormat="1" spans="1:7">
+      <c r="F28" s="13">
+        <v>0.15058823529411799</v>
+      </c>
+      <c r="G28" s="13">
+        <v>1.49312063808574E-2</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7" s="9" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A29" s="4" t="s">
         <v>35</v>
       </c>
@@ -2386,16 +1602,16 @@
         <v>1530</v>
       </c>
       <c r="E29" s="5">
-        <v>1.63699300699301</v>
-      </c>
-      <c r="F29" s="14">
-        <v>0.20958904109589</v>
-      </c>
-      <c r="G29" s="14">
-        <v>0.0224245617396302</v>
-      </c>
-    </row>
-    <row r="30" s="10" customFormat="1" spans="1:7">
+        <v>1.6369930069930101</v>
+      </c>
+      <c r="F29" s="13">
+        <v>0.20958904109588999</v>
+      </c>
+      <c r="G29" s="13">
+        <v>2.24245617396302E-2</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7" s="9" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A30" s="4" t="s">
         <v>36</v>
       </c>
@@ -2411,14 +1627,14 @@
       <c r="E30" s="5">
         <v>1.60037037037037</v>
       </c>
-      <c r="F30" s="14">
+      <c r="F30" s="13">
         <v>0.179012345679012</v>
       </c>
-      <c r="G30" s="14">
-        <v>0.0197576588934614</v>
-      </c>
-    </row>
-    <row r="31" s="10" customFormat="1" spans="1:7">
+      <c r="G30" s="13">
+        <v>1.9757658893461399E-2</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7" s="9" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A31" s="4" t="s">
         <v>37</v>
       </c>
@@ -2432,16 +1648,16 @@
         <v>1170</v>
       </c>
       <c r="E31" s="5">
-        <v>1.1481308411215</v>
-      </c>
-      <c r="F31" s="14">
+        <v>1.1481308411215001</v>
+      </c>
+      <c r="F31" s="13">
         <v>0.131460674157303</v>
       </c>
-      <c r="G31" s="14">
-        <v>0.012900346529455</v>
-      </c>
-    </row>
-    <row r="32" s="10" customFormat="1" spans="1:7">
+      <c r="G31" s="13">
+        <v>1.2900346529455001E-2</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7" s="9" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A32" s="4" t="s">
         <v>38</v>
       </c>
@@ -2455,16 +1671,16 @@
         <v>1390</v>
       </c>
       <c r="E32" s="5">
-        <v>1.2822480620155</v>
-      </c>
-      <c r="F32" s="14">
-        <v>0.156179775280899</v>
-      </c>
-      <c r="G32" s="14">
-        <v>0.0144072815956798</v>
-      </c>
-    </row>
-    <row r="33" s="10" customFormat="1" spans="1:7">
+        <v>1.2822480620154999</v>
+      </c>
+      <c r="F32" s="13">
+        <v>0.15617977528089899</v>
+      </c>
+      <c r="G32" s="13">
+        <v>1.44072815956798E-2</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7" s="9" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A33" s="4" t="s">
         <v>39</v>
       </c>
@@ -2478,16 +1694,16 @@
         <v>1340</v>
       </c>
       <c r="E33" s="5">
-        <v>2.04241935483871</v>
-      </c>
-      <c r="F33" s="14">
-        <v>0.121818181818182</v>
-      </c>
-      <c r="G33" s="14">
-        <v>0.0185674486803519</v>
-      </c>
-    </row>
-    <row r="34" s="10" customFormat="1" spans="1:7">
+        <v>2.0424193548387102</v>
+      </c>
+      <c r="F33" s="13">
+        <v>0.12181818181818201</v>
+      </c>
+      <c r="G33" s="13">
+        <v>1.85674486803519E-2</v>
+      </c>
+    </row>
+    <row r="34" spans="1:7" s="9" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A34" s="4" t="s">
         <v>40</v>
       </c>
@@ -2501,16 +1717,16 @@
         <v>1304</v>
       </c>
       <c r="E34" s="5">
-        <v>1.31049833887043</v>
-      </c>
-      <c r="F34" s="14">
+        <v>1.3104983388704301</v>
+      </c>
+      <c r="F34" s="13">
         <v>0.135833333333333</v>
       </c>
-      <c r="G34" s="14">
-        <v>0.0136510243632337</v>
-      </c>
-    </row>
-    <row r="35" s="10" customFormat="1" spans="1:7">
+      <c r="G34" s="13">
+        <v>1.36510243632337E-2</v>
+      </c>
+    </row>
+    <row r="35" spans="1:7" s="9" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A35" s="4" t="s">
         <v>41</v>
       </c>
@@ -2526,14 +1742,14 @@
       <c r="E35" s="5">
         <v>1.12062015503876</v>
       </c>
-      <c r="F35" s="14">
+      <c r="F35" s="13">
         <v>0.136274509803922</v>
       </c>
-      <c r="G35" s="14">
-        <v>0.0109864721082231</v>
-      </c>
-    </row>
-    <row r="36" s="10" customFormat="1" spans="1:7">
+      <c r="G35" s="13">
+        <v>1.0986472108223099E-2</v>
+      </c>
+    </row>
+    <row r="36" spans="1:7" s="9" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A36" s="4" t="s">
         <v>42</v>
       </c>
@@ -2547,16 +1763,16 @@
         <v>1210</v>
       </c>
       <c r="E36" s="5">
-        <v>0.981081081081081</v>
-      </c>
-      <c r="F36" s="14">
-        <v>0.1375</v>
-      </c>
-      <c r="G36" s="14">
-        <v>0.0111486486486486</v>
-      </c>
-    </row>
-    <row r="37" s="10" customFormat="1" spans="1:7">
+        <v>0.98108108108108105</v>
+      </c>
+      <c r="F36" s="13">
+        <v>0.13750000000000001</v>
+      </c>
+      <c r="G36" s="13">
+        <v>1.1148648648648601E-2</v>
+      </c>
+    </row>
+    <row r="37" spans="1:7" s="9" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A37" s="4" t="s">
         <v>43</v>
       </c>
@@ -2570,16 +1786,16 @@
         <v>1354</v>
       </c>
       <c r="E37" s="5">
-        <v>1.19851674641148</v>
-      </c>
-      <c r="F37" s="14">
-        <v>0.147173913043478</v>
-      </c>
-      <c r="G37" s="14">
-        <v>0.0130273559392553</v>
-      </c>
-    </row>
-    <row r="38" s="10" customFormat="1" spans="1:7">
+        <v>1.1985167464114801</v>
+      </c>
+      <c r="F37" s="13">
+        <v>0.14717391304347799</v>
+      </c>
+      <c r="G37" s="13">
+        <v>1.3027355939255299E-2</v>
+      </c>
+    </row>
+    <row r="38" spans="1:7" s="9" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A38" s="4" t="s">
         <v>44</v>
       </c>
@@ -2593,16 +1809,16 @@
         <v>954</v>
       </c>
       <c r="E38" s="5">
-        <v>0.320373134328358</v>
-      </c>
-      <c r="F38" s="14">
+        <v>0.32037313432835801</v>
+      </c>
+      <c r="F38" s="13">
         <v>1.51428571428571</v>
       </c>
-      <c r="G38" s="14">
-        <v>0.0508528784648188</v>
-      </c>
-    </row>
-    <row r="39" s="10" customFormat="1" spans="1:7">
+      <c r="G38" s="13">
+        <v>5.0852878464818799E-2</v>
+      </c>
+    </row>
+    <row r="39" spans="1:7" s="9" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A39" s="4" t="s">
         <v>46</v>
       </c>
@@ -2616,16 +1832,16 @@
         <v>1014</v>
       </c>
       <c r="E39" s="5">
-        <v>0.316875</v>
-      </c>
-      <c r="F39" s="14">
+        <v>0.31687500000000002</v>
+      </c>
+      <c r="F39" s="13">
         <v>1.56</v>
       </c>
-      <c r="G39" s="14">
-        <v>0.04875</v>
-      </c>
-    </row>
-    <row r="40" s="10" customFormat="1" spans="1:7">
+      <c r="G39" s="13">
+        <v>4.8750000000000002E-2</v>
+      </c>
+    </row>
+    <row r="40" spans="1:7" s="9" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A40" s="4" t="s">
         <v>47</v>
       </c>
@@ -2639,16 +1855,16 @@
         <v>1030</v>
       </c>
       <c r="E40" s="5">
-        <v>0.374545454545455</v>
-      </c>
-      <c r="F40" s="14">
+        <v>0.37454545454545501</v>
+      </c>
+      <c r="F40" s="13">
         <v>1.37333333333333</v>
       </c>
-      <c r="G40" s="14">
-        <v>0.0499393939393939</v>
-      </c>
-    </row>
-    <row r="41" s="10" customFormat="1" spans="1:7">
+      <c r="G40" s="13">
+        <v>4.9939393939393902E-2</v>
+      </c>
+    </row>
+    <row r="41" spans="1:7" s="9" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A41" s="4" t="s">
         <v>48</v>
       </c>
@@ -2662,16 +1878,16 @@
         <v>930</v>
       </c>
       <c r="E41" s="5">
-        <v>0.405384615384615</v>
-      </c>
-      <c r="F41" s="14">
-        <v>1.25675675675676</v>
-      </c>
-      <c r="G41" s="14">
-        <v>0.0547817047817048</v>
-      </c>
-    </row>
-    <row r="42" s="10" customFormat="1" spans="1:7">
+        <v>0.40538461538461501</v>
+      </c>
+      <c r="F41" s="13">
+        <v>1.2567567567567599</v>
+      </c>
+      <c r="G41" s="13">
+        <v>5.4781704781704799E-2</v>
+      </c>
+    </row>
+    <row r="42" spans="1:7" s="9" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A42" s="4" t="s">
         <v>49</v>
       </c>
@@ -2685,16 +1901,16 @@
         <v>972</v>
       </c>
       <c r="E42" s="5">
-        <v>0.319270072992701</v>
-      </c>
-      <c r="F42" s="14">
+        <v>0.31927007299270099</v>
+      </c>
+      <c r="F42" s="13">
         <v>2.16</v>
       </c>
-      <c r="G42" s="14">
-        <v>0.0709489051094891</v>
-      </c>
-    </row>
-    <row r="43" s="10" customFormat="1" spans="1:7">
+      <c r="G42" s="13">
+        <v>7.0948905109489105E-2</v>
+      </c>
+    </row>
+    <row r="43" spans="1:7" s="9" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A43" s="4" t="s">
         <v>50</v>
       </c>
@@ -2708,16 +1924,16 @@
         <v>870</v>
       </c>
       <c r="E43" s="5">
-        <v>0.302083333333333</v>
-      </c>
-      <c r="F43" s="14">
+        <v>0.30208333333333298</v>
+      </c>
+      <c r="F43" s="13">
         <v>1.30827067669173</v>
       </c>
-      <c r="G43" s="14">
-        <v>0.0454260651629073</v>
-      </c>
-    </row>
-    <row r="44" s="10" customFormat="1" spans="1:7">
+      <c r="G43" s="13">
+        <v>4.54260651629073E-2</v>
+      </c>
+    </row>
+    <row r="44" spans="1:7" s="9" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A44" s="4" t="s">
         <v>51</v>
       </c>
@@ -2731,16 +1947,16 @@
         <v>1170</v>
       </c>
       <c r="E44" s="5">
-        <v>0.550588235294118</v>
-      </c>
-      <c r="F44" s="14">
-        <v>0.951219512195122</v>
-      </c>
-      <c r="G44" s="14">
-        <v>0.0447632711621234</v>
-      </c>
-    </row>
-    <row r="45" s="10" customFormat="1" spans="1:7">
+        <v>0.55058823529411804</v>
+      </c>
+      <c r="F44" s="13">
+        <v>0.95121951219512202</v>
+      </c>
+      <c r="G44" s="13">
+        <v>4.4763271162123398E-2</v>
+      </c>
+    </row>
+    <row r="45" spans="1:7" s="9" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A45" s="4" t="s">
         <v>52</v>
       </c>
@@ -2754,16 +1970,16 @@
         <v>1294</v>
       </c>
       <c r="E45" s="5">
-        <v>0.803094405594406</v>
-      </c>
-      <c r="F45" s="14">
-        <v>0.868456375838926</v>
-      </c>
-      <c r="G45" s="14">
-        <v>0.0538989533955977</v>
-      </c>
-    </row>
-    <row r="46" s="10" customFormat="1" spans="1:7">
+        <v>0.80309440559440604</v>
+      </c>
+      <c r="F45" s="13">
+        <v>0.86845637583892599</v>
+      </c>
+      <c r="G45" s="13">
+        <v>5.38989533955977E-2</v>
+      </c>
+    </row>
+    <row r="46" spans="1:7" s="9" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A46" s="4" t="s">
         <v>53</v>
       </c>
@@ -2777,16 +1993,16 @@
         <v>1218</v>
       </c>
       <c r="E46" s="5">
-        <v>0.729887640449438</v>
-      </c>
-      <c r="F46" s="14">
-        <v>0.929770992366412</v>
-      </c>
-      <c r="G46" s="14">
-        <v>0.0557166137747663</v>
-      </c>
-    </row>
-    <row r="47" s="10" customFormat="1" spans="1:7">
+        <v>0.72988764044943799</v>
+      </c>
+      <c r="F46" s="13">
+        <v>0.92977099236641203</v>
+      </c>
+      <c r="G46" s="13">
+        <v>5.5716613774766298E-2</v>
+      </c>
+    </row>
+    <row r="47" spans="1:7" s="9" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A47" s="4" t="s">
         <v>54</v>
       </c>
@@ -2802,14 +2018,14 @@
       <c r="E47" s="5">
         <v>0.71741935483871</v>
       </c>
-      <c r="F47" s="14">
-        <v>0.863354037267081</v>
-      </c>
-      <c r="G47" s="14">
-        <v>0.0445602083750751</v>
-      </c>
-    </row>
-    <row r="48" s="10" customFormat="1" spans="1:7">
+      <c r="F47" s="13">
+        <v>0.86335403726708104</v>
+      </c>
+      <c r="G47" s="13">
+        <v>4.45602083750751E-2</v>
+      </c>
+    </row>
+    <row r="48" spans="1:7" s="9" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A48" s="4" t="s">
         <v>55</v>
       </c>
@@ -2825,14 +2041,14 @@
       <c r="E48" s="5">
         <v>0.8</v>
       </c>
-      <c r="F48" s="14">
-        <v>0.729483282674772</v>
-      </c>
-      <c r="G48" s="14">
-        <v>0.0486322188449848</v>
-      </c>
-    </row>
-    <row r="49" s="10" customFormat="1" spans="1:7">
+      <c r="F48" s="13">
+        <v>0.72948328267477203</v>
+      </c>
+      <c r="G48" s="13">
+        <v>4.8632218844984802E-2</v>
+      </c>
+    </row>
+    <row r="49" spans="1:7" s="9" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A49" s="4" t="s">
         <v>56</v>
       </c>
@@ -2846,16 +2062,16 @@
         <v>1246</v>
       </c>
       <c r="E49" s="5">
-        <v>0.682116788321168</v>
-      </c>
-      <c r="F49" s="14">
-        <v>0.81437908496732</v>
-      </c>
-      <c r="G49" s="14">
-        <v>0.0445827966222985</v>
-      </c>
-    </row>
-    <row r="50" s="10" customFormat="1" spans="1:7">
+        <v>0.68211678832116796</v>
+      </c>
+      <c r="F49" s="13">
+        <v>0.81437908496732003</v>
+      </c>
+      <c r="G49" s="13">
+        <v>4.4582796622298498E-2</v>
+      </c>
+    </row>
+    <row r="50" spans="1:7" s="9" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A50" s="4" t="s">
         <v>57</v>
       </c>
@@ -2869,16 +2085,16 @@
         <v>1518</v>
       </c>
       <c r="E50" s="5">
-        <v>0.954298245614035</v>
-      </c>
-      <c r="F50" s="14">
-        <v>0.834065934065934</v>
-      </c>
-      <c r="G50" s="14">
-        <v>0.0524339695392327</v>
-      </c>
-    </row>
-    <row r="51" s="10" customFormat="1" spans="1:7">
+        <v>0.95429824561403498</v>
+      </c>
+      <c r="F50" s="13">
+        <v>0.83406593406593399</v>
+      </c>
+      <c r="G50" s="13">
+        <v>5.2433969539232697E-2</v>
+      </c>
+    </row>
+    <row r="51" spans="1:7" s="9" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A51" s="4" t="s">
         <v>58</v>
       </c>
@@ -2892,16 +2108,16 @@
         <v>1298</v>
       </c>
       <c r="E51" s="5">
-        <v>0.994982578397213</v>
-      </c>
-      <c r="F51" s="14">
-        <v>0.477205882352941</v>
-      </c>
-      <c r="G51" s="14">
-        <v>0.0365802418528387</v>
-      </c>
-    </row>
-    <row r="52" s="10" customFormat="1" spans="1:7">
+        <v>0.99498257839721305</v>
+      </c>
+      <c r="F51" s="13">
+        <v>0.47720588235294098</v>
+      </c>
+      <c r="G51" s="13">
+        <v>3.6580241852838702E-2</v>
+      </c>
+    </row>
+    <row r="52" spans="1:7" s="9" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A52" s="4" t="s">
         <v>59</v>
       </c>
@@ -2917,14 +2133,14 @@
       <c r="E52" s="5">
         <v>1.02964285714286</v>
       </c>
-      <c r="F52" s="14">
-        <v>0.525423728813559</v>
-      </c>
-      <c r="G52" s="14">
-        <v>0.0349031476997579</v>
-      </c>
-    </row>
-    <row r="53" s="10" customFormat="1" spans="1:7">
+      <c r="F52" s="13">
+        <v>0.52542372881355903</v>
+      </c>
+      <c r="G52" s="13">
+        <v>3.49031476997579E-2</v>
+      </c>
+    </row>
+    <row r="53" spans="1:7" s="9" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A53" s="4" t="s">
         <v>60</v>
       </c>
@@ -2938,16 +2154,16 @@
         <v>1510</v>
       </c>
       <c r="E53" s="5">
-        <v>1.09919117647059</v>
-      </c>
-      <c r="F53" s="14">
-        <v>0.511864406779661</v>
-      </c>
-      <c r="G53" s="14">
-        <v>0.0372607178464606</v>
-      </c>
-    </row>
-    <row r="54" s="10" customFormat="1" spans="1:7">
+        <v>1.0991911764705899</v>
+      </c>
+      <c r="F53" s="13">
+        <v>0.51186440677966105</v>
+      </c>
+      <c r="G53" s="13">
+        <v>3.7260717846460602E-2</v>
+      </c>
+    </row>
+    <row r="54" spans="1:7" s="9" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A54" s="4" t="s">
         <v>61</v>
       </c>
@@ -2961,16 +2177,16 @@
         <v>1230</v>
       </c>
       <c r="E54" s="5">
-        <v>0.785833333333333</v>
-      </c>
-      <c r="F54" s="14">
-        <v>0.656</v>
-      </c>
-      <c r="G54" s="14">
-        <v>0.0419111111111111</v>
-      </c>
-    </row>
-    <row r="55" s="10" customFormat="1" spans="1:7">
+        <v>0.78583333333333305</v>
+      </c>
+      <c r="F54" s="13">
+        <v>0.65600000000000003</v>
+      </c>
+      <c r="G54" s="13">
+        <v>4.19111111111111E-2</v>
+      </c>
+    </row>
+    <row r="55" spans="1:7" s="9" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A55" s="4" t="s">
         <v>62</v>
       </c>
@@ -2986,14 +2202,14 @@
       <c r="E55" s="5">
         <v>1.06778443113772</v>
       </c>
-      <c r="F55" s="14">
-        <v>0.588514851485149</v>
-      </c>
-      <c r="G55" s="14">
-        <v>0.0422884923222861</v>
-      </c>
-    </row>
-    <row r="56" s="10" customFormat="1" spans="1:7">
+      <c r="F55" s="13">
+        <v>0.58851485148514904</v>
+      </c>
+      <c r="G55" s="13">
+        <v>4.2288492322286098E-2</v>
+      </c>
+    </row>
+    <row r="56" spans="1:7" s="9" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A56" s="4" t="s">
         <v>63</v>
       </c>
@@ -3007,16 +2223,16 @@
         <v>1906</v>
       </c>
       <c r="E56" s="5">
-        <v>1.94290432801822</v>
-      </c>
-      <c r="F56" s="14">
+        <v>1.9429043280182201</v>
+      </c>
+      <c r="F56" s="13">
         <v>0.262534435261708</v>
       </c>
-      <c r="G56" s="14">
-        <v>0.0267617676035568</v>
-      </c>
-    </row>
-    <row r="57" s="10" customFormat="1" spans="1:7">
+      <c r="G56" s="13">
+        <v>2.6761767603556801E-2</v>
+      </c>
+    </row>
+    <row r="57" spans="1:7" s="9" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A57" s="4" t="s">
         <v>64</v>
       </c>
@@ -3030,16 +2246,16 @@
         <v>2310</v>
       </c>
       <c r="E57" s="5">
-        <v>2.37416666666667</v>
-      </c>
-      <c r="F57" s="14">
+        <v>2.3741666666666701</v>
+      </c>
+      <c r="F57" s="13">
         <v>0.23583460949464</v>
       </c>
-      <c r="G57" s="14">
-        <v>0.0242385570869491</v>
-      </c>
-    </row>
-    <row r="58" s="10" customFormat="1" spans="1:7">
+      <c r="G57" s="13">
+        <v>2.4238557086949102E-2</v>
+      </c>
+    </row>
+    <row r="58" spans="1:7" s="9" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A58" s="4" t="s">
         <v>65</v>
       </c>
@@ -3053,16 +2269,16 @@
         <v>1900</v>
       </c>
       <c r="E58" s="5">
-        <v>1.87828571428571</v>
-      </c>
-      <c r="F58" s="14">
-        <v>0.196078431372549</v>
-      </c>
-      <c r="G58" s="14">
-        <v>0.0193837535014006</v>
-      </c>
-    </row>
-    <row r="59" s="10" customFormat="1" spans="1:7">
+        <v>1.8782857142857099</v>
+      </c>
+      <c r="F58" s="13">
+        <v>0.19607843137254899</v>
+      </c>
+      <c r="G58" s="13">
+        <v>1.9383753501400602E-2</v>
+      </c>
+    </row>
+    <row r="59" spans="1:7" s="9" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A59" s="4" t="s">
         <v>66</v>
       </c>
@@ -3076,16 +2292,16 @@
         <v>2250</v>
       </c>
       <c r="E59" s="5">
-        <v>2.04642857142857</v>
-      </c>
-      <c r="F59" s="14">
+        <v>2.0464285714285699</v>
+      </c>
+      <c r="F59" s="13">
         <v>0.260567458019687</v>
       </c>
-      <c r="G59" s="14">
-        <v>0.0236992307056001</v>
-      </c>
-    </row>
-    <row r="60" s="10" customFormat="1" spans="1:7">
+      <c r="G59" s="13">
+        <v>2.3699230705600101E-2</v>
+      </c>
+    </row>
+    <row r="60" spans="1:7" s="9" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A60" s="4" t="s">
         <v>67</v>
       </c>
@@ -3101,14 +2317,14 @@
       <c r="E60" s="5">
         <v>2.35137614678899</v>
       </c>
-      <c r="F60" s="14">
-        <v>0.23582995951417</v>
-      </c>
-      <c r="G60" s="14">
-        <v>0.0237993537124392</v>
-      </c>
-    </row>
-    <row r="61" s="10" customFormat="1" spans="1:7">
+      <c r="F60" s="13">
+        <v>0.23582995951416999</v>
+      </c>
+      <c r="G60" s="13">
+        <v>2.37993537124392E-2</v>
+      </c>
+    </row>
+    <row r="61" spans="1:7" s="9" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A61" s="4" t="s">
         <v>68</v>
       </c>
@@ -3122,16 +2338,16 @@
         <v>2244</v>
       </c>
       <c r="E61" s="5">
-        <v>2.1432664756447</v>
-      </c>
-      <c r="F61" s="14">
+        <v>2.1432664756447002</v>
+      </c>
+      <c r="F61" s="13">
         <v>0.213918017159199</v>
       </c>
-      <c r="G61" s="14">
-        <v>0.0204315202635338</v>
-      </c>
-    </row>
-    <row r="62" s="10" customFormat="1" spans="1:7">
+      <c r="G61" s="13">
+        <v>2.0431520263533801E-2</v>
+      </c>
+    </row>
+    <row r="62" spans="1:7" s="9" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A62" s="4" t="s">
         <v>69</v>
       </c>
@@ -3147,14 +2363,14 @@
       <c r="E62" s="5">
         <v>2.1</v>
       </c>
-      <c r="F62" s="14">
-        <v>0.164675767918089</v>
-      </c>
-      <c r="G62" s="14">
-        <v>0.0179180887372014</v>
-      </c>
-    </row>
-    <row r="63" s="10" customFormat="1" spans="1:7">
+      <c r="F62" s="13">
+        <v>0.16467576791808899</v>
+      </c>
+      <c r="G62" s="13">
+        <v>1.7918088737201399E-2</v>
+      </c>
+    </row>
+    <row r="63" spans="1:7" s="9" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A63" s="4" t="s">
         <v>70</v>
       </c>
@@ -3170,14 +2386,14 @@
       <c r="E63" s="5">
         <v>2.39</v>
       </c>
-      <c r="F63" s="14">
-        <v>0.134725121781489</v>
-      </c>
-      <c r="G63" s="14">
-        <v>0.0166318719554628</v>
-      </c>
-    </row>
-    <row r="64" s="10" customFormat="1" spans="1:7">
+      <c r="F63" s="13">
+        <v>0.13472512178148899</v>
+      </c>
+      <c r="G63" s="13">
+        <v>1.6631871955462799E-2</v>
+      </c>
+    </row>
+    <row r="64" spans="1:7" s="9" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A64" s="4" t="s">
         <v>71</v>
       </c>
@@ -3191,16 +2407,16 @@
         <v>1754</v>
       </c>
       <c r="E64" s="5">
-        <v>2.51</v>
-      </c>
-      <c r="F64" s="14">
+        <v>2.5099999999999998</v>
+      </c>
+      <c r="F64" s="13">
         <v>0.132477341389728</v>
       </c>
-      <c r="G64" s="14">
-        <v>0.0189577039274924</v>
-      </c>
-    </row>
-    <row r="65" s="10" customFormat="1" spans="1:7">
+      <c r="G64" s="13">
+        <v>1.8957703927492402E-2</v>
+      </c>
+    </row>
+    <row r="65" spans="1:7" s="9" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A65" s="4" t="s">
         <v>72</v>
       </c>
@@ -3214,16 +2430,16 @@
         <v>2770</v>
       </c>
       <c r="E65" s="5">
-        <v>2.22</v>
-      </c>
-      <c r="F65" s="14">
-        <v>0.216575449569977</v>
-      </c>
-      <c r="G65" s="14">
-        <v>0.017357310398749</v>
-      </c>
-    </row>
-    <row r="66" s="10" customFormat="1" spans="1:7">
+        <v>2.2200000000000002</v>
+      </c>
+      <c r="F65" s="13">
+        <v>0.21657544956997701</v>
+      </c>
+      <c r="G65" s="13">
+        <v>1.7357310398749E-2</v>
+      </c>
+    </row>
+    <row r="66" spans="1:7" s="9" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A66" s="4" t="s">
         <v>73</v>
       </c>
@@ -3237,16 +2453,16 @@
         <v>1778</v>
       </c>
       <c r="E66" s="5">
-        <v>2.45</v>
-      </c>
-      <c r="F66" s="14">
-        <v>0.134493192133132</v>
-      </c>
-      <c r="G66" s="14">
-        <v>0.0185325264750378</v>
-      </c>
-    </row>
-    <row r="67" s="10" customFormat="1" spans="1:7">
+        <v>2.4500000000000002</v>
+      </c>
+      <c r="F66" s="13">
+        <v>0.13449319213313199</v>
+      </c>
+      <c r="G66" s="13">
+        <v>1.8532526475037801E-2</v>
+      </c>
+    </row>
+    <row r="67" spans="1:7" s="9" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A67" s="4" t="s">
         <v>74</v>
       </c>
@@ -3262,14 +2478,14 @@
       <c r="E67" s="5">
         <v>2.83</v>
       </c>
-      <c r="F67" s="14">
-        <v>0.164425531914894</v>
-      </c>
-      <c r="G67" s="14">
-        <v>0.0240851063829787</v>
-      </c>
-    </row>
-    <row r="68" s="10" customFormat="1" spans="1:7">
+      <c r="F67" s="13">
+        <v>0.16442553191489401</v>
+      </c>
+      <c r="G67" s="13">
+        <v>2.4085106382978699E-2</v>
+      </c>
+    </row>
+    <row r="68" spans="1:7" s="9" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A68" s="4" t="s">
         <v>75</v>
       </c>
@@ -3283,16 +2499,16 @@
         <v>2040</v>
       </c>
       <c r="E68" s="5">
-        <v>2.35301587301587</v>
-      </c>
-      <c r="F68" s="14">
-        <v>0.0841237113402062</v>
-      </c>
-      <c r="G68" s="14">
-        <v>0.00970315823924071</v>
-      </c>
-    </row>
-    <row r="69" s="10" customFormat="1" spans="1:7">
+        <v>2.3530158730158699</v>
+      </c>
+      <c r="F68" s="13">
+        <v>8.41237113402062E-2</v>
+      </c>
+      <c r="G68" s="13">
+        <v>9.7031582392407105E-3</v>
+      </c>
+    </row>
+    <row r="69" spans="1:7" s="9" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A69" s="4" t="s">
         <v>76</v>
       </c>
@@ -3306,16 +2522,16 @@
         <v>2040</v>
       </c>
       <c r="E69" s="5">
-        <v>2.38539682539683</v>
-      </c>
-      <c r="F69" s="14">
-        <v>0.0995121951219512</v>
-      </c>
-      <c r="G69" s="14">
-        <v>0.0116360820751065</v>
-      </c>
-    </row>
-    <row r="70" s="10" customFormat="1" spans="1:7">
+        <v>2.3853968253968301</v>
+      </c>
+      <c r="F69" s="13">
+        <v>9.9512195121951197E-2</v>
+      </c>
+      <c r="G69" s="13">
+        <v>1.16360820751065E-2</v>
+      </c>
+    </row>
+    <row r="70" spans="1:7" s="9" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A70" s="4" t="s">
         <v>77</v>
       </c>
@@ -3329,16 +2545,16 @@
         <v>1854</v>
       </c>
       <c r="E70" s="5">
-        <v>2.13253521126761</v>
-      </c>
-      <c r="F70" s="14">
+        <v>2.1325352112676099</v>
+      </c>
+      <c r="F70" s="13">
         <v>0.102430939226519</v>
       </c>
-      <c r="G70" s="14">
-        <v>0.0117819624931912</v>
-      </c>
-    </row>
-    <row r="71" s="10" customFormat="1" spans="1:7">
+      <c r="G70" s="13">
+        <v>1.17819624931912E-2</v>
+      </c>
+    </row>
+    <row r="71" spans="1:7" s="9" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A71" s="4" t="s">
         <v>78</v>
       </c>
@@ -3352,16 +2568,16 @@
         <v>2140</v>
       </c>
       <c r="E71" s="5">
-        <v>2.66693467336683</v>
-      </c>
-      <c r="F71" s="14">
-        <v>0.0962230215827338</v>
-      </c>
-      <c r="G71" s="14">
-        <v>0.0119916127399588</v>
-      </c>
-    </row>
-    <row r="72" s="10" customFormat="1" spans="1:7">
+        <v>2.6669346733668302</v>
+      </c>
+      <c r="F71" s="13">
+        <v>9.6223021582733798E-2</v>
+      </c>
+      <c r="G71" s="13">
+        <v>1.19916127399588E-2</v>
+      </c>
+    </row>
+    <row r="72" spans="1:7" s="9" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A72" s="4" t="s">
         <v>79</v>
       </c>
@@ -3375,16 +2591,16 @@
         <v>1890</v>
       </c>
       <c r="E72" s="5">
-        <v>2.42224137931034</v>
-      </c>
-      <c r="F72" s="14">
-        <v>0.0924657534246575</v>
-      </c>
-      <c r="G72" s="14">
-        <v>0.0118504959848843</v>
-      </c>
-    </row>
-    <row r="73" s="10" customFormat="1" spans="1:7">
+        <v>2.4222413793103401</v>
+      </c>
+      <c r="F72" s="13">
+        <v>9.2465753424657501E-2</v>
+      </c>
+      <c r="G72" s="13">
+        <v>1.18504959848843E-2</v>
+      </c>
+    </row>
+    <row r="73" spans="1:7" s="9" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A73" s="4" t="s">
         <v>80</v>
       </c>
@@ -3400,38 +2616,37 @@
       <c r="E73" s="5">
         <v>2.47147928994083</v>
       </c>
-      <c r="F73" s="14">
-        <v>0.0735705717712915</v>
-      </c>
-      <c r="G73" s="14">
-        <v>0.00988196437401371</v>
+      <c r="F73" s="13">
+        <v>7.3570571771291504E-2</v>
+      </c>
+      <c r="G73" s="13">
+        <v>9.8819643740137107E-3</v>
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:H75"/>
-  <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="14" outlineLevelCol="7"/>
+  <sheetFormatPr defaultColWidth="8.7265625" defaultRowHeight="14" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="8.72727272727273" style="2"/>
-    <col min="2" max="2" width="10.6363636363636" style="2" customWidth="1"/>
-    <col min="3" max="3" width="8.72727272727273" style="2"/>
-    <col min="4" max="4" width="17.0909090909091" style="2" customWidth="1"/>
-    <col min="5" max="5" width="17.3636363636364" style="2" customWidth="1"/>
-    <col min="6" max="6" width="16.5454545454545" style="2" customWidth="1"/>
-    <col min="7" max="7" width="10.1818181818182" style="2" customWidth="1"/>
-    <col min="8" max="8" width="20.9090909090909" style="2" customWidth="1"/>
-    <col min="9" max="9" width="0.0909090909090909" style="1" customWidth="1"/>
-    <col min="10" max="16384" width="8.72727272727273" style="1"/>
+    <col min="1" max="1" width="8.7265625" style="2"/>
+    <col min="2" max="2" width="10.6328125" style="2" customWidth="1"/>
+    <col min="3" max="3" width="8.7265625" style="2"/>
+    <col min="4" max="4" width="17.08984375" style="2" customWidth="1"/>
+    <col min="5" max="5" width="17.36328125" style="2" customWidth="1"/>
+    <col min="6" max="6" width="16.54296875" style="2" customWidth="1"/>
+    <col min="7" max="7" width="10.1796875" style="2" customWidth="1"/>
+    <col min="8" max="8" width="20.90625" style="2" customWidth="1"/>
+    <col min="9" max="9" width="8.984375E-2" style="1" customWidth="1"/>
+    <col min="10" max="16384" width="8.7265625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" ht="16" spans="1:8">
+    <row r="1" spans="1:8" ht="16" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
@@ -3457,35 +2672,35 @@
         <v>85</v>
       </c>
     </row>
-    <row r="2" s="1" customFormat="1" spans="1:8">
-      <c r="A2" s="8" t="s">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A2" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="B2" s="8" t="s">
-        <v>8</v>
-      </c>
-      <c r="C2" s="8">
+      <c r="B2" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="C2" s="7">
         <v>30</v>
       </c>
-      <c r="D2" s="9">
-        <v>364.903513675112</v>
-      </c>
-      <c r="E2" s="9">
-        <v>337.120216078617</v>
-      </c>
-      <c r="F2" s="9">
+      <c r="D2" s="8">
+        <v>364.90351367511198</v>
+      </c>
+      <c r="E2" s="8">
+        <v>337.12021607861698</v>
+      </c>
+      <c r="F2" s="8">
         <v>156.286527006867</v>
       </c>
-      <c r="G2" s="9">
+      <c r="G2" s="8">
         <f t="shared" ref="G2:G65" si="0">D2/E2</f>
-        <v>1.0824136206356</v>
-      </c>
-      <c r="H2" s="9">
+        <v>1.0824136206356001</v>
+      </c>
+      <c r="H2" s="8">
         <f t="shared" ref="H2:H65" si="1">D2*F2*PI()</f>
         <v>179163.467175372</v>
       </c>
     </row>
-    <row r="3" s="1" customFormat="1" spans="1:8">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3" s="4" t="s">
         <v>9</v>
       </c>
@@ -3499,21 +2714,21 @@
         <v>251.184816102045</v>
       </c>
       <c r="E3" s="5">
-        <v>375.21552476761</v>
+        <v>375.21552476761002</v>
       </c>
       <c r="F3" s="5">
-        <v>156.665223941334</v>
+        <v>156.66522394133401</v>
       </c>
       <c r="G3" s="5">
         <f t="shared" si="0"/>
-        <v>0.66944142638452</v>
+        <v>0.66944142638451998</v>
       </c>
       <c r="H3" s="5">
         <f t="shared" si="1"/>
         <v>123627.719946367</v>
       </c>
     </row>
-    <row r="4" s="1" customFormat="1" spans="1:8">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4" s="4" t="s">
         <v>10</v>
       </c>
@@ -3524,24 +2739,24 @@
         <v>30</v>
       </c>
       <c r="D4" s="5">
-        <v>333.56286407767</v>
+        <v>333.56286407766999</v>
       </c>
       <c r="E4" s="5">
-        <v>369.223088138455</v>
+        <v>369.22308813845501</v>
       </c>
       <c r="F4" s="5">
         <v>139.055216146053</v>
       </c>
       <c r="G4" s="5">
         <f t="shared" si="0"/>
-        <v>0.903418217315238</v>
+        <v>0.90341821731523797</v>
       </c>
       <c r="H4" s="5">
         <f t="shared" si="1"/>
         <v>145718.553447112</v>
       </c>
     </row>
-    <row r="5" s="1" customFormat="1" spans="1:8">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
         <v>11</v>
       </c>
@@ -3555,21 +2770,21 @@
         <v>304.55481230477</v>
       </c>
       <c r="E5" s="5">
-        <v>323.461667138033</v>
+        <v>323.46166713803302</v>
       </c>
       <c r="F5" s="5">
         <v>150.291969902913</v>
       </c>
       <c r="G5" s="5">
         <f t="shared" si="0"/>
-        <v>0.941548391187897</v>
+        <v>0.94154839118789702</v>
       </c>
       <c r="H5" s="5">
         <f t="shared" si="1"/>
         <v>143797.427197304</v>
       </c>
     </row>
-    <row r="6" s="1" customFormat="1" spans="1:8">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
         <v>12</v>
       </c>
@@ -3583,7 +2798,7 @@
         <v>471.56237943225</v>
       </c>
       <c r="E6" s="5">
-        <v>411.180735341916</v>
+        <v>411.18073534191598</v>
       </c>
       <c r="F6" s="5">
         <v>165.1366338645</v>
@@ -3594,10 +2809,10 @@
       </c>
       <c r="H6" s="5">
         <f t="shared" si="1"/>
-        <v>244642.806826342</v>
-      </c>
-    </row>
-    <row r="7" s="1" customFormat="1" spans="1:8">
+        <v>244642.80682634201</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A7" s="4" t="s">
         <v>13</v>
       </c>
@@ -3608,24 +2823,24 @@
         <v>30</v>
       </c>
       <c r="D7" s="5">
-        <v>417.579305933118</v>
+        <v>417.57930593311801</v>
       </c>
       <c r="E7" s="5">
-        <v>509.363433926645</v>
+        <v>509.36343392664497</v>
       </c>
       <c r="F7" s="5">
-        <v>149.376534600863</v>
+        <v>149.37653460086301</v>
       </c>
       <c r="G7" s="5">
         <f t="shared" si="0"/>
-        <v>0.819806209319012</v>
+        <v>0.81980620931901205</v>
       </c>
       <c r="H7" s="5">
         <f t="shared" si="1"/>
         <v>195961.710109459</v>
       </c>
     </row>
-    <row r="8" s="1" customFormat="1" spans="1:8">
+    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A8" s="4" t="s">
         <v>14</v>
       </c>
@@ -3636,13 +2851,13 @@
         <v>60</v>
       </c>
       <c r="D8" s="5">
-        <v>400.150071633601</v>
+        <v>400.15007163360099</v>
       </c>
       <c r="E8" s="5">
-        <v>525.834924345716</v>
+        <v>525.83492434571599</v>
       </c>
       <c r="F8" s="5">
-        <v>161.820264436471</v>
+        <v>161.82026443647101</v>
       </c>
       <c r="G8" s="5">
         <f t="shared" si="0"/>
@@ -3653,7 +2868,7 @@
         <v>203425.634001937</v>
       </c>
     </row>
-    <row r="9" s="1" customFormat="1" spans="1:8">
+    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A9" s="4" t="s">
         <v>15</v>
       </c>
@@ -3664,13 +2879,13 @@
         <v>60</v>
       </c>
       <c r="D9" s="5">
-        <v>266.967906090027</v>
+        <v>266.96790609002699</v>
       </c>
       <c r="E9" s="5">
-        <v>491.270687191086</v>
+        <v>491.27068719108598</v>
       </c>
       <c r="F9" s="5">
-        <v>147.955722252869</v>
+        <v>147.95572225286901</v>
       </c>
       <c r="G9" s="5">
         <f t="shared" si="0"/>
@@ -3681,7 +2896,7 @@
         <v>124091.117110573</v>
       </c>
     </row>
-    <row r="10" s="1" customFormat="1" spans="1:8">
+    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A10" s="4" t="s">
         <v>16</v>
       </c>
@@ -3692,13 +2907,13 @@
         <v>60</v>
       </c>
       <c r="D10" s="5">
-        <v>385.084243440042</v>
+        <v>385.08424344004197</v>
       </c>
       <c r="E10" s="5">
-        <v>597.91316254264</v>
+        <v>597.91316254263995</v>
       </c>
       <c r="F10" s="5">
-        <v>172.287268210443</v>
+        <v>172.28726821044299</v>
       </c>
       <c r="G10" s="5">
         <f t="shared" si="0"/>
@@ -3706,10 +2921,10 @@
       </c>
       <c r="H10" s="5">
         <f t="shared" si="1"/>
-        <v>208429.317507477</v>
-      </c>
-    </row>
-    <row r="11" s="1" customFormat="1" spans="1:8">
+        <v>208429.31750747701</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A11" s="4" t="s">
         <v>17</v>
       </c>
@@ -3720,24 +2935,24 @@
         <v>60</v>
       </c>
       <c r="D11" s="5">
-        <v>337.818456273338</v>
+        <v>337.81845627333797</v>
       </c>
       <c r="E11" s="5">
-        <v>569.850339693802</v>
+        <v>569.85033969380197</v>
       </c>
       <c r="F11" s="5">
-        <v>175.165632673637</v>
+        <v>175.16563267363699</v>
       </c>
       <c r="G11" s="5">
         <f t="shared" si="0"/>
-        <v>0.592819610241626</v>
+        <v>0.59281961024162599</v>
       </c>
       <c r="H11" s="5">
         <f t="shared" si="1"/>
-        <v>185901.180548894</v>
-      </c>
-    </row>
-    <row r="12" s="1" customFormat="1" spans="1:8">
+        <v>185901.18054889399</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A12" s="4" t="s">
         <v>18</v>
       </c>
@@ -3748,13 +2963,13 @@
         <v>60</v>
       </c>
       <c r="D12" s="5">
-        <v>397.963914714132</v>
+        <v>397.96391471413199</v>
       </c>
       <c r="E12" s="5">
-        <v>509.435891423948</v>
+        <v>509.43589142394802</v>
       </c>
       <c r="F12" s="5">
-        <v>181.024764476807</v>
+        <v>181.02476447680701</v>
       </c>
       <c r="G12" s="5">
         <f t="shared" si="0"/>
@@ -3762,10 +2977,10 @@
       </c>
       <c r="H12" s="5">
         <f t="shared" si="1"/>
-        <v>226324.494017749</v>
-      </c>
-    </row>
-    <row r="13" s="1" customFormat="1" spans="1:8">
+        <v>226324.49401774901</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A13" s="4" t="s">
         <v>19</v>
       </c>
@@ -3779,21 +2994,21 @@
         <v>346.409379761016</v>
       </c>
       <c r="E13" s="5">
-        <v>426.873720786657</v>
+        <v>426.87372078665697</v>
       </c>
       <c r="F13" s="5">
-        <v>160.344448381877</v>
+        <v>160.34444838187699</v>
       </c>
       <c r="G13" s="5">
         <f t="shared" si="0"/>
-        <v>0.811503175043527</v>
+        <v>0.81150317504352698</v>
       </c>
       <c r="H13" s="5">
         <f t="shared" si="1"/>
-        <v>174499.201322377</v>
-      </c>
-    </row>
-    <row r="14" s="1" customFormat="1" spans="1:8">
+        <v>174499.20132237699</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A14" s="4" t="s">
         <v>20</v>
       </c>
@@ -3804,24 +3019,24 @@
         <v>90</v>
       </c>
       <c r="D14" s="5">
-        <v>488.055235353675</v>
+        <v>488.05523535367502</v>
       </c>
       <c r="E14" s="5">
-        <v>516.262820943135</v>
+        <v>516.26282094313501</v>
       </c>
       <c r="F14" s="5">
-        <v>182.3607389043</v>
+        <v>182.36073890430001</v>
       </c>
       <c r="G14" s="5">
         <f t="shared" si="0"/>
-        <v>0.945361965949961</v>
+        <v>0.94536196594996103</v>
       </c>
       <c r="H14" s="5">
         <f t="shared" si="1"/>
-        <v>279608.385439272</v>
-      </c>
-    </row>
-    <row r="15" s="1" customFormat="1" spans="1:8">
+        <v>279608.38543927198</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A15" s="4" t="s">
         <v>21</v>
       </c>
@@ -3835,22 +3050,21 @@
         <v>421.299719104291</v>
       </c>
       <c r="E15" s="5">
-        <v>475.631695537112</v>
+        <v>475.63169553711202</v>
       </c>
       <c r="F15" s="5">
-        <f>AVERAGE([1]Sheet1!G33:G63)</f>
-        <v>158.334757265894</v>
+        <v>158.33475726589401</v>
       </c>
       <c r="G15" s="5">
         <f t="shared" si="0"/>
-        <v>0.885768806110648</v>
+        <v>0.88576880611064801</v>
       </c>
       <c r="H15" s="5">
         <f t="shared" si="1"/>
         <v>209564.300877703</v>
       </c>
     </row>
-    <row r="16" s="1" customFormat="1" spans="1:8">
+    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A16" s="4" t="s">
         <v>22</v>
       </c>
@@ -3861,24 +3075,24 @@
         <v>90</v>
       </c>
       <c r="D16" s="5">
-        <v>399.280612230313</v>
+        <v>399.28061223031301</v>
       </c>
       <c r="E16" s="5">
-        <v>461.069755933118</v>
+        <v>461.06975593311802</v>
       </c>
       <c r="F16" s="5">
-        <v>152.371588403452</v>
+        <v>152.37158840345199</v>
       </c>
       <c r="G16" s="5">
         <f t="shared" si="0"/>
-        <v>0.865987428349631</v>
+        <v>0.86598742834963105</v>
       </c>
       <c r="H16" s="5">
         <f t="shared" si="1"/>
         <v>191131.421752661</v>
       </c>
     </row>
-    <row r="17" s="1" customFormat="1" spans="1:8">
+    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A17" s="4" t="s">
         <v>23</v>
       </c>
@@ -3889,24 +3103,24 @@
         <v>90</v>
       </c>
       <c r="D17" s="5">
-        <v>458.386311279269</v>
+        <v>458.38631127926902</v>
       </c>
       <c r="E17" s="5">
-        <v>483.752687692747</v>
+        <v>483.75268769274697</v>
       </c>
       <c r="F17" s="5">
         <v>161.939522015991</v>
       </c>
       <c r="G17" s="5">
         <f t="shared" si="0"/>
-        <v>0.947563337509374</v>
+        <v>0.94756333750937405</v>
       </c>
       <c r="H17" s="5">
         <f t="shared" si="1"/>
-        <v>233203.124908215</v>
-      </c>
-    </row>
-    <row r="18" s="1" customFormat="1" spans="1:8">
+        <v>233203.12490821499</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A18" s="4" t="s">
         <v>24</v>
       </c>
@@ -3917,24 +3131,24 @@
         <v>90</v>
       </c>
       <c r="D18" s="5">
-        <v>368.15126351755</v>
+        <v>368.15126351754998</v>
       </c>
       <c r="E18" s="5">
-        <v>522.31337596465</v>
+        <v>522.31337596465005</v>
       </c>
       <c r="F18" s="5">
-        <v>147.03479223301</v>
+        <v>147.03479223300999</v>
       </c>
       <c r="G18" s="5">
         <f t="shared" si="0"/>
-        <v>0.704847473679223</v>
+        <v>0.70484747367922296</v>
       </c>
       <c r="H18" s="5">
         <f t="shared" si="1"/>
-        <v>170057.691863105</v>
-      </c>
-    </row>
-    <row r="19" s="1" customFormat="1" spans="1:8">
+        <v>170057.69186310499</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A19" s="4" t="s">
         <v>25</v>
       </c>
@@ -3945,24 +3159,24 @@
         <v>90</v>
       </c>
       <c r="D19" s="5">
-        <v>449.846155887478</v>
+        <v>449.84615588747801</v>
       </c>
       <c r="E19" s="5">
-        <v>457.134639756037</v>
+        <v>457.13463975603702</v>
       </c>
       <c r="F19" s="5">
-        <v>163.526061065472</v>
+        <v>163.52606106547199</v>
       </c>
       <c r="G19" s="5">
         <f t="shared" si="0"/>
-        <v>0.984056154938403</v>
+        <v>0.98405615493840304</v>
       </c>
       <c r="H19" s="5">
         <f t="shared" si="1"/>
-        <v>231100.487765716</v>
-      </c>
-    </row>
-    <row r="20" s="1" customFormat="1" spans="1:8">
+        <v>231100.48776571601</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A20" s="4" t="s">
         <v>26</v>
       </c>
@@ -3973,13 +3187,13 @@
         <v>150</v>
       </c>
       <c r="D20" s="5">
-        <v>515.406350793275</v>
+        <v>515.40635079327501</v>
       </c>
       <c r="E20" s="5">
-        <v>476.169028569737</v>
+        <v>476.16902856973701</v>
       </c>
       <c r="F20" s="5">
-        <v>187.711611543926</v>
+        <v>187.71161154392601</v>
       </c>
       <c r="G20" s="5">
         <f t="shared" si="0"/>
@@ -3987,10 +3201,10 @@
       </c>
       <c r="H20" s="5">
         <f t="shared" si="1"/>
-        <v>303942.041723197</v>
-      </c>
-    </row>
-    <row r="21" s="1" customFormat="1" spans="1:8">
+        <v>303942.04172319698</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A21" s="4" t="s">
         <v>27</v>
       </c>
@@ -4001,24 +3215,24 @@
         <v>150</v>
       </c>
       <c r="D21" s="5">
-        <v>457.228521436452</v>
+        <v>457.22852143645201</v>
       </c>
       <c r="E21" s="5">
-        <v>467.949895995146</v>
+        <v>467.94989599514599</v>
       </c>
       <c r="F21" s="5">
-        <v>202.671077967785</v>
+        <v>202.67107796778501</v>
       </c>
       <c r="G21" s="5">
         <f t="shared" si="0"/>
-        <v>0.977088627114888</v>
+        <v>0.97708862711488798</v>
       </c>
       <c r="H21" s="5">
         <f t="shared" si="1"/>
-        <v>291121.958001759</v>
-      </c>
-    </row>
-    <row r="22" s="1" customFormat="1" spans="1:8">
+        <v>291121.95800175902</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A22" s="4" t="s">
         <v>28</v>
       </c>
@@ -4029,24 +3243,24 @@
         <v>150</v>
       </c>
       <c r="D22" s="5">
-        <v>445.042652305825</v>
+        <v>445.04265230582502</v>
       </c>
       <c r="E22" s="5">
-        <v>554.925629314995</v>
+        <v>554.92562931499504</v>
       </c>
       <c r="F22" s="5">
-        <v>180.529143635383</v>
+        <v>180.52914363538301</v>
       </c>
       <c r="G22" s="5">
         <f t="shared" si="0"/>
-        <v>0.801986119933205</v>
+        <v>0.80198611993320501</v>
       </c>
       <c r="H22" s="5">
         <f t="shared" si="1"/>
-        <v>252405.509188616</v>
-      </c>
-    </row>
-    <row r="23" s="1" customFormat="1" spans="1:8">
+        <v>252405.50918861601</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A23" s="4" t="s">
         <v>29</v>
       </c>
@@ -4063,18 +3277,18 @@
         <v>514.544768171084</v>
       </c>
       <c r="F23" s="5">
-        <v>189.718442364209</v>
+        <v>189.71844236420901</v>
       </c>
       <c r="G23" s="5">
         <f t="shared" si="0"/>
-        <v>0.788944836573795</v>
+        <v>0.78894483657379499</v>
       </c>
       <c r="H23" s="5">
         <f t="shared" si="1"/>
-        <v>241952.006420574</v>
-      </c>
-    </row>
-    <row r="24" s="1" customFormat="1" spans="1:8">
+        <v>241952.00642057401</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A24" s="4" t="s">
         <v>30</v>
       </c>
@@ -4085,24 +3299,24 @@
         <v>150</v>
       </c>
       <c r="D24" s="5">
-        <v>407.473501965427</v>
+        <v>407.47350196542698</v>
       </c>
       <c r="E24" s="5">
-        <v>537.951891096377</v>
+        <v>537.95189109637704</v>
       </c>
       <c r="F24" s="5">
         <v>186.864525479517</v>
       </c>
       <c r="G24" s="5">
         <f t="shared" si="0"/>
-        <v>0.757453424199276</v>
+        <v>0.75745342419927597</v>
       </c>
       <c r="H24" s="5">
         <f t="shared" si="1"/>
         <v>239208.224108636</v>
       </c>
     </row>
-    <row r="25" s="1" customFormat="1" spans="1:8">
+    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A25" s="4" t="s">
         <v>31</v>
       </c>
@@ -4116,21 +3330,21 @@
         <v>450.39360210356</v>
       </c>
       <c r="E25" s="5">
-        <v>551.144301904406</v>
+        <v>551.14430190440601</v>
       </c>
       <c r="F25" s="5">
-        <v>153.438936245955</v>
+        <v>153.43893624595501</v>
       </c>
       <c r="G25" s="5">
         <f t="shared" si="0"/>
-        <v>0.817197239538329</v>
+        <v>0.81719723953832901</v>
       </c>
       <c r="H25" s="5">
         <f t="shared" si="1"/>
         <v>217108.918693313</v>
       </c>
     </row>
-    <row r="26" s="1" customFormat="1" spans="1:8">
+    <row r="26" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A26" s="4" t="s">
         <v>32</v>
       </c>
@@ -4141,7 +3355,7 @@
         <v>210</v>
       </c>
       <c r="D26" s="5">
-        <v>544.651544189468</v>
+        <v>544.65154418946804</v>
       </c>
       <c r="E26" s="5">
         <v>373.127503677552</v>
@@ -4158,7 +3372,7 @@
         <v>199661.444423223</v>
       </c>
     </row>
-    <row r="27" s="1" customFormat="1" spans="1:8">
+    <row r="27" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A27" s="4" t="s">
         <v>33</v>
       </c>
@@ -4169,24 +3383,24 @@
         <v>210</v>
       </c>
       <c r="D27" s="5">
-        <v>439.255122368171</v>
+        <v>439.25512236817099</v>
       </c>
       <c r="E27" s="5">
-        <v>278.910468874929</v>
+        <v>278.91046887492899</v>
       </c>
       <c r="F27" s="5">
-        <v>130.553885332191</v>
+        <v>130.55388533219099</v>
       </c>
       <c r="G27" s="5">
         <f t="shared" si="0"/>
-        <v>1.57489650402884</v>
+        <v>1.5748965040288401</v>
       </c>
       <c r="H27" s="5">
         <f t="shared" si="1"/>
         <v>180159.226484471</v>
       </c>
     </row>
-    <row r="28" s="1" customFormat="1" spans="1:8">
+    <row r="28" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A28" s="4" t="s">
         <v>34</v>
       </c>
@@ -4197,24 +3411,24 @@
         <v>210</v>
       </c>
       <c r="D28" s="5">
-        <v>445.219827101248</v>
+        <v>445.21982710124797</v>
       </c>
       <c r="E28" s="5">
-        <v>496.387604923717</v>
+        <v>496.38760492371699</v>
       </c>
       <c r="F28" s="5">
-        <v>158.010625755895</v>
+        <v>158.01062575589501</v>
       </c>
       <c r="G28" s="5">
         <f t="shared" si="0"/>
-        <v>0.89691971089743</v>
+        <v>0.89691971089742994</v>
       </c>
       <c r="H28" s="5">
         <f t="shared" si="1"/>
-        <v>221009.357650237</v>
-      </c>
-    </row>
-    <row r="29" s="1" customFormat="1" spans="1:8">
+        <v>221009.35765023701</v>
+      </c>
+    </row>
+    <row r="29" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A29" s="4" t="s">
         <v>35</v>
       </c>
@@ -4225,10 +3439,10 @@
         <v>210</v>
       </c>
       <c r="D29" s="5">
-        <v>592.53601385844</v>
+        <v>592.53601385844001</v>
       </c>
       <c r="E29" s="5">
-        <v>486.336993877231</v>
+        <v>486.33699387723101</v>
       </c>
       <c r="F29" s="5">
         <v>161.737148481052</v>
@@ -4242,7 +3456,7 @@
         <v>301074.799789468</v>
       </c>
     </row>
-    <row r="30" s="1" customFormat="1" spans="1:8">
+    <row r="30" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A30" s="4" t="s">
         <v>36</v>
       </c>
@@ -4253,24 +3467,24 @@
         <v>210</v>
       </c>
       <c r="D30" s="5">
-        <v>537.643856914516</v>
+        <v>537.64385691451605</v>
       </c>
       <c r="E30" s="5">
-        <v>499.902603694056</v>
+        <v>499.90260369405598</v>
       </c>
       <c r="F30" s="5">
-        <v>169.209307269713</v>
+        <v>169.20930726971301</v>
       </c>
       <c r="G30" s="5">
         <f t="shared" si="0"/>
-        <v>1.07549721274018</v>
+        <v>1.0754972127401801</v>
       </c>
       <c r="H30" s="5">
         <f t="shared" si="1"/>
-        <v>285804.332617535</v>
-      </c>
-    </row>
-    <row r="31" s="1" customFormat="1" spans="1:8">
+        <v>285804.33261753502</v>
+      </c>
+    </row>
+    <row r="31" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A31" s="4" t="s">
         <v>37</v>
       </c>
@@ -4281,7 +3495,7 @@
         <v>210</v>
       </c>
       <c r="D31" s="5">
-        <v>532.44240252014</v>
+        <v>532.44240252014004</v>
       </c>
       <c r="E31" s="5">
         <v>435.896183918612</v>
@@ -4291,14 +3505,14 @@
       </c>
       <c r="G31" s="5">
         <f t="shared" si="0"/>
-        <v>1.22148902000838</v>
+        <v>1.2214890200083801</v>
       </c>
       <c r="H31" s="5">
         <f t="shared" si="1"/>
-        <v>285321.235585449</v>
-      </c>
-    </row>
-    <row r="32" s="1" customFormat="1" spans="1:8">
+        <v>285321.23558544897</v>
+      </c>
+    </row>
+    <row r="32" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A32" s="4" t="s">
         <v>38</v>
       </c>
@@ -4315,7 +3529,7 @@
         <v>338.45534068486</v>
       </c>
       <c r="F32" s="5">
-        <v>147.229021739701</v>
+        <v>147.22902173970101</v>
       </c>
       <c r="G32" s="5">
         <f t="shared" si="0"/>
@@ -4326,7 +3540,7 @@
         <v>195687.456457188</v>
       </c>
     </row>
-    <row r="33" s="1" customFormat="1" spans="1:8">
+    <row r="33" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A33" s="4" t="s">
         <v>39</v>
       </c>
@@ -4337,24 +3551,24 @@
         <v>300</v>
       </c>
       <c r="D33" s="5">
-        <v>516.937206712899</v>
+        <v>516.93720671289896</v>
       </c>
       <c r="E33" s="5">
-        <v>560.390815894591</v>
+        <v>560.39081589459101</v>
       </c>
       <c r="F33" s="5">
         <v>210.802363467406</v>
       </c>
       <c r="G33" s="5">
         <f t="shared" si="0"/>
-        <v>0.922458384489539</v>
+        <v>0.92245838448953899</v>
       </c>
       <c r="H33" s="5">
         <f t="shared" si="1"/>
-        <v>342344.330695398</v>
-      </c>
-    </row>
-    <row r="34" s="1" customFormat="1" spans="1:8">
+        <v>342344.33069539798</v>
+      </c>
+    </row>
+    <row r="34" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A34" s="4" t="s">
         <v>40</v>
       </c>
@@ -4365,24 +3579,24 @@
         <v>300</v>
       </c>
       <c r="D34" s="5">
-        <v>502.55792570609</v>
+        <v>502.55792570608997</v>
       </c>
       <c r="E34" s="5">
-        <v>473.919999613857</v>
+        <v>473.91999961385699</v>
       </c>
       <c r="F34" s="5">
-        <v>155.95362163504</v>
+        <v>155.95362163504001</v>
       </c>
       <c r="G34" s="5">
         <f t="shared" si="0"/>
-        <v>1.06042776442346</v>
+        <v>1.0604277644234601</v>
       </c>
       <c r="H34" s="5">
         <f t="shared" si="1"/>
-        <v>246224.61317461</v>
-      </c>
-    </row>
-    <row r="35" s="1" customFormat="1" spans="1:8">
+        <v>246224.61317461001</v>
+      </c>
+    </row>
+    <row r="35" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A35" s="4" t="s">
         <v>41</v>
       </c>
@@ -4393,24 +3607,24 @@
         <v>300</v>
       </c>
       <c r="D35" s="5">
-        <v>372.915938362999</v>
+        <v>372.91593836299899</v>
       </c>
       <c r="E35" s="5">
-        <v>350.248205919633</v>
+        <v>350.24820591963299</v>
       </c>
       <c r="F35" s="5">
-        <v>169.166287392125</v>
+        <v>169.16628739212501</v>
       </c>
       <c r="G35" s="5">
         <f t="shared" si="0"/>
-        <v>1.06471905368894</v>
+        <v>1.0647190536889399</v>
       </c>
       <c r="H35" s="5">
         <f t="shared" si="1"/>
         <v>198186.759319798</v>
       </c>
     </row>
-    <row r="36" s="1" customFormat="1" spans="1:8">
+    <row r="36" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A36" s="4" t="s">
         <v>42</v>
       </c>
@@ -4421,24 +3635,24 @@
         <v>300</v>
       </c>
       <c r="D36" s="5">
-        <v>314.425861023463</v>
+        <v>314.42586102346303</v>
       </c>
       <c r="E36" s="5">
-        <v>384.442766444175</v>
+        <v>384.44276644417499</v>
       </c>
       <c r="F36" s="5">
         <v>157.446054490291</v>
       </c>
       <c r="G36" s="5">
         <f t="shared" si="0"/>
-        <v>0.817874306575413</v>
+        <v>0.81787430657541305</v>
       </c>
       <c r="H36" s="5">
         <f t="shared" si="1"/>
-        <v>155524.893811412</v>
-      </c>
-    </row>
-    <row r="37" s="1" customFormat="1" spans="1:8">
+        <v>155524.89381141201</v>
+      </c>
+    </row>
+    <row r="37" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A37" s="4" t="s">
         <v>43</v>
       </c>
@@ -4449,24 +3663,24 @@
         <v>300</v>
       </c>
       <c r="D37" s="5">
-        <v>383.839308803464</v>
+        <v>383.83930880346401</v>
       </c>
       <c r="E37" s="5">
-        <v>429.824632655471</v>
+        <v>429.82463265547102</v>
       </c>
       <c r="F37" s="5">
-        <v>143.786618512202</v>
+        <v>143.78661851220201</v>
       </c>
       <c r="G37" s="5">
         <f t="shared" si="0"/>
-        <v>0.893013754079406</v>
+        <v>0.89301375407940597</v>
       </c>
       <c r="H37" s="5">
         <f t="shared" si="1"/>
         <v>173387.50274644</v>
       </c>
     </row>
-    <row r="38" s="1" customFormat="1" spans="1:8">
+    <row r="38" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A38" s="4" t="s">
         <v>44</v>
       </c>
@@ -4477,24 +3691,24 @@
         <v>30</v>
       </c>
       <c r="D38" s="5">
-        <v>271.679190903335</v>
+        <v>271.67919090333498</v>
       </c>
       <c r="E38" s="5">
-        <v>449.724074271845</v>
+        <v>449.72407427184498</v>
       </c>
       <c r="F38" s="5">
-        <v>138.437316219924</v>
+        <v>138.43731621992401</v>
       </c>
       <c r="G38" s="5">
         <f t="shared" si="0"/>
-        <v>0.604101951498182</v>
+        <v>0.60410195149818202</v>
       </c>
       <c r="H38" s="5">
         <f t="shared" si="1"/>
         <v>118156.990071436</v>
       </c>
     </row>
-    <row r="39" s="1" customFormat="1" spans="1:8">
+    <row r="39" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A39" s="4" t="s">
         <v>46</v>
       </c>
@@ -4505,24 +3719,24 @@
         <v>30</v>
       </c>
       <c r="D39" s="5">
-        <v>353.652284857776</v>
+        <v>353.65228485777601</v>
       </c>
       <c r="E39" s="5">
-        <v>377.788533180038</v>
+        <v>377.78853318003797</v>
       </c>
       <c r="F39" s="5">
-        <v>160.331358712315</v>
+        <v>160.33135871231499</v>
       </c>
       <c r="G39" s="5">
         <f t="shared" si="0"/>
-        <v>0.936111749821799</v>
+        <v>0.93611174982179901</v>
       </c>
       <c r="H39" s="5">
         <f t="shared" si="1"/>
-        <v>178133.177146194</v>
-      </c>
-    </row>
-    <row r="40" s="1" customFormat="1" spans="1:8">
+        <v>178133.17714619401</v>
+      </c>
+    </row>
+    <row r="40" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A40" s="4" t="s">
         <v>47</v>
       </c>
@@ -4533,24 +3747,24 @@
         <v>30</v>
       </c>
       <c r="D40" s="5">
-        <v>432.102927098801</v>
+        <v>432.10292709880099</v>
       </c>
       <c r="E40" s="5">
-        <v>432.927827127356</v>
+        <v>432.92782712735601</v>
       </c>
       <c r="F40" s="5">
         <v>184.099075813821</v>
       </c>
       <c r="G40" s="5">
         <f t="shared" si="0"/>
-        <v>0.99809460150892</v>
+        <v>0.99809460150892004</v>
       </c>
       <c r="H40" s="5">
         <f t="shared" si="1"/>
         <v>249912.90873512</v>
       </c>
     </row>
-    <row r="41" s="1" customFormat="1" spans="1:8">
+    <row r="41" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A41" s="4" t="s">
         <v>48</v>
       </c>
@@ -4561,24 +3775,24 @@
         <v>30</v>
       </c>
       <c r="D41" s="5">
-        <v>298.400914055092</v>
+        <v>298.40091405509202</v>
       </c>
       <c r="E41" s="5">
-        <v>399.593993678031</v>
+        <v>399.59399367803098</v>
       </c>
       <c r="F41" s="5">
-        <v>154.806120975389</v>
+        <v>154.80612097538901</v>
       </c>
       <c r="G41" s="5">
         <f t="shared" si="0"/>
-        <v>0.7467602586027</v>
+        <v>0.74676025860270001</v>
       </c>
       <c r="H41" s="5">
         <f t="shared" si="1"/>
-        <v>145123.635819803</v>
-      </c>
-    </row>
-    <row r="42" s="1" customFormat="1" spans="1:8">
+        <v>145123.63581980299</v>
+      </c>
+    </row>
+    <row r="42" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A42" s="4" t="s">
         <v>49</v>
       </c>
@@ -4589,13 +3803,13 @@
         <v>30</v>
       </c>
       <c r="D42" s="5">
-        <v>229.431947925861</v>
+        <v>229.43194792586101</v>
       </c>
       <c r="E42" s="5">
-        <v>471.571649823478</v>
+        <v>471.57164982347803</v>
       </c>
       <c r="F42" s="5">
-        <v>145.560669450574</v>
+        <v>145.56066945057401</v>
       </c>
       <c r="G42" s="5">
         <f t="shared" si="0"/>
@@ -4603,10 +3817,10 @@
       </c>
       <c r="H42" s="5">
         <f t="shared" si="1"/>
-        <v>104917.469997004</v>
-      </c>
-    </row>
-    <row r="43" s="1" customFormat="1" spans="1:8">
+        <v>104917.46999700399</v>
+      </c>
+    </row>
+    <row r="43" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A43" s="4" t="s">
         <v>50</v>
       </c>
@@ -4617,24 +3831,24 @@
         <v>30</v>
       </c>
       <c r="D43" s="5">
-        <v>263.302629533354</v>
+        <v>263.30262953335398</v>
       </c>
       <c r="E43" s="5">
-        <v>379.852568321328</v>
+        <v>379.85256832132802</v>
       </c>
       <c r="F43" s="5">
         <v>147.8290747886</v>
       </c>
       <c r="G43" s="5">
         <f t="shared" si="0"/>
-        <v>0.693170591677082</v>
+        <v>0.69317059167708195</v>
       </c>
       <c r="H43" s="5">
         <f t="shared" si="1"/>
         <v>122282.674220325</v>
       </c>
     </row>
-    <row r="44" s="1" customFormat="1" spans="1:8">
+    <row r="44" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A44" s="4" t="s">
         <v>51</v>
       </c>
@@ -4645,24 +3859,24 @@
         <v>60</v>
       </c>
       <c r="D44" s="5">
-        <v>503.405901518948</v>
+        <v>503.40590151894799</v>
       </c>
       <c r="E44" s="5">
-        <v>653.74887835891</v>
+        <v>653.74887835891002</v>
       </c>
       <c r="F44" s="5">
-        <v>204.943562871907</v>
+        <v>204.94356287190701</v>
       </c>
       <c r="G44" s="5">
         <f t="shared" si="0"/>
-        <v>0.770029468781095</v>
+        <v>0.77002946878109502</v>
       </c>
       <c r="H44" s="5">
         <f t="shared" si="1"/>
-        <v>324117.482698818</v>
-      </c>
-    </row>
-    <row r="45" s="1" customFormat="1" spans="1:8">
+        <v>324117.48269881803</v>
+      </c>
+    </row>
+    <row r="45" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A45" s="4" t="s">
         <v>52</v>
       </c>
@@ -4673,24 +3887,24 @@
         <v>60</v>
       </c>
       <c r="D45" s="5">
-        <v>333.885307296264</v>
+        <v>333.88530729626399</v>
       </c>
       <c r="E45" s="5">
-        <v>575.559751309209</v>
+        <v>575.55975130920899</v>
       </c>
       <c r="F45" s="5">
         <v>190.720729508679</v>
       </c>
       <c r="G45" s="5">
         <f t="shared" si="0"/>
-        <v>0.580105378350006</v>
+        <v>0.58010537835000597</v>
       </c>
       <c r="H45" s="5">
         <f t="shared" si="1"/>
-        <v>200053.005400546</v>
-      </c>
-    </row>
-    <row r="46" s="1" customFormat="1" spans="1:8">
+        <v>200053.00540054601</v>
+      </c>
+    </row>
+    <row r="46" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A46" s="4" t="s">
         <v>53</v>
       </c>
@@ -4701,24 +3915,24 @@
         <v>60</v>
       </c>
       <c r="D46" s="5">
-        <v>415.678397922782</v>
+        <v>415.67839792278198</v>
       </c>
       <c r="E46" s="5">
-        <v>482.920566380673</v>
+        <v>482.92056638067299</v>
       </c>
       <c r="F46" s="5">
-        <v>182.200843948973</v>
+        <v>182.20084394897299</v>
       </c>
       <c r="G46" s="5">
         <f t="shared" si="0"/>
-        <v>0.860759360567622</v>
+        <v>0.86075936056762203</v>
       </c>
       <c r="H46" s="5">
         <f t="shared" si="1"/>
         <v>237934.66115959</v>
       </c>
     </row>
-    <row r="47" s="1" customFormat="1" spans="1:8">
+    <row r="47" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A47" s="4" t="s">
         <v>54</v>
       </c>
@@ -4729,24 +3943,24 @@
         <v>60</v>
       </c>
       <c r="D47" s="5">
-        <v>342.180980222361</v>
+        <v>342.18098022236097</v>
       </c>
       <c r="E47" s="5">
-        <v>541.473721562794</v>
+        <v>541.47372156279403</v>
       </c>
       <c r="F47" s="5">
-        <v>198.255157751331</v>
+        <v>198.25515775133101</v>
       </c>
       <c r="G47" s="5">
         <f t="shared" si="0"/>
-        <v>0.631943835122345</v>
+        <v>0.63194383512234498</v>
       </c>
       <c r="H47" s="5">
         <f t="shared" si="1"/>
-        <v>213122.957086916</v>
-      </c>
-    </row>
-    <row r="48" s="1" customFormat="1" spans="1:8">
+        <v>213122.95708691599</v>
+      </c>
+    </row>
+    <row r="48" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A48" s="4" t="s">
         <v>55</v>
       </c>
@@ -4757,13 +3971,13 @@
         <v>60</v>
       </c>
       <c r="D48" s="5">
-        <v>419.872560444723</v>
+        <v>419.87256044472298</v>
       </c>
       <c r="E48" s="5">
-        <v>501.884743877232</v>
+        <v>501.88474387723198</v>
       </c>
       <c r="F48" s="5">
-        <v>232.865658690886</v>
+        <v>232.86565869088599</v>
       </c>
       <c r="G48" s="5">
         <f t="shared" si="0"/>
@@ -4774,7 +3988,7 @@
         <v>307165.767065541</v>
       </c>
     </row>
-    <row r="49" s="1" customFormat="1" spans="1:8">
+    <row r="49" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A49" s="4" t="s">
         <v>56</v>
       </c>
@@ -4788,21 +4002,21 @@
         <v>424.993014090445</v>
       </c>
       <c r="E49" s="5">
-        <v>506.652678564129</v>
+        <v>506.65267856412902</v>
       </c>
       <c r="F49" s="5">
         <v>182.681457652018</v>
       </c>
       <c r="G49" s="5">
         <f t="shared" si="0"/>
-        <v>0.838825159860774</v>
+        <v>0.83882515986077399</v>
       </c>
       <c r="H49" s="5">
         <f t="shared" si="1"/>
         <v>243908.048966909</v>
       </c>
     </row>
-    <row r="50" s="1" customFormat="1" spans="1:8">
+    <row r="50" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A50" s="4" t="s">
         <v>57</v>
       </c>
@@ -4813,24 +4027,24 @@
         <v>90</v>
       </c>
       <c r="D50" s="5">
-        <v>445.694640423654</v>
+        <v>445.69464042365399</v>
       </c>
       <c r="E50" s="5">
-        <v>447.34825139747</v>
+        <v>447.34825139746999</v>
       </c>
       <c r="F50" s="5">
-        <v>181.800791100324</v>
+        <v>181.80079110032401</v>
       </c>
       <c r="G50" s="5">
         <f t="shared" si="0"/>
-        <v>0.996303526461431</v>
+        <v>0.99630352646143105</v>
       </c>
       <c r="H50" s="5">
         <f t="shared" si="1"/>
-        <v>254555.832964012</v>
-      </c>
-    </row>
-    <row r="51" s="1" customFormat="1" spans="1:8">
+        <v>254555.83296401199</v>
+      </c>
+    </row>
+    <row r="51" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A51" s="4" t="s">
         <v>58</v>
       </c>
@@ -4841,24 +4055,24 @@
         <v>90</v>
       </c>
       <c r="D51" s="5">
-        <v>409.639183598117</v>
+        <v>409.63918359811697</v>
       </c>
       <c r="E51" s="5">
-        <v>611.646906413651</v>
+        <v>611.64690641365098</v>
       </c>
       <c r="F51" s="5">
         <v>207.535327611062</v>
       </c>
       <c r="G51" s="5">
         <f t="shared" si="0"/>
-        <v>0.669731473016038</v>
+        <v>0.66973147301603797</v>
       </c>
       <c r="H51" s="5">
         <f t="shared" si="1"/>
-        <v>267081.249626272</v>
-      </c>
-    </row>
-    <row r="52" s="1" customFormat="1" spans="1:8">
+        <v>267081.24962627201</v>
+      </c>
+    </row>
+    <row r="52" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A52" s="4" t="s">
         <v>59</v>
       </c>
@@ -4869,24 +4083,24 @@
         <v>90</v>
       </c>
       <c r="D52" s="5">
-        <v>336.032512773058</v>
+        <v>336.03251277305799</v>
       </c>
       <c r="E52" s="5">
-        <v>560.864909557039</v>
+        <v>560.86490955703903</v>
       </c>
       <c r="F52" s="5">
-        <v>169.296480643204</v>
+        <v>169.29648064320401</v>
       </c>
       <c r="G52" s="5">
         <f t="shared" si="0"/>
-        <v>0.599132709226631</v>
+        <v>0.59913270922663098</v>
       </c>
       <c r="H52" s="5">
         <f t="shared" si="1"/>
-        <v>178722.447097743</v>
-      </c>
-    </row>
-    <row r="53" s="1" customFormat="1" spans="1:8">
+        <v>178722.44709774299</v>
+      </c>
+    </row>
+    <row r="53" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A53" s="4" t="s">
         <v>60</v>
       </c>
@@ -4897,24 +4111,24 @@
         <v>90</v>
       </c>
       <c r="D53" s="5">
-        <v>351.784046092233</v>
+        <v>351.78404609223298</v>
       </c>
       <c r="E53" s="5">
-        <v>550.586549174757</v>
+        <v>550.58654917475701</v>
       </c>
       <c r="F53" s="5">
         <v>200.983236941748</v>
       </c>
       <c r="G53" s="5">
         <f t="shared" si="0"/>
-        <v>0.638925971982974</v>
+        <v>0.63892597198297396</v>
       </c>
       <c r="H53" s="5">
         <f t="shared" si="1"/>
-        <v>222119.071247629</v>
-      </c>
-    </row>
-    <row r="54" s="1" customFormat="1" spans="1:8">
+        <v>222119.07124762901</v>
+      </c>
+    </row>
+    <row r="54" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A54" s="4" t="s">
         <v>61</v>
       </c>
@@ -4925,24 +4139,24 @@
         <v>90</v>
       </c>
       <c r="D54" s="5">
-        <v>377.950702454153</v>
+        <v>377.95070245415297</v>
       </c>
       <c r="E54" s="5">
-        <v>473.11927688781</v>
+        <v>473.11927688780997</v>
       </c>
       <c r="F54" s="5">
-        <v>206.646304004854</v>
+        <v>206.64630400485399</v>
       </c>
       <c r="G54" s="5">
         <f t="shared" si="0"/>
-        <v>0.79884866442205</v>
+        <v>0.79884866442205005</v>
       </c>
       <c r="H54" s="5">
         <f t="shared" si="1"/>
-        <v>245365.033095746</v>
-      </c>
-    </row>
-    <row r="55" s="1" customFormat="1" spans="1:8">
+        <v>245365.03309574601</v>
+      </c>
+    </row>
+    <row r="55" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A55" s="4" t="s">
         <v>62</v>
       </c>
@@ -4956,21 +4170,21 @@
         <v>392.25062110373</v>
       </c>
       <c r="E55" s="5">
-        <v>462.797612812979</v>
+        <v>462.79761281297903</v>
       </c>
       <c r="F55" s="5">
-        <v>137.916905710271</v>
+        <v>137.91690571027101</v>
       </c>
       <c r="G55" s="5">
         <f t="shared" si="0"/>
-        <v>0.847564054446068</v>
+        <v>0.84756405444606797</v>
       </c>
       <c r="H55" s="5">
         <f t="shared" si="1"/>
-        <v>169953.854007294</v>
-      </c>
-    </row>
-    <row r="56" s="1" customFormat="1" spans="1:8">
+        <v>169953.85400729399</v>
+      </c>
+    </row>
+    <row r="56" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A56" s="4" t="s">
         <v>63</v>
       </c>
@@ -4981,7 +4195,7 @@
         <v>150</v>
       </c>
       <c r="D56" s="5">
-        <v>368.047757394822</v>
+        <v>368.04775739482199</v>
       </c>
       <c r="E56" s="5">
         <v>695.963278802589</v>
@@ -4991,14 +4205,14 @@
       </c>
       <c r="G56" s="5">
         <f t="shared" si="0"/>
-        <v>0.52883215049514</v>
+        <v>0.52883215049513999</v>
       </c>
       <c r="H56" s="5">
         <f t="shared" si="1"/>
-        <v>213331.191290336</v>
-      </c>
-    </row>
-    <row r="57" s="1" customFormat="1" spans="1:8">
+        <v>213331.19129033599</v>
+      </c>
+    </row>
+    <row r="57" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A57" s="4" t="s">
         <v>64</v>
       </c>
@@ -5009,24 +4223,24 @@
         <v>150</v>
       </c>
       <c r="D57" s="5">
-        <v>429.91270615324</v>
+        <v>429.91270615323998</v>
       </c>
       <c r="E57" s="5">
-        <v>578.698930031488</v>
+        <v>578.69893003148798</v>
       </c>
       <c r="F57" s="5">
-        <v>158.569564418788</v>
+        <v>158.56956441878799</v>
       </c>
       <c r="G57" s="5">
         <f t="shared" si="0"/>
-        <v>0.742895284305861</v>
+        <v>0.74289528430586105</v>
       </c>
       <c r="H57" s="5">
         <f t="shared" si="1"/>
-        <v>214165.734436096</v>
-      </c>
-    </row>
-    <row r="58" s="1" customFormat="1" spans="1:8">
+        <v>214165.73443609601</v>
+      </c>
+    </row>
+    <row r="58" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A58" s="4" t="s">
         <v>65</v>
       </c>
@@ -5037,24 +4251,24 @@
         <v>150</v>
       </c>
       <c r="D58" s="5">
-        <v>467.491358281848</v>
+        <v>467.49135828184802</v>
       </c>
       <c r="E58" s="5">
-        <v>548.884381465137</v>
+        <v>548.88438146513704</v>
       </c>
       <c r="F58" s="5">
         <v>182.738941335687</v>
       </c>
       <c r="G58" s="5">
         <f t="shared" si="0"/>
-        <v>0.851711897930077</v>
+        <v>0.85171189793007696</v>
       </c>
       <c r="H58" s="5">
         <f t="shared" si="1"/>
-        <v>268382.728919331</v>
-      </c>
-    </row>
-    <row r="59" s="1" customFormat="1" spans="1:8">
+        <v>268382.72891933098</v>
+      </c>
+    </row>
+    <row r="59" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A59" s="4" t="s">
         <v>66</v>
       </c>
@@ -5065,24 +4279,24 @@
         <v>150</v>
       </c>
       <c r="D59" s="5">
-        <v>450.708203055397</v>
+        <v>450.70820305539701</v>
       </c>
       <c r="E59" s="5">
-        <v>661.530417475728</v>
+        <v>661.53041747572797</v>
       </c>
       <c r="F59" s="5">
         <v>160.835729725871</v>
       </c>
       <c r="G59" s="5">
         <f t="shared" si="0"/>
-        <v>0.681311382136006</v>
+        <v>0.68131138213600595</v>
       </c>
       <c r="H59" s="5">
         <f t="shared" si="1"/>
         <v>227733.997209233</v>
       </c>
     </row>
-    <row r="60" s="1" customFormat="1" spans="1:8">
+    <row r="60" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A60" s="4" t="s">
         <v>67</v>
       </c>
@@ -5093,13 +4307,13 @@
         <v>150</v>
       </c>
       <c r="D60" s="5">
-        <v>376.28128913835</v>
+        <v>376.28128913835002</v>
       </c>
       <c r="E60" s="5">
-        <v>515.018739114078</v>
+        <v>515.01873911407802</v>
       </c>
       <c r="F60" s="5">
-        <v>162.886577160194</v>
+        <v>162.88657716019401</v>
       </c>
       <c r="G60" s="5">
         <f t="shared" si="0"/>
@@ -5110,7 +4324,7 @@
         <v>192551.893288611</v>
       </c>
     </row>
-    <row r="61" s="1" customFormat="1" spans="1:8">
+    <row r="61" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A61" s="4" t="s">
         <v>68</v>
       </c>
@@ -5121,13 +4335,13 @@
         <v>150</v>
       </c>
       <c r="D61" s="5">
-        <v>263.200076213592</v>
+        <v>263.20007621359201</v>
       </c>
       <c r="E61" s="5">
-        <v>541.476485131761</v>
+        <v>541.47648513176102</v>
       </c>
       <c r="F61" s="5">
-        <v>150.251644743412</v>
+        <v>150.25164474341199</v>
       </c>
       <c r="G61" s="5">
         <f t="shared" si="0"/>
@@ -5138,7 +4352,7 @@
         <v>124238.19071975</v>
       </c>
     </row>
-    <row r="62" s="1" customFormat="1" spans="1:8">
+    <row r="62" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A62" s="4" t="s">
         <v>69</v>
       </c>
@@ -5149,24 +4363,24 @@
         <v>210</v>
       </c>
       <c r="D62" s="5">
-        <v>324.850533623644</v>
+        <v>324.85053362364403</v>
       </c>
       <c r="E62" s="5">
-        <v>637.888745174186</v>
+        <v>637.88874517418606</v>
       </c>
       <c r="F62" s="5">
-        <v>152.063413292404</v>
+        <v>152.06341329240399</v>
       </c>
       <c r="G62" s="5">
         <f t="shared" si="0"/>
-        <v>0.50925892027604</v>
+        <v>0.50925892027604003</v>
       </c>
       <c r="H62" s="5">
         <f t="shared" si="1"/>
         <v>155188.019903812</v>
       </c>
     </row>
-    <row r="63" s="1" customFormat="1" spans="1:8">
+    <row r="63" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A63" s="4" t="s">
         <v>70</v>
       </c>
@@ -5177,24 +4391,24 @@
         <v>210</v>
       </c>
       <c r="D63" s="5">
-        <v>448.233681600758</v>
+        <v>448.23368160075802</v>
       </c>
       <c r="E63" s="5">
-        <v>548.379068387402</v>
+        <v>548.37906838740196</v>
       </c>
       <c r="F63" s="5">
-        <v>159.604300473597</v>
+        <v>159.60430047359699</v>
       </c>
       <c r="G63" s="5">
         <f t="shared" si="0"/>
-        <v>0.81737926817459</v>
+        <v>0.81737926817458995</v>
       </c>
       <c r="H63" s="5">
         <f t="shared" si="1"/>
-        <v>224749.611324629</v>
-      </c>
-    </row>
-    <row r="64" s="1" customFormat="1" spans="1:8">
+        <v>224749.61132462899</v>
+      </c>
+    </row>
+    <row r="64" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A64" s="4" t="s">
         <v>71</v>
       </c>
@@ -5205,24 +4419,24 @@
         <v>210</v>
       </c>
       <c r="D64" s="5">
-        <v>588.761379572291</v>
+        <v>588.76137957229105</v>
       </c>
       <c r="E64" s="5">
-        <v>542.987671123065</v>
+        <v>542.98767112306496</v>
       </c>
       <c r="F64" s="5">
-        <v>180.277681999475</v>
+        <v>180.27768199947499</v>
       </c>
       <c r="G64" s="5">
         <f t="shared" si="0"/>
-        <v>1.08429971965027</v>
+        <v>1.0842997196502699</v>
       </c>
       <c r="H64" s="5">
         <f t="shared" si="1"/>
-        <v>333450.330533625</v>
-      </c>
-    </row>
-    <row r="65" s="1" customFormat="1" spans="1:8">
+        <v>333450.33053362498</v>
+      </c>
+    </row>
+    <row r="65" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A65" s="4" t="s">
         <v>72</v>
       </c>
@@ -5233,24 +4447,24 @@
         <v>210</v>
       </c>
       <c r="D65" s="5">
-        <v>293.239002727693</v>
+        <v>293.23900272769299</v>
       </c>
       <c r="E65" s="5">
-        <v>633.557135413777</v>
+        <v>633.55713541377702</v>
       </c>
       <c r="F65" s="5">
         <v>193.591605929265</v>
       </c>
       <c r="G65" s="5">
         <f t="shared" si="0"/>
-        <v>0.462845395208402</v>
+        <v>0.46284539520840201</v>
       </c>
       <c r="H65" s="5">
         <f t="shared" si="1"/>
         <v>178343.846431374</v>
       </c>
     </row>
-    <row r="66" s="1" customFormat="1" spans="1:8">
+    <row r="66" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A66" s="4" t="s">
         <v>73</v>
       </c>
@@ -5261,24 +4475,24 @@
         <v>210</v>
       </c>
       <c r="D66" s="5">
-        <v>376.039657394822</v>
+        <v>376.03965739482197</v>
       </c>
       <c r="E66" s="5">
-        <v>671.419205420712</v>
+        <v>671.41920542071205</v>
       </c>
       <c r="F66" s="5">
-        <v>158.124949644013</v>
+        <v>158.12494964401299</v>
       </c>
       <c r="G66" s="5">
         <f t="shared" ref="G66:G72" si="2">D66/E66</f>
-        <v>0.560066876787052</v>
+        <v>0.56006687678705203</v>
       </c>
       <c r="H66" s="5">
         <f t="shared" ref="H66:H72" si="3">D66*F66*PI()</f>
-        <v>186803.032109959</v>
-      </c>
-    </row>
-    <row r="67" s="1" customFormat="1" spans="1:8">
+        <v>186803.03210995899</v>
+      </c>
+    </row>
+    <row r="67" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A67" s="4" t="s">
         <v>74</v>
       </c>
@@ -5292,21 +4506,21 @@
         <v>415.673297478096</v>
       </c>
       <c r="E67" s="5">
-        <v>544.893753717736</v>
+        <v>544.89375371773599</v>
       </c>
       <c r="F67" s="5">
-        <v>195.933008441866</v>
+        <v>195.93300844186601</v>
       </c>
       <c r="G67" s="5">
         <f t="shared" si="2"/>
-        <v>0.762852014070658</v>
+        <v>0.76285201407065795</v>
       </c>
       <c r="H67" s="5">
         <f t="shared" si="3"/>
-        <v>255864.248139653</v>
-      </c>
-    </row>
-    <row r="68" s="1" customFormat="1" spans="1:8">
+        <v>255864.24813965301</v>
+      </c>
+    </row>
+    <row r="68" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A68" s="4" t="s">
         <v>75</v>
       </c>
@@ -5317,10 +4531,10 @@
         <v>300</v>
       </c>
       <c r="D68" s="5">
-        <v>276.256081757793</v>
+        <v>276.25608175779303</v>
       </c>
       <c r="E68" s="5">
-        <v>477.163666670925</v>
+        <v>477.16366667092501</v>
       </c>
       <c r="F68" s="5">
         <v>141.486436982626</v>
@@ -5331,10 +4545,10 @@
       </c>
       <c r="H68" s="5">
         <f t="shared" si="3"/>
-        <v>122793.825762995</v>
-      </c>
-    </row>
-    <row r="69" s="1" customFormat="1" spans="1:8">
+        <v>122793.82576299499</v>
+      </c>
+    </row>
+    <row r="69" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A69" s="4" t="s">
         <v>76</v>
       </c>
@@ -5345,24 +4559,24 @@
         <v>300</v>
       </c>
       <c r="D69" s="5">
-        <v>341.863913121506</v>
+        <v>341.86391312150602</v>
       </c>
       <c r="E69" s="5">
-        <v>506.449489673433</v>
+        <v>506.44948967343299</v>
       </c>
       <c r="F69" s="5">
-        <v>183.506570609003</v>
+        <v>183.50657060900301</v>
       </c>
       <c r="G69" s="5">
         <f t="shared" si="2"/>
-        <v>0.67502074756151</v>
+        <v>0.67502074756150998</v>
       </c>
       <c r="H69" s="5">
         <f t="shared" si="3"/>
-        <v>197085.535306557</v>
-      </c>
-    </row>
-    <row r="70" s="1" customFormat="1" spans="1:8">
+        <v>197085.53530655699</v>
+      </c>
+    </row>
+    <row r="70" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A70" s="4" t="s">
         <v>77</v>
       </c>
@@ -5376,21 +4590,21 @@
         <v>350.330803575657</v>
       </c>
       <c r="E70" s="5">
-        <v>539.800048247691</v>
+        <v>539.80004824769105</v>
       </c>
       <c r="F70" s="5">
         <v>177.334184063462</v>
       </c>
       <c r="G70" s="5">
         <f t="shared" si="2"/>
-        <v>0.649001060138671</v>
+        <v>0.64900106013867098</v>
       </c>
       <c r="H70" s="5">
         <f t="shared" si="3"/>
-        <v>195173.414024958</v>
-      </c>
-    </row>
-    <row r="71" s="1" customFormat="1" spans="1:8">
+        <v>195173.41402495801</v>
+      </c>
+    </row>
+    <row r="71" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A71" s="4" t="s">
         <v>78</v>
       </c>
@@ -5404,21 +4618,21 @@
         <v>417.069810409924</v>
       </c>
       <c r="E71" s="5">
-        <v>530.954005798274</v>
+        <v>530.95400579827401</v>
       </c>
       <c r="F71" s="5">
-        <v>136.173548880798</v>
+        <v>136.17354888079799</v>
       </c>
       <c r="G71" s="5">
         <f t="shared" si="2"/>
-        <v>0.785510243552776</v>
+        <v>0.78551024355277599</v>
       </c>
       <c r="H71" s="5">
         <f t="shared" si="3"/>
         <v>178423.224284553</v>
       </c>
     </row>
-    <row r="72" s="1" customFormat="1" spans="1:8">
+    <row r="72" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A72" s="4" t="s">
         <v>80</v>
       </c>
@@ -5429,7 +4643,7 @@
         <v>300</v>
       </c>
       <c r="D72" s="5">
-        <v>367.898998470874</v>
+        <v>367.89899847087401</v>
       </c>
       <c r="E72" s="5">
         <v>588.736522645631</v>
@@ -5446,61 +4660,41 @@
         <v>148809.24533131</v>
       </c>
     </row>
-    <row r="73" s="1" customFormat="1" spans="1:8">
-      <c r="A73" s="2"/>
-      <c r="B73" s="2"/>
-      <c r="C73" s="2"/>
-      <c r="D73" s="2"/>
+    <row r="73" spans="1:8" x14ac:dyDescent="0.25">
       <c r="E73" s="6"/>
-      <c r="F73" s="2"/>
       <c r="G73" s="6"/>
-      <c r="H73" s="2"/>
-    </row>
-    <row r="74" s="1" customFormat="1" spans="1:8">
-      <c r="A74" s="2"/>
-      <c r="B74" s="2"/>
-      <c r="C74" s="2"/>
-      <c r="D74" s="2"/>
+    </row>
+    <row r="74" spans="1:8" x14ac:dyDescent="0.25">
       <c r="E74" s="6"/>
-      <c r="F74" s="2"/>
       <c r="G74" s="6"/>
-      <c r="H74" s="2"/>
-    </row>
-    <row r="75" s="1" customFormat="1" spans="1:8">
-      <c r="A75" s="2"/>
-      <c r="B75" s="2"/>
-      <c r="C75" s="2"/>
-      <c r="D75" s="2"/>
+    </row>
+    <row r="75" spans="1:8" x14ac:dyDescent="0.25">
       <c r="E75" s="6"/>
-      <c r="F75" s="2"/>
       <c r="G75" s="6"/>
-      <c r="H75" s="2"/>
     </row>
   </sheetData>
+  <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
-  <dimension ref="A1:H71"/>
-  <sheetFormatPr defaultColWidth="8.75454545454545" defaultRowHeight="14" outlineLevelCol="7"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
+  <dimension ref="A1:H76"/>
+  <sheetFormatPr defaultColWidth="8.7265625" defaultRowHeight="14" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="8.75454545454545" style="2"/>
-    <col min="2" max="2" width="14.8181818181818" style="2" customWidth="1"/>
-    <col min="3" max="3" width="6.5" style="2" customWidth="1"/>
-    <col min="4" max="4" width="13.8727272727273" style="2" customWidth="1"/>
-    <col min="5" max="5" width="14.8727272727273" style="2" customWidth="1"/>
-    <col min="6" max="6" width="15.3727272727273" style="2" customWidth="1"/>
-    <col min="7" max="7" width="18.3727272727273" style="2" customWidth="1"/>
-    <col min="8" max="8" width="21.0909090909091" style="2" customWidth="1"/>
-    <col min="9" max="16382" width="8.75454545454545" style="2"/>
-    <col min="16383" max="16384" width="8.75454545454545" style="7"/>
+    <col min="1" max="1" width="8.7265625" style="2"/>
+    <col min="2" max="2" width="10.6328125" style="2" customWidth="1"/>
+    <col min="3" max="3" width="8.7265625" style="2"/>
+    <col min="4" max="4" width="18.26953125" style="3" customWidth="1"/>
+    <col min="5" max="5" width="15.08984375" style="3" customWidth="1"/>
+    <col min="6" max="6" width="15.90625" style="3" customWidth="1"/>
+    <col min="7" max="7" width="18.26953125" style="3" customWidth="1"/>
+    <col min="8" max="8" width="20.453125" style="3" customWidth="1"/>
+    <col min="9" max="16384" width="8.7265625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" s="2" customFormat="1" ht="16" spans="1:8">
+    <row r="1" spans="1:8" ht="16" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
@@ -5526,7 +4720,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="2" s="2" customFormat="1" spans="1:8">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" s="4" t="s">
         <v>7</v>
       </c>
@@ -5537,24 +4731,22 @@
         <v>30</v>
       </c>
       <c r="D2" s="5">
-        <v>359.488651535566</v>
+        <v>359.48865153556602</v>
       </c>
       <c r="E2" s="5">
-        <v>263.199659183674</v>
+        <v>263.19965918367399</v>
       </c>
       <c r="F2" s="5">
         <v>142.517600168417</v>
       </c>
       <c r="G2" s="5">
-        <f t="shared" ref="G2:G31" si="0">D2/E2</f>
-        <v>1.36584011031981</v>
+        <v>1.3658401103198099</v>
       </c>
       <c r="H2" s="5">
-        <f t="shared" ref="H2:H31" si="1">D2*F2*PI()</f>
         <v>160954.66125437</v>
       </c>
     </row>
-    <row r="3" s="2" customFormat="1" spans="1:8">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3" s="4" t="s">
         <v>9</v>
       </c>
@@ -5565,7 +4757,7 @@
         <v>30</v>
       </c>
       <c r="D3" s="5">
-        <v>206.447675025549</v>
+        <v>206.44767502554899</v>
       </c>
       <c r="E3" s="5">
         <v>262.284112736331</v>
@@ -5574,15 +4766,13 @@
         <v>118.654193408278</v>
       </c>
       <c r="G3" s="5">
-        <f t="shared" si="0"/>
-        <v>0.78711467832246</v>
+        <v>0.78711467832245996</v>
       </c>
       <c r="H3" s="5">
-        <f t="shared" si="1"/>
-        <v>76956.084069054</v>
-      </c>
-    </row>
-    <row r="4" s="2" customFormat="1" spans="1:8">
+        <v>76956.084069054006</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4" s="4" t="s">
         <v>10</v>
       </c>
@@ -5593,24 +4783,22 @@
         <v>30</v>
       </c>
       <c r="D4" s="5">
-        <v>183.93701566422</v>
+        <v>183.93701566422001</v>
       </c>
       <c r="E4" s="5">
         <v>288.436836881364</v>
       </c>
       <c r="F4" s="5">
-        <v>125.332455730523</v>
+        <v>125.33245573052299</v>
       </c>
       <c r="G4" s="5">
-        <f t="shared" si="0"/>
-        <v>0.637702928838713</v>
+        <v>0.63770292883871305</v>
       </c>
       <c r="H4" s="5">
-        <f t="shared" si="1"/>
-        <v>72424.0084067936</v>
-      </c>
-    </row>
-    <row r="5" s="2" customFormat="1" spans="1:8">
+        <v>72424.008406793597</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
         <v>11</v>
       </c>
@@ -5624,21 +4812,19 @@
         <v>221.433964620897</v>
       </c>
       <c r="E5" s="5">
-        <v>255.578618238558</v>
+        <v>255.57861823855799</v>
       </c>
       <c r="F5" s="5">
         <v>119.772789447527</v>
       </c>
       <c r="G5" s="5">
-        <f t="shared" si="0"/>
-        <v>0.866402542384081</v>
+        <v>0.86640254238408099</v>
       </c>
       <c r="H5" s="5">
-        <f t="shared" si="1"/>
-        <v>83320.577752198</v>
-      </c>
-    </row>
-    <row r="6" s="2" customFormat="1" spans="1:8">
+        <v>83320.577752198005</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
         <v>12</v>
       </c>
@@ -5658,15 +4844,13 @@
         <v>100.055819007888</v>
       </c>
       <c r="G6" s="5">
-        <f t="shared" si="0"/>
-        <v>0.73691654816741</v>
+        <v>0.73691654816741003</v>
       </c>
       <c r="H6" s="5">
-        <f t="shared" si="1"/>
-        <v>59556.2896075231</v>
-      </c>
-    </row>
-    <row r="7" s="2" customFormat="1" spans="1:8">
+        <v>59556.289607523096</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A7" s="4" t="s">
         <v>13</v>
       </c>
@@ -5677,24 +4861,22 @@
         <v>30</v>
       </c>
       <c r="D7" s="5">
-        <v>242.001061888445</v>
+        <v>242.00106188844501</v>
       </c>
       <c r="E7" s="5">
-        <v>234.546935750999</v>
+        <v>234.54693575099901</v>
       </c>
       <c r="F7" s="5">
         <v>120.396777993528</v>
       </c>
       <c r="G7" s="5">
-        <f t="shared" si="0"/>
         <v>1.0317809572467</v>
       </c>
       <c r="H7" s="5">
-        <f t="shared" si="1"/>
-        <v>91533.9088951766</v>
-      </c>
-    </row>
-    <row r="8" s="2" customFormat="1" spans="1:8">
+        <v>91533.908895176603</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A8" s="4" t="s">
         <v>14</v>
       </c>
@@ -5708,21 +4890,19 @@
         <v>303.576122164607</v>
       </c>
       <c r="E8" s="5">
-        <v>367.382981112092</v>
+        <v>367.38298111209201</v>
       </c>
       <c r="F8" s="5">
-        <v>170.078894042365</v>
+        <v>170.07889404236499</v>
       </c>
       <c r="G8" s="5">
-        <f t="shared" si="0"/>
-        <v>0.826320591241495</v>
+        <v>0.82632059124149504</v>
       </c>
       <c r="H8" s="5">
-        <f t="shared" si="1"/>
         <v>162206.369819171</v>
       </c>
     </row>
-    <row r="9" s="2" customFormat="1" spans="1:8">
+    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A9" s="4" t="s">
         <v>15</v>
       </c>
@@ -5733,24 +4913,22 @@
         <v>60</v>
       </c>
       <c r="D9" s="5">
-        <v>349.023618446602</v>
+        <v>349.02361844660197</v>
       </c>
       <c r="E9" s="5">
         <v>376.423938861191</v>
       </c>
       <c r="F9" s="5">
-        <v>171.140662240882</v>
+        <v>171.14066224088199</v>
       </c>
       <c r="G9" s="5">
-        <f t="shared" si="0"/>
-        <v>0.927208879176271</v>
+        <v>0.92720887917627104</v>
       </c>
       <c r="H9" s="5">
-        <f t="shared" si="1"/>
         <v>187654.030840158</v>
       </c>
     </row>
-    <row r="10" s="2" customFormat="1" spans="1:8">
+    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A10" s="4" t="s">
         <v>16</v>
       </c>
@@ -5761,24 +4939,22 @@
         <v>60</v>
       </c>
       <c r="D10" s="5">
-        <v>329.756537125369</v>
+        <v>329.75653712536899</v>
       </c>
       <c r="E10" s="5">
         <v>347.923149071338</v>
       </c>
       <c r="F10" s="5">
-        <v>171.703490628957</v>
+        <v>171.70349062895701</v>
       </c>
       <c r="G10" s="5">
-        <f t="shared" si="0"/>
-        <v>0.947785561281396</v>
+        <v>0.94778556128139602</v>
       </c>
       <c r="H10" s="5">
-        <f t="shared" si="1"/>
-        <v>177878.070835195</v>
-      </c>
-    </row>
-    <row r="11" s="2" customFormat="1" spans="1:8">
+        <v>177878.07083519499</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A11" s="4" t="s">
         <v>17</v>
       </c>
@@ -5789,24 +4965,22 @@
         <v>60</v>
       </c>
       <c r="D11" s="5">
-        <v>384.800889894086</v>
+        <v>384.80088989408603</v>
       </c>
       <c r="E11" s="5">
-        <v>383.547518902618</v>
+        <v>383.54751890261798</v>
       </c>
       <c r="F11" s="5">
-        <v>178.793536054722</v>
+        <v>178.79353605472201</v>
       </c>
       <c r="G11" s="5">
-        <f t="shared" si="0"/>
         <v>1.00326783756822</v>
       </c>
       <c r="H11" s="5">
-        <f t="shared" si="1"/>
-        <v>216141.297419341</v>
-      </c>
-    </row>
-    <row r="12" s="2" customFormat="1" spans="1:8">
+        <v>216141.29741934099</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A12" s="4" t="s">
         <v>18</v>
       </c>
@@ -5817,24 +4991,22 @@
         <v>60</v>
       </c>
       <c r="D12" s="5">
-        <v>276.728216514968</v>
+        <v>276.72821651496798</v>
       </c>
       <c r="E12" s="5">
         <v>302.30824888754</v>
       </c>
       <c r="F12" s="5">
-        <v>166.079120125405</v>
+        <v>166.07912012540501</v>
       </c>
       <c r="G12" s="5">
-        <f t="shared" si="0"/>
-        <v>0.91538427262007</v>
+        <v>0.91538427262007005</v>
       </c>
       <c r="H12" s="5">
-        <f t="shared" si="1"/>
         <v>144383.76157171</v>
       </c>
     </row>
-    <row r="13" s="2" customFormat="1" spans="1:8">
+    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A13" s="4" t="s">
         <v>19</v>
       </c>
@@ -5848,21 +5020,19 @@
         <v>395.906696522917</v>
       </c>
       <c r="E13" s="5">
-        <v>362.854954414089</v>
+        <v>362.85495441408898</v>
       </c>
       <c r="F13" s="5">
-        <v>167.281618378867</v>
+        <v>167.28161837886699</v>
       </c>
       <c r="G13" s="5">
-        <f t="shared" si="0"/>
-        <v>1.09108802761753</v>
+        <v>1.0910880276175301</v>
       </c>
       <c r="H13" s="5">
-        <f t="shared" si="1"/>
-        <v>208061.124696406</v>
-      </c>
-    </row>
-    <row r="14" s="2" customFormat="1" spans="1:8">
+        <v>208061.12469640601</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A14" s="4" t="s">
         <v>20</v>
       </c>
@@ -5873,24 +5043,22 @@
         <v>90</v>
       </c>
       <c r="D14" s="5">
-        <v>430.101449317764</v>
+        <v>430.10144931776398</v>
       </c>
       <c r="E14" s="5">
-        <v>430.25512658095</v>
+        <v>430.25512658094999</v>
       </c>
       <c r="F14" s="5">
-        <v>141.601082432432</v>
+        <v>141.60108243243201</v>
       </c>
       <c r="G14" s="5">
-        <f t="shared" si="0"/>
-        <v>0.999642822935296</v>
+        <v>0.99964282293529605</v>
       </c>
       <c r="H14" s="5">
-        <f t="shared" si="1"/>
-        <v>191331.88575861</v>
-      </c>
-    </row>
-    <row r="15" s="2" customFormat="1" spans="1:8">
+        <v>191331.88575861001</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A15" s="4" t="s">
         <v>21</v>
       </c>
@@ -5901,24 +5069,22 @@
         <v>90</v>
       </c>
       <c r="D15" s="5">
-        <v>322.434630369406</v>
+        <v>322.43463036940602</v>
       </c>
       <c r="E15" s="5">
-        <v>311.821491913332</v>
+        <v>311.82149191333201</v>
       </c>
       <c r="F15" s="5">
-        <v>130.423431695477</v>
+        <v>130.42343169547701</v>
       </c>
       <c r="G15" s="5">
-        <f t="shared" si="0"/>
-        <v>1.03403594277916</v>
+        <v>1.0340359427791601</v>
       </c>
       <c r="H15" s="5">
-        <f t="shared" si="1"/>
-        <v>132113.493220124</v>
-      </c>
-    </row>
-    <row r="16" s="2" customFormat="1" spans="1:8">
+        <v>132113.49322012399</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A16" s="4" t="s">
         <v>22</v>
       </c>
@@ -5929,24 +5095,22 @@
         <v>90</v>
       </c>
       <c r="D16" s="5">
-        <v>368.54478285801</v>
+        <v>368.54478285801002</v>
       </c>
       <c r="E16" s="5">
-        <v>323.782974868528</v>
+        <v>323.78297486852802</v>
       </c>
       <c r="F16" s="5">
-        <v>141.247585275081</v>
+        <v>141.24758527508101</v>
       </c>
       <c r="G16" s="5">
-        <f t="shared" si="0"/>
         <v>1.13824632999205</v>
       </c>
       <c r="H16" s="5">
-        <f t="shared" si="1"/>
-        <v>163538.937695344</v>
-      </c>
-    </row>
-    <row r="17" s="2" customFormat="1" spans="1:8">
+        <v>163538.93769534401</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A17" s="4" t="s">
         <v>23</v>
       </c>
@@ -5957,24 +5121,22 @@
         <v>90</v>
       </c>
       <c r="D17" s="5">
-        <v>267.952992747002</v>
+        <v>267.95299274700199</v>
       </c>
       <c r="E17" s="5">
         <v>336.094999328955</v>
       </c>
       <c r="F17" s="5">
-        <v>125.28350391205</v>
+        <v>125.28350391204999</v>
       </c>
       <c r="G17" s="5">
-        <f t="shared" si="0"/>
-        <v>0.797253732670808</v>
+        <v>0.79725373267080801</v>
       </c>
       <c r="H17" s="5">
-        <f t="shared" si="1"/>
-        <v>105463.547543356</v>
-      </c>
-    </row>
-    <row r="18" s="2" customFormat="1" spans="1:8">
+        <v>105463.54754335601</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A18" s="4" t="s">
         <v>24</v>
       </c>
@@ -5985,24 +5147,22 @@
         <v>90</v>
       </c>
       <c r="D18" s="5">
-        <v>440.44737223301</v>
+        <v>440.44737223301001</v>
       </c>
       <c r="E18" s="5">
-        <v>328.844577135922</v>
+        <v>328.84457713592201</v>
       </c>
       <c r="F18" s="5">
-        <v>157.168009854369</v>
+        <v>157.16800985436899</v>
       </c>
       <c r="G18" s="5">
-        <f t="shared" si="0"/>
-        <v>1.33937854797271</v>
+        <v>1.3393785479727101</v>
       </c>
       <c r="H18" s="5">
-        <f t="shared" si="1"/>
         <v>217474.354219331</v>
       </c>
     </row>
-    <row r="19" s="2" customFormat="1" spans="1:8">
+    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A19" s="4" t="s">
         <v>25</v>
       </c>
@@ -6013,24 +5173,22 @@
         <v>90</v>
       </c>
       <c r="D19" s="5">
-        <v>475.150489261189</v>
+        <v>475.15048926118902</v>
       </c>
       <c r="E19" s="5">
-        <v>325.754292564528</v>
+        <v>325.75429256452799</v>
       </c>
       <c r="F19" s="5">
-        <v>157.630912798958</v>
+        <v>157.63091279895801</v>
       </c>
       <c r="G19" s="5">
-        <f t="shared" si="0"/>
-        <v>1.4586162027844</v>
+        <v>1.4586162027844001</v>
       </c>
       <c r="H19" s="5">
-        <f t="shared" si="1"/>
-        <v>235300.279978947</v>
-      </c>
-    </row>
-    <row r="20" s="2" customFormat="1" spans="1:8">
+        <v>235300.27997894699</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A20" s="4" t="s">
         <v>26</v>
       </c>
@@ -6044,21 +5202,19 @@
         <v>478.757223831565</v>
       </c>
       <c r="E20" s="5">
-        <v>397.277138078573</v>
+        <v>397.27713807857299</v>
       </c>
       <c r="F20" s="5">
-        <v>195.829240336419</v>
+        <v>195.82924033641899</v>
       </c>
       <c r="G20" s="5">
-        <f t="shared" si="0"/>
-        <v>1.20509633689739</v>
+        <v>1.2050963368973899</v>
       </c>
       <c r="H20" s="5">
-        <f t="shared" si="1"/>
-        <v>294538.961929617</v>
-      </c>
-    </row>
-    <row r="21" s="2" customFormat="1" spans="1:8">
+        <v>294538.96192961698</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A21" s="4" t="s">
         <v>27</v>
       </c>
@@ -6072,21 +5228,19 @@
         <v>530.770322097492</v>
       </c>
       <c r="E21" s="5">
-        <v>378.546886245955</v>
+        <v>378.54688624595502</v>
       </c>
       <c r="F21" s="5">
-        <v>182.019643133091</v>
+        <v>182.01964313309099</v>
       </c>
       <c r="G21" s="5">
-        <f t="shared" si="0"/>
-        <v>1.40212571119296</v>
+        <v>1.4021257111929599</v>
       </c>
       <c r="H21" s="5">
-        <f t="shared" si="1"/>
         <v>303511.228545502</v>
       </c>
     </row>
-    <row r="22" s="2" customFormat="1" spans="1:8">
+    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A22" s="4" t="s">
         <v>28</v>
       </c>
@@ -6097,24 +5251,22 @@
         <v>150</v>
       </c>
       <c r="D22" s="5">
-        <v>431.532087098166</v>
+        <v>431.53208709816602</v>
       </c>
       <c r="E22" s="5">
         <v>348.393583009709</v>
       </c>
       <c r="F22" s="5">
-        <v>173.401841024811</v>
+        <v>173.40184102481101</v>
       </c>
       <c r="G22" s="5">
-        <f t="shared" si="0"/>
-        <v>1.23863385591158</v>
+        <v>1.2386338559115799</v>
       </c>
       <c r="H22" s="5">
-        <f t="shared" si="1"/>
-        <v>235080.53507611</v>
-      </c>
-    </row>
-    <row r="23" s="2" customFormat="1" spans="1:8">
+        <v>235080.53507611001</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A23" s="4" t="s">
         <v>29</v>
       </c>
@@ -6125,24 +5277,22 @@
         <v>150</v>
       </c>
       <c r="D23" s="5">
-        <v>466.630175793755</v>
+        <v>466.63017579375497</v>
       </c>
       <c r="E23" s="5">
-        <v>316.397702164786</v>
+        <v>316.39770216478598</v>
       </c>
       <c r="F23" s="5">
         <v>169.601209223301</v>
       </c>
       <c r="G23" s="5">
-        <f t="shared" si="0"/>
         <v>1.47482163303046</v>
       </c>
       <c r="H23" s="5">
-        <f t="shared" si="1"/>
-        <v>248628.916379326</v>
-      </c>
-    </row>
-    <row r="24" s="2" customFormat="1" spans="1:8">
+        <v>248628.91637932599</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A24" s="4" t="s">
         <v>30</v>
       </c>
@@ -6153,24 +5303,22 @@
         <v>150</v>
       </c>
       <c r="D24" s="5">
-        <v>463.017328256943</v>
+        <v>463.01732825694302</v>
       </c>
       <c r="E24" s="5">
-        <v>380.352966121021</v>
+        <v>380.35296612102098</v>
       </c>
       <c r="F24" s="5">
-        <v>167.030184612779</v>
+        <v>167.03018461277901</v>
       </c>
       <c r="G24" s="5">
-        <f t="shared" si="0"/>
-        <v>1.21733592083943</v>
+        <v>1.2173359208394301</v>
       </c>
       <c r="H24" s="5">
-        <f t="shared" si="1"/>
-        <v>242964.083663485</v>
-      </c>
-    </row>
-    <row r="25" s="2" customFormat="1" spans="1:8">
+        <v>242964.08366348501</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A25" s="4" t="s">
         <v>31</v>
       </c>
@@ -6184,21 +5332,19 @@
         <v>416.602795527046</v>
       </c>
       <c r="E25" s="5">
-        <v>430.839710679612</v>
+        <v>430.83971067961198</v>
       </c>
       <c r="F25" s="5">
         <v>158.358924953768</v>
       </c>
       <c r="G25" s="5">
-        <f t="shared" si="0"/>
-        <v>0.966955424953497</v>
+        <v>0.96695542495349696</v>
       </c>
       <c r="H25" s="5">
-        <f t="shared" si="1"/>
-        <v>207259.572184023</v>
-      </c>
-    </row>
-    <row r="26" s="2" customFormat="1" spans="1:8">
+        <v>207259.57218402301</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A26" s="4" t="s">
         <v>32</v>
       </c>
@@ -6209,24 +5355,22 @@
         <v>210</v>
       </c>
       <c r="D26" s="5">
-        <v>504.687621402056</v>
+        <v>504.68762140205598</v>
       </c>
       <c r="E26" s="5">
-        <v>375.470236165049</v>
+        <v>375.47023616504902</v>
       </c>
       <c r="F26" s="5">
-        <v>204.595512649914</v>
+        <v>204.59551264991401</v>
       </c>
       <c r="G26" s="5">
-        <f t="shared" si="0"/>
-        <v>1.34414814488839</v>
+        <v>1.3441481448883901</v>
       </c>
       <c r="H26" s="5">
-        <f t="shared" si="1"/>
-        <v>324390.875403723</v>
-      </c>
-    </row>
-    <row r="27" s="2" customFormat="1" spans="1:8">
+        <v>324390.87540372298</v>
+      </c>
+    </row>
+    <row r="27" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A27" s="4" t="s">
         <v>33</v>
       </c>
@@ -6237,24 +5381,22 @@
         <v>210</v>
       </c>
       <c r="D27" s="5">
-        <v>439.615048404993</v>
+        <v>439.61504840499299</v>
       </c>
       <c r="E27" s="5">
-        <v>377.576148682386</v>
+        <v>377.57614868238602</v>
       </c>
       <c r="F27" s="5">
-        <v>192.416481289875</v>
+        <v>192.41648128987501</v>
       </c>
       <c r="G27" s="5">
-        <f t="shared" si="0"/>
         <v>1.16430831221491</v>
       </c>
       <c r="H27" s="5">
-        <f t="shared" si="1"/>
-        <v>265744.748773921</v>
-      </c>
-    </row>
-    <row r="28" s="2" customFormat="1" spans="1:8">
+        <v>265744.74877392099</v>
+      </c>
+    </row>
+    <row r="28" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A28" s="4" t="s">
         <v>34</v>
       </c>
@@ -6265,24 +5407,22 @@
         <v>210</v>
       </c>
       <c r="D28" s="5">
-        <v>574.867542436216</v>
+        <v>574.86754243621601</v>
       </c>
       <c r="E28" s="5">
-        <v>379.945521607586</v>
+        <v>379.94552160758599</v>
       </c>
       <c r="F28" s="5">
         <v>158.830405384963</v>
       </c>
       <c r="G28" s="5">
-        <f t="shared" si="0"/>
         <v>1.51302623598219</v>
       </c>
       <c r="H28" s="5">
-        <f t="shared" si="1"/>
-        <v>286847.656233591</v>
-      </c>
-    </row>
-    <row r="29" s="2" customFormat="1" spans="1:8">
+        <v>286847.65623359103</v>
+      </c>
+    </row>
+    <row r="29" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A29" s="4" t="s">
         <v>35</v>
       </c>
@@ -6293,24 +5433,22 @@
         <v>210</v>
       </c>
       <c r="D29" s="5">
-        <v>533.706902823199</v>
+        <v>533.70690282319902</v>
       </c>
       <c r="E29" s="5">
-        <v>405.53619741952</v>
+        <v>405.53619741952002</v>
       </c>
       <c r="F29" s="5">
-        <v>180.309085743485</v>
+        <v>180.30908574348501</v>
       </c>
       <c r="G29" s="5">
-        <f t="shared" si="0"/>
-        <v>1.31605244172837</v>
+        <v>1.3160524417283701</v>
       </c>
       <c r="H29" s="5">
-        <f t="shared" si="1"/>
-        <v>302322.384192221</v>
-      </c>
-    </row>
-    <row r="30" s="2" customFormat="1" spans="1:8">
+        <v>302322.38419222098</v>
+      </c>
+    </row>
+    <row r="30" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A30" s="4" t="s">
         <v>36</v>
       </c>
@@ -6321,24 +5459,22 @@
         <v>210</v>
       </c>
       <c r="D30" s="5">
-        <v>527.488990746359</v>
+        <v>527.48899074635904</v>
       </c>
       <c r="E30" s="5">
-        <v>388.175051380461</v>
+        <v>388.17505138046101</v>
       </c>
       <c r="F30" s="5">
-        <v>195.97596565534</v>
+        <v>195.97596565533999</v>
       </c>
       <c r="G30" s="5">
-        <f t="shared" si="0"/>
-        <v>1.3588946246557</v>
+        <v>1.3588946246557001</v>
       </c>
       <c r="H30" s="5">
-        <f t="shared" si="1"/>
-        <v>324762.656835578</v>
-      </c>
-    </row>
-    <row r="31" s="2" customFormat="1" spans="1:8">
+        <v>324762.65683557797</v>
+      </c>
+    </row>
+    <row r="31" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A31" s="4" t="s">
         <v>37</v>
       </c>
@@ -6349,24 +5485,22 @@
         <v>210</v>
       </c>
       <c r="D31" s="5">
-        <v>438.713639667129</v>
+        <v>438.71363966712897</v>
       </c>
       <c r="E31" s="5">
-        <v>318.926038735883</v>
+        <v>318.92603873588303</v>
       </c>
       <c r="F31" s="5">
-        <v>175.635574806816</v>
+        <v>175.63557480681601</v>
       </c>
       <c r="G31" s="5">
-        <f t="shared" si="0"/>
-        <v>1.37559680421845</v>
+        <v>1.3755968042184501</v>
       </c>
       <c r="H31" s="5">
-        <f t="shared" si="1"/>
-        <v>242071.407841967</v>
-      </c>
-    </row>
-    <row r="32" s="2" customFormat="1" spans="1:8">
+        <v>242071.40784196701</v>
+      </c>
+    </row>
+    <row r="32" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A32" s="4" t="s">
         <v>38</v>
       </c>
@@ -6377,22 +5511,22 @@
         <v>300</v>
       </c>
       <c r="D32" s="5">
-        <v>223.361621653293</v>
+        <v>223.36162165329301</v>
       </c>
       <c r="E32" s="5">
         <v>105.543805755939</v>
       </c>
       <c r="F32" s="5">
-        <v>63.9011176507508</v>
+        <v>63.901117650750798</v>
       </c>
       <c r="G32" s="5">
-        <v>2.37663644519923</v>
+        <v>2.3766364451992299</v>
       </c>
       <c r="H32" s="5">
-        <v>44502.5590652989</v>
-      </c>
-    </row>
-    <row r="33" s="2" customFormat="1" spans="1:8">
+        <v>44502.559065298898</v>
+      </c>
+    </row>
+    <row r="33" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A33" s="4" t="s">
         <v>39</v>
       </c>
@@ -6403,24 +5537,22 @@
         <v>300</v>
       </c>
       <c r="D33" s="5">
-        <v>457.339719981796</v>
+        <v>457.33971998179601</v>
       </c>
       <c r="E33" s="5">
-        <v>386.120115203001</v>
+        <v>386.12011520300098</v>
       </c>
       <c r="F33" s="5">
         <v>148.329968965137</v>
       </c>
       <c r="G33" s="5">
-        <f t="shared" ref="G33:G71" si="2">D33/E33</f>
         <v>1.18444935131481</v>
       </c>
       <c r="H33" s="5">
-        <f t="shared" ref="H33:H71" si="3">D33*F33*PI()</f>
         <v>213116.806658827</v>
       </c>
     </row>
-    <row r="34" s="2" customFormat="1" spans="1:8">
+    <row r="34" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A34" s="4" t="s">
         <v>40</v>
       </c>
@@ -6434,21 +5566,19 @@
         <v>449.735482965578</v>
       </c>
       <c r="E34" s="5">
-        <v>310.011936098853</v>
+        <v>310.01193609885303</v>
       </c>
       <c r="F34" s="5">
-        <v>136.839223712857</v>
+        <v>136.83922371285701</v>
       </c>
       <c r="G34" s="5">
-        <f t="shared" si="2"/>
         <v>1.45070376523235</v>
       </c>
       <c r="H34" s="5">
-        <f t="shared" si="3"/>
         <v>193338.180924744</v>
       </c>
     </row>
-    <row r="35" s="2" customFormat="1" spans="1:8">
+    <row r="35" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A35" s="4" t="s">
         <v>42</v>
       </c>
@@ -6459,24 +5589,22 @@
         <v>300</v>
       </c>
       <c r="D35" s="5">
-        <v>351.433853070916</v>
+        <v>351.43385307091597</v>
       </c>
       <c r="E35" s="5">
-        <v>325.472663349515</v>
+        <v>325.47266334951502</v>
       </c>
       <c r="F35" s="5">
-        <v>150.612590154073</v>
+        <v>150.61259015407299</v>
       </c>
       <c r="G35" s="5">
-        <f t="shared" si="2"/>
-        <v>1.07976457824208</v>
+        <v>1.0797645782420799</v>
       </c>
       <c r="H35" s="5">
-        <f t="shared" si="3"/>
-        <v>166285.639171995</v>
-      </c>
-    </row>
-    <row r="36" s="2" customFormat="1" spans="1:8">
+        <v>166285.63917199499</v>
+      </c>
+    </row>
+    <row r="36" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A36" s="4" t="s">
         <v>43</v>
       </c>
@@ -6487,24 +5615,22 @@
         <v>300</v>
       </c>
       <c r="D36" s="5">
-        <v>402.53495185853</v>
+        <v>402.53495185853001</v>
       </c>
       <c r="E36" s="5">
-        <v>335.116516269071</v>
+        <v>335.11651626907098</v>
       </c>
       <c r="F36" s="5">
         <v>165.919408710125</v>
       </c>
       <c r="G36" s="5">
-        <f t="shared" si="2"/>
         <v>1.20117908941058</v>
       </c>
       <c r="H36" s="5">
-        <f t="shared" si="3"/>
-        <v>209821.824883449</v>
-      </c>
-    </row>
-    <row r="37" s="2" customFormat="1" spans="1:8">
+        <v>209821.82488344901</v>
+      </c>
+    </row>
+    <row r="37" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A37" s="4" t="s">
         <v>44</v>
       </c>
@@ -6515,7 +5641,7 @@
         <v>30</v>
       </c>
       <c r="D37" s="5">
-        <v>278.960375217824</v>
+        <v>278.96037521782398</v>
       </c>
       <c r="E37" s="5">
         <v>338.345652999751</v>
@@ -6524,15 +5650,13 @@
         <v>125.503708289768</v>
       </c>
       <c r="G37" s="5">
-        <f t="shared" si="2"/>
-        <v>0.824483402534004</v>
+        <v>0.82448340253400398</v>
       </c>
       <c r="H37" s="5">
-        <f t="shared" si="3"/>
         <v>109988.922981572</v>
       </c>
     </row>
-    <row r="38" s="2" customFormat="1" spans="1:8">
+    <row r="38" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A38" s="4" t="s">
         <v>47</v>
       </c>
@@ -6543,24 +5667,22 @@
         <v>30</v>
       </c>
       <c r="D38" s="5">
-        <v>269.086153794333</v>
+        <v>269.08615379433297</v>
       </c>
       <c r="E38" s="5">
-        <v>312.030561927878</v>
+        <v>312.03056192787801</v>
       </c>
       <c r="F38" s="5">
-        <v>134.154594699822</v>
+        <v>134.15459469982201</v>
       </c>
       <c r="G38" s="5">
-        <f t="shared" si="2"/>
-        <v>0.862371147658699</v>
+        <v>0.86237114765869904</v>
       </c>
       <c r="H38" s="5">
-        <f t="shared" si="3"/>
-        <v>113408.805282187</v>
-      </c>
-    </row>
-    <row r="39" s="2" customFormat="1" spans="1:8">
+        <v>113408.80528218699</v>
+      </c>
+    </row>
+    <row r="39" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A39" s="4" t="s">
         <v>48</v>
       </c>
@@ -6571,24 +5693,22 @@
         <v>30</v>
       </c>
       <c r="D39" s="5">
-        <v>281.757803863681</v>
+        <v>281.75780386368098</v>
       </c>
       <c r="E39" s="5">
-        <v>328.637344907866</v>
+        <v>328.63734490786601</v>
       </c>
       <c r="F39" s="5">
-        <v>139.587087923519</v>
+        <v>139.58708792351899</v>
       </c>
       <c r="G39" s="5">
-        <f t="shared" si="2"/>
-        <v>0.857351753321499</v>
+        <v>0.85735175332149904</v>
       </c>
       <c r="H39" s="5">
-        <f t="shared" si="3"/>
         <v>123558.057880579</v>
       </c>
     </row>
-    <row r="40" s="2" customFormat="1" spans="1:8">
+    <row r="40" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A40" s="4" t="s">
         <v>49</v>
       </c>
@@ -6599,7 +5719,7 @@
         <v>30</v>
       </c>
       <c r="D40" s="5">
-        <v>242.090697862211</v>
+        <v>242.09069786221099</v>
       </c>
       <c r="E40" s="5">
         <v>337.372430153099</v>
@@ -6608,15 +5728,13 @@
         <v>126.688668054518</v>
       </c>
       <c r="G40" s="5">
-        <f t="shared" si="2"/>
-        <v>0.717577004595042</v>
+        <v>0.71757700459504203</v>
       </c>
       <c r="H40" s="5">
-        <f t="shared" si="3"/>
-        <v>96353.1118315422</v>
-      </c>
-    </row>
-    <row r="41" s="2" customFormat="1" spans="1:8">
+        <v>96353.111831542206</v>
+      </c>
+    </row>
+    <row r="41" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A41" s="4" t="s">
         <v>50</v>
       </c>
@@ -6627,24 +5745,22 @@
         <v>30</v>
       </c>
       <c r="D41" s="5">
-        <v>233.129376227077</v>
+        <v>233.12937622707699</v>
       </c>
       <c r="E41" s="5">
-        <v>315.360724555016</v>
+        <v>315.36072455501602</v>
       </c>
       <c r="F41" s="5">
-        <v>126.766947788565</v>
+        <v>126.76694778856501</v>
       </c>
       <c r="G41" s="5">
-        <f t="shared" si="2"/>
-        <v>0.7392467040911</v>
+        <v>0.73924670409110005</v>
       </c>
       <c r="H41" s="5">
-        <f t="shared" si="3"/>
-        <v>92843.8001674091</v>
-      </c>
-    </row>
-    <row r="42" s="2" customFormat="1" spans="1:8">
+        <v>92843.800167409107</v>
+      </c>
+    </row>
+    <row r="42" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A42" s="4" t="s">
         <v>51</v>
       </c>
@@ -6658,21 +5774,19 @@
         <v>289.759952405609</v>
       </c>
       <c r="E42" s="5">
-        <v>343.840576299892</v>
+        <v>343.84057629989201</v>
       </c>
       <c r="F42" s="5">
-        <v>156.338151877023</v>
+        <v>156.33815187702299</v>
       </c>
       <c r="G42" s="5">
-        <f t="shared" si="2"/>
-        <v>0.842715992172155</v>
+        <v>0.84271599217215498</v>
       </c>
       <c r="H42" s="5">
-        <f t="shared" si="3"/>
-        <v>142315.82936419</v>
-      </c>
-    </row>
-    <row r="43" s="2" customFormat="1" spans="1:8">
+        <v>142315.82936418999</v>
+      </c>
+    </row>
+    <row r="43" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A43" s="4" t="s">
         <v>52</v>
       </c>
@@ -6683,24 +5797,22 @@
         <v>60</v>
       </c>
       <c r="D43" s="5">
-        <v>359.327111402373</v>
+        <v>359.32711140237302</v>
       </c>
       <c r="E43" s="5">
-        <v>299.971832308522</v>
+        <v>299.97183230852198</v>
       </c>
       <c r="F43" s="5">
-        <v>160.02391399137</v>
+        <v>160.02391399136999</v>
       </c>
       <c r="G43" s="5">
-        <f t="shared" si="2"/>
-        <v>1.19786950873709</v>
+        <v>1.1978695087370901</v>
       </c>
       <c r="H43" s="5">
-        <f t="shared" si="3"/>
         <v>180644.501681044</v>
       </c>
     </row>
-    <row r="44" s="2" customFormat="1" spans="1:8">
+    <row r="44" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A44" s="4" t="s">
         <v>53</v>
       </c>
@@ -6711,24 +5823,22 @@
         <v>60</v>
       </c>
       <c r="D44" s="5">
-        <v>356.321232732316</v>
+        <v>356.32123273231599</v>
       </c>
       <c r="E44" s="5">
-        <v>372.696636419325</v>
+        <v>372.69663641932499</v>
       </c>
       <c r="F44" s="5">
-        <v>165.060994093851</v>
+        <v>165.06099409385101</v>
       </c>
       <c r="G44" s="5">
-        <f t="shared" si="2"/>
-        <v>0.956062378656445</v>
+        <v>0.95606237865644506</v>
       </c>
       <c r="H44" s="5">
-        <f t="shared" si="3"/>
-        <v>184771.945341287</v>
-      </c>
-    </row>
-    <row r="45" s="2" customFormat="1" spans="1:8">
+        <v>184771.94534128701</v>
+      </c>
+    </row>
+    <row r="45" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A45" s="4" t="s">
         <v>54</v>
       </c>
@@ -6739,24 +5849,22 @@
         <v>60</v>
       </c>
       <c r="D45" s="5">
-        <v>318.690720264408</v>
+        <v>318.69072026440801</v>
       </c>
       <c r="E45" s="5">
-        <v>293.493081491427</v>
+        <v>293.49308149142701</v>
       </c>
       <c r="F45" s="5">
-        <v>162.193244463954</v>
+        <v>162.19324446395399</v>
       </c>
       <c r="G45" s="5">
-        <f t="shared" si="2"/>
-        <v>1.08585428537169</v>
+        <v>1.0858542853716899</v>
       </c>
       <c r="H45" s="5">
-        <f t="shared" si="3"/>
-        <v>162387.296605652</v>
-      </c>
-    </row>
-    <row r="46" s="2" customFormat="1" spans="1:8">
+        <v>162387.29660565199</v>
+      </c>
+    </row>
+    <row r="46" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A46" s="4" t="s">
         <v>55</v>
       </c>
@@ -6767,24 +5875,22 @@
         <v>60</v>
       </c>
       <c r="D46" s="5">
-        <v>382.684482288113</v>
+        <v>382.68448228811297</v>
       </c>
       <c r="E46" s="5">
-        <v>324.319886053529</v>
+        <v>324.31988605352899</v>
       </c>
       <c r="F46" s="5">
-        <v>164.054643007085</v>
+        <v>164.05464300708499</v>
       </c>
       <c r="G46" s="5">
-        <f t="shared" si="2"/>
-        <v>1.1799599677491</v>
+        <v>1.1799599677490999</v>
       </c>
       <c r="H46" s="5">
-        <f t="shared" si="3"/>
-        <v>197232.850285643</v>
-      </c>
-    </row>
-    <row r="47" s="2" customFormat="1" spans="1:8">
+        <v>197232.85028564301</v>
+      </c>
+    </row>
+    <row r="47" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A47" s="4" t="s">
         <v>56</v>
       </c>
@@ -6795,24 +5901,22 @@
         <v>60</v>
       </c>
       <c r="D47" s="5">
-        <v>316.117057535304</v>
+        <v>316.11705753530401</v>
       </c>
       <c r="E47" s="5">
-        <v>332.21266021624</v>
+        <v>332.21266021624001</v>
       </c>
       <c r="F47" s="5">
-        <v>156.280247054281</v>
+        <v>156.28024705428101</v>
       </c>
       <c r="G47" s="5">
-        <f t="shared" si="2"/>
-        <v>0.951550303138781</v>
+        <v>0.95155030313878097</v>
       </c>
       <c r="H47" s="5">
-        <f t="shared" si="3"/>
-        <v>155203.63643737</v>
-      </c>
-    </row>
-    <row r="48" s="2" customFormat="1" spans="1:8">
+        <v>155203.63643737001</v>
+      </c>
+    </row>
+    <row r="48" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A48" s="4" t="s">
         <v>57</v>
       </c>
@@ -6823,24 +5927,22 @@
         <v>90</v>
       </c>
       <c r="D48" s="5">
-        <v>251.67062753843</v>
+        <v>251.67062753843001</v>
       </c>
       <c r="E48" s="5">
-        <v>310.104119781553</v>
+        <v>310.10411978155298</v>
       </c>
       <c r="F48" s="5">
-        <v>194.088819043285</v>
+        <v>194.08881904328501</v>
       </c>
       <c r="G48" s="5">
-        <f t="shared" si="2"/>
-        <v>0.811568152386091</v>
+        <v>0.81156815238609104</v>
       </c>
       <c r="H48" s="5">
-        <f t="shared" si="3"/>
-        <v>153455.663826327</v>
-      </c>
-    </row>
-    <row r="49" s="2" customFormat="1" spans="1:8">
+        <v>153455.66382632701</v>
+      </c>
+    </row>
+    <row r="49" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A49" s="4" t="s">
         <v>58</v>
       </c>
@@ -6851,24 +5953,22 @@
         <v>90</v>
       </c>
       <c r="D49" s="5">
-        <v>306.301261476226</v>
+        <v>306.30126147622599</v>
       </c>
       <c r="E49" s="5">
-        <v>404.953550037341</v>
+        <v>404.95355003734102</v>
       </c>
       <c r="F49" s="5">
-        <v>170.435544834454</v>
+        <v>170.43554483445399</v>
       </c>
       <c r="G49" s="5">
-        <f t="shared" si="2"/>
-        <v>0.756386161938775</v>
+        <v>0.75638616193877495</v>
       </c>
       <c r="H49" s="5">
-        <f t="shared" si="3"/>
-        <v>164005.658162431</v>
-      </c>
-    </row>
-    <row r="50" s="2" customFormat="1" spans="1:8">
+        <v>164005.65816243101</v>
+      </c>
+    </row>
+    <row r="50" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A50" s="4" t="s">
         <v>59</v>
       </c>
@@ -6879,24 +5979,22 @@
         <v>90</v>
       </c>
       <c r="D50" s="5">
-        <v>290.513687864078</v>
+        <v>290.51368786407801</v>
       </c>
       <c r="E50" s="5">
-        <v>337.771452049622</v>
+        <v>337.77145204962198</v>
       </c>
       <c r="F50" s="5">
         <v>170.647722599784</v>
       </c>
       <c r="G50" s="5">
-        <f t="shared" si="2"/>
-        <v>0.860089525332054</v>
+        <v>0.86008952533205396</v>
       </c>
       <c r="H50" s="5">
-        <f t="shared" si="3"/>
-        <v>155746.024141533</v>
-      </c>
-    </row>
-    <row r="51" s="2" customFormat="1" spans="1:8">
+        <v>155746.02414153301</v>
+      </c>
+    </row>
+    <row r="51" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A51" s="4" t="s">
         <v>60</v>
       </c>
@@ -6907,7 +6005,7 @@
         <v>90</v>
       </c>
       <c r="D51" s="5">
-        <v>348.280448609885</v>
+        <v>348.28044860988501</v>
       </c>
       <c r="E51" s="5">
         <v>316.772288184025</v>
@@ -6916,15 +6014,13 @@
         <v>160.331420531774</v>
       </c>
       <c r="G51" s="5">
-        <f t="shared" si="2"/>
         <v>1.09946627783159</v>
       </c>
       <c r="H51" s="5">
-        <f t="shared" si="3"/>
-        <v>175427.473329636</v>
-      </c>
-    </row>
-    <row r="52" s="2" customFormat="1" spans="1:8">
+        <v>175427.47332963601</v>
+      </c>
+    </row>
+    <row r="52" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A52" s="4" t="s">
         <v>61</v>
       </c>
@@ -6935,24 +6031,22 @@
         <v>90</v>
       </c>
       <c r="D52" s="5">
-        <v>308.117681577078</v>
+        <v>308.11768157707797</v>
       </c>
       <c r="E52" s="5">
-        <v>356.307832725551</v>
+        <v>356.30783272555101</v>
       </c>
       <c r="F52" s="5">
-        <v>141.368907719631</v>
+        <v>141.36890771963101</v>
       </c>
       <c r="G52" s="5">
-        <f t="shared" si="2"/>
-        <v>0.86475135620835</v>
+        <v>0.86475135620834997</v>
       </c>
       <c r="H52" s="5">
-        <f t="shared" si="3"/>
-        <v>136842.309913385</v>
-      </c>
-    </row>
-    <row r="53" s="2" customFormat="1" spans="1:8">
+        <v>136842.30991338499</v>
+      </c>
+    </row>
+    <row r="53" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A53" s="4" t="s">
         <v>62</v>
       </c>
@@ -6963,24 +6057,22 @@
         <v>90</v>
       </c>
       <c r="D53" s="5">
-        <v>326.365730550865</v>
+        <v>326.36573055086501</v>
       </c>
       <c r="E53" s="5">
-        <v>354.559548712537</v>
+        <v>354.55954871253698</v>
       </c>
       <c r="F53" s="5">
         <v>167.521373079358</v>
       </c>
       <c r="G53" s="5">
-        <f t="shared" si="2"/>
-        <v>0.920482135471888</v>
+        <v>0.92048213547188795</v>
       </c>
       <c r="H53" s="5">
-        <f t="shared" si="3"/>
         <v>171761.034391375</v>
       </c>
     </row>
-    <row r="54" s="2" customFormat="1" spans="1:8">
+    <row r="54" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A54" s="4" t="s">
         <v>63</v>
       </c>
@@ -6991,24 +6083,22 @@
         <v>150</v>
       </c>
       <c r="D54" s="5">
-        <v>339.89856252229</v>
+        <v>339.89856252228998</v>
       </c>
       <c r="E54" s="5">
         <v>404.377081553398</v>
       </c>
       <c r="F54" s="5">
-        <v>168.973096403804</v>
+        <v>168.97309640380399</v>
       </c>
       <c r="G54" s="5">
-        <f t="shared" si="2"/>
-        <v>0.840548532613628</v>
+        <v>0.84054853261362805</v>
       </c>
       <c r="H54" s="5">
-        <f t="shared" si="3"/>
-        <v>180433.329486447</v>
-      </c>
-    </row>
-    <row r="55" s="2" customFormat="1" spans="1:8">
+        <v>180433.32948644701</v>
+      </c>
+    </row>
+    <row r="55" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A55" s="4" t="s">
         <v>64</v>
       </c>
@@ -7019,24 +6109,22 @@
         <v>150</v>
       </c>
       <c r="D55" s="5">
-        <v>501.030341110437</v>
+        <v>501.03034111043701</v>
       </c>
       <c r="E55" s="5">
         <v>419.223260447006</v>
       </c>
       <c r="F55" s="5">
-        <v>184.032612095469</v>
+        <v>184.03261209546901</v>
       </c>
       <c r="G55" s="5">
-        <f t="shared" si="2"/>
-        <v>1.19513965082997</v>
+        <v>1.1951396508299701</v>
       </c>
       <c r="H55" s="5">
-        <f t="shared" si="3"/>
-        <v>289673.448472154</v>
-      </c>
-    </row>
-    <row r="56" s="2" customFormat="1" spans="1:8">
+        <v>289673.44847215398</v>
+      </c>
+    </row>
+    <row r="56" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A56" s="4" t="s">
         <v>65</v>
       </c>
@@ -7047,24 +6135,22 @@
         <v>150</v>
       </c>
       <c r="D56" s="5">
-        <v>438.164992718447</v>
+        <v>438.16499271844702</v>
       </c>
       <c r="E56" s="5">
-        <v>369.813692327729</v>
+        <v>369.81369232772897</v>
       </c>
       <c r="F56" s="5">
-        <v>190.911956287</v>
+        <v>190.91195628700001</v>
       </c>
       <c r="G56" s="5">
-        <f t="shared" si="2"/>
         <v>1.18482631067685</v>
       </c>
       <c r="H56" s="5">
-        <f t="shared" si="3"/>
-        <v>262797.165803572</v>
-      </c>
-    </row>
-    <row r="57" s="2" customFormat="1" spans="1:8">
+        <v>262797.16580357199</v>
+      </c>
+    </row>
+    <row r="57" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A57" s="4" t="s">
         <v>66</v>
       </c>
@@ -7075,24 +6161,22 @@
         <v>150</v>
       </c>
       <c r="D57" s="5">
-        <v>444.733027076591</v>
+        <v>444.73302707659099</v>
       </c>
       <c r="E57" s="5">
-        <v>398.075249393204</v>
+        <v>398.07524939320399</v>
       </c>
       <c r="F57" s="5">
         <v>163.654490358684</v>
       </c>
       <c r="G57" s="5">
-        <f t="shared" si="2"/>
-        <v>1.11720843673278</v>
+        <v>1.1172084367327799</v>
       </c>
       <c r="H57" s="5">
-        <f t="shared" si="3"/>
         <v>228653.146041056</v>
       </c>
     </row>
-    <row r="58" s="2" customFormat="1" spans="1:8">
+    <row r="58" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A58" s="4" t="s">
         <v>67</v>
       </c>
@@ -7103,24 +6187,22 @@
         <v>150</v>
       </c>
       <c r="D58" s="5">
-        <v>382.358842801326</v>
+        <v>382.35884280132598</v>
       </c>
       <c r="E58" s="5">
-        <v>346.82328595785</v>
+        <v>346.82328595784998</v>
       </c>
       <c r="F58" s="5">
-        <v>182.194243369642</v>
+        <v>182.19424336964201</v>
       </c>
       <c r="G58" s="5">
-        <f t="shared" si="2"/>
-        <v>1.10246012387933</v>
+        <v>1.1024601238793299</v>
       </c>
       <c r="H58" s="5">
-        <f t="shared" si="3"/>
-        <v>218854.591338882</v>
-      </c>
-    </row>
-    <row r="59" s="2" customFormat="1" spans="1:8">
+        <v>218854.59133888199</v>
+      </c>
+    </row>
+    <row r="59" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A59" s="4" t="s">
         <v>68</v>
       </c>
@@ -7131,24 +6213,22 @@
         <v>150</v>
       </c>
       <c r="D59" s="5">
-        <v>405.630124457453</v>
+        <v>405.63012445745301</v>
       </c>
       <c r="E59" s="5">
-        <v>351.674517047401</v>
+        <v>351.67451704740103</v>
       </c>
       <c r="F59" s="5">
-        <v>155.730246944603</v>
+        <v>155.73024694460301</v>
       </c>
       <c r="G59" s="5">
-        <f t="shared" si="2"/>
         <v>1.15342484255912</v>
       </c>
       <c r="H59" s="5">
-        <f t="shared" si="3"/>
-        <v>198450.887615397</v>
-      </c>
-    </row>
-    <row r="60" s="2" customFormat="1" spans="1:8">
+        <v>198450.88761539699</v>
+      </c>
+    </row>
+    <row r="60" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A60" s="4" t="s">
         <v>69</v>
       </c>
@@ -7159,24 +6239,22 @@
         <v>210</v>
       </c>
       <c r="D60" s="5">
-        <v>484.549697994379</v>
+        <v>484.54969799437902</v>
       </c>
       <c r="E60" s="5">
         <v>386.700558277977</v>
       </c>
       <c r="F60" s="5">
-        <v>184.498045145631</v>
+        <v>184.49804514563101</v>
       </c>
       <c r="G60" s="5">
-        <f t="shared" si="2"/>
-        <v>1.25303594117406</v>
+        <v>1.2530359411740599</v>
       </c>
       <c r="H60" s="5">
-        <f t="shared" si="3"/>
         <v>280853.58305287</v>
       </c>
     </row>
-    <row r="61" s="2" customFormat="1" spans="1:8">
+    <row r="61" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A61" s="4" t="s">
         <v>70</v>
       </c>
@@ -7187,24 +6265,22 @@
         <v>210</v>
       </c>
       <c r="D61" s="5">
-        <v>418.443392532839</v>
+        <v>418.44339253283903</v>
       </c>
       <c r="E61" s="5">
-        <v>432.35867184466</v>
+        <v>432.35867184466002</v>
       </c>
       <c r="F61" s="5">
-        <v>199.71274480297</v>
+        <v>199.71274480297001</v>
       </c>
       <c r="G61" s="5">
-        <f t="shared" si="2"/>
-        <v>0.967815426825021</v>
+        <v>0.96781542682502097</v>
       </c>
       <c r="H61" s="5">
-        <f t="shared" si="3"/>
-        <v>262538.11802486</v>
-      </c>
-    </row>
-    <row r="62" s="2" customFormat="1" spans="1:8">
+        <v>262538.11802485998</v>
+      </c>
+    </row>
+    <row r="62" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A62" s="4" t="s">
         <v>71</v>
       </c>
@@ -7218,21 +6294,19 @@
         <v>403.33884339059</v>
       </c>
       <c r="E62" s="5">
-        <v>454.57808639532</v>
+        <v>454.57808639531999</v>
       </c>
       <c r="F62" s="5">
         <v>166.925207244212</v>
       </c>
       <c r="G62" s="5">
-        <f t="shared" si="2"/>
-        <v>0.887281757440084</v>
+        <v>0.88728175744008397</v>
       </c>
       <c r="H62" s="5">
-        <f t="shared" si="3"/>
         <v>211515.328128202</v>
       </c>
     </row>
-    <row r="63" s="2" customFormat="1" spans="1:8">
+    <row r="63" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A63" s="4" t="s">
         <v>72</v>
       </c>
@@ -7243,24 +6317,22 @@
         <v>210</v>
       </c>
       <c r="D63" s="5">
-        <v>432.231986496028</v>
+        <v>432.23198649602801</v>
       </c>
       <c r="E63" s="5">
-        <v>413.010550772286</v>
+        <v>413.01055077228602</v>
       </c>
       <c r="F63" s="5">
         <v>196.305929159312</v>
       </c>
       <c r="G63" s="5">
-        <f t="shared" si="2"/>
-        <v>1.04653981765793</v>
+        <v>1.0465398176579299</v>
       </c>
       <c r="H63" s="5">
-        <f t="shared" si="3"/>
-        <v>266563.19958748</v>
-      </c>
-    </row>
-    <row r="64" s="2" customFormat="1" spans="1:8">
+        <v>266563.19958747999</v>
+      </c>
+    </row>
+    <row r="64" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A64" s="4" t="s">
         <v>73</v>
       </c>
@@ -7271,24 +6343,22 @@
         <v>210</v>
       </c>
       <c r="D64" s="5">
-        <v>417.245147994379</v>
+        <v>417.24514799437901</v>
       </c>
       <c r="E64" s="5">
-        <v>354.466158584568</v>
+        <v>354.46615858456801</v>
       </c>
       <c r="F64" s="5">
-        <v>149.041051622381</v>
+        <v>149.04105162238099</v>
       </c>
       <c r="G64" s="5">
-        <f t="shared" si="2"/>
-        <v>1.17710855575183</v>
+        <v>1.1771085557518299</v>
       </c>
       <c r="H64" s="5">
-        <f t="shared" si="3"/>
-        <v>195365.140514398</v>
-      </c>
-    </row>
-    <row r="65" s="2" customFormat="1" spans="1:8">
+        <v>195365.14051439799</v>
+      </c>
+    </row>
+    <row r="65" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A65" s="4" t="s">
         <v>74</v>
       </c>
@@ -7299,24 +6369,22 @@
         <v>210</v>
       </c>
       <c r="D65" s="5">
-        <v>436.972148932039</v>
+        <v>436.97214893203898</v>
       </c>
       <c r="E65" s="5">
-        <v>396.092191067961</v>
+        <v>396.09219106796098</v>
       </c>
       <c r="F65" s="5">
-        <v>166.692157839806</v>
+        <v>166.69215783980599</v>
       </c>
       <c r="G65" s="5">
-        <f t="shared" si="2"/>
         <v>1.1032081893709</v>
       </c>
       <c r="H65" s="5">
-        <f t="shared" si="3"/>
-        <v>228833.076140529</v>
-      </c>
-    </row>
-    <row r="66" s="2" customFormat="1" spans="1:8">
+        <v>228833.07614052901</v>
+      </c>
+    </row>
+    <row r="66" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A66" s="4" t="s">
         <v>75</v>
       </c>
@@ -7327,24 +6395,22 @@
         <v>300</v>
       </c>
       <c r="D66" s="5">
-        <v>347.882081435716</v>
+        <v>347.88208143571597</v>
       </c>
       <c r="E66" s="5">
-        <v>402.036870226537</v>
+        <v>402.03687022653702</v>
       </c>
       <c r="F66" s="5">
         <v>230.588298278906</v>
       </c>
       <c r="G66" s="5">
-        <f t="shared" si="2"/>
-        <v>0.865298949421464</v>
+        <v>0.86529894942146401</v>
       </c>
       <c r="H66" s="5">
-        <f t="shared" si="3"/>
-        <v>252010.825430877</v>
-      </c>
-    </row>
-    <row r="67" s="2" customFormat="1" spans="1:8">
+        <v>252010.82543087701</v>
+      </c>
+    </row>
+    <row r="67" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A67" s="4" t="s">
         <v>76</v>
       </c>
@@ -7355,24 +6421,22 @@
         <v>300</v>
       </c>
       <c r="D67" s="5">
-        <v>364.871101806904</v>
+        <v>364.87110180690399</v>
       </c>
       <c r="E67" s="5">
-        <v>425.907112796656</v>
+        <v>425.90711279665601</v>
       </c>
       <c r="F67" s="5">
-        <v>191.412041814995</v>
+        <v>191.41204181499501</v>
       </c>
       <c r="G67" s="5">
-        <f t="shared" si="2"/>
-        <v>0.856691731234616</v>
+        <v>0.85669173123461595</v>
       </c>
       <c r="H67" s="5">
-        <f t="shared" si="3"/>
-        <v>219411.101029456</v>
-      </c>
-    </row>
-    <row r="68" s="2" customFormat="1" spans="1:8">
+        <v>219411.10102945601</v>
+      </c>
+    </row>
+    <row r="68" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A68" s="4" t="s">
         <v>77</v>
       </c>
@@ -7383,24 +6447,22 @@
         <v>300</v>
       </c>
       <c r="D68" s="5">
-        <v>400.540619579288</v>
+        <v>400.54061957928798</v>
       </c>
       <c r="E68" s="5">
-        <v>381.894619428263</v>
+        <v>381.89461942826301</v>
       </c>
       <c r="F68" s="5">
         <v>213.877404649407</v>
       </c>
       <c r="G68" s="5">
-        <f t="shared" si="2"/>
         <v>1.04882498784335</v>
       </c>
       <c r="H68" s="5">
-        <f t="shared" si="3"/>
-        <v>269129.524060148</v>
-      </c>
-    </row>
-    <row r="69" s="2" customFormat="1" spans="1:8">
+        <v>269129.52406014799</v>
+      </c>
+    </row>
+    <row r="69" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A69" s="4" t="s">
         <v>78</v>
       </c>
@@ -7411,24 +6473,22 @@
         <v>300</v>
       </c>
       <c r="D69" s="5">
-        <v>327.352298294411</v>
+        <v>327.35229829441101</v>
       </c>
       <c r="E69" s="5">
-        <v>417.724273222251</v>
+        <v>417.72427322225099</v>
       </c>
       <c r="F69" s="5">
-        <v>215.064461138809</v>
+        <v>215.06446113880901</v>
       </c>
       <c r="G69" s="5">
-        <f t="shared" si="2"/>
-        <v>0.78365639556752</v>
+        <v>0.78365639556751998</v>
       </c>
       <c r="H69" s="5">
-        <f t="shared" si="3"/>
-        <v>221173.921046827</v>
-      </c>
-    </row>
-    <row r="70" s="2" customFormat="1" spans="1:8">
+        <v>221173.92104682699</v>
+      </c>
+    </row>
+    <row r="70" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A70" s="4" t="s">
         <v>79</v>
       </c>
@@ -7439,24 +6499,22 @@
         <v>300</v>
       </c>
       <c r="D70" s="5">
-        <v>300.207580898623</v>
+        <v>300.20758089862301</v>
       </c>
       <c r="E70" s="5">
-        <v>440.037235278844</v>
+        <v>440.03723527884398</v>
       </c>
       <c r="F70" s="5">
-        <v>186.767537785053</v>
+        <v>186.76753778505301</v>
       </c>
       <c r="G70" s="5">
-        <f t="shared" si="2"/>
-        <v>0.682232222253616</v>
+        <v>0.68223222225361602</v>
       </c>
       <c r="H70" s="5">
-        <f t="shared" si="3"/>
-        <v>176146.054968801</v>
-      </c>
-    </row>
-    <row r="71" s="2" customFormat="1" spans="1:8">
+        <v>176146.05496880101</v>
+      </c>
+    </row>
+    <row r="71" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A71" s="4" t="s">
         <v>80</v>
       </c>
@@ -7467,47 +6525,65 @@
         <v>300</v>
       </c>
       <c r="D71" s="5">
-        <v>416.184680798274</v>
+        <v>416.18468079827397</v>
       </c>
       <c r="E71" s="5">
-        <v>473.983129004854</v>
+        <v>473.98312900485399</v>
       </c>
       <c r="F71" s="5">
-        <v>194.816706256742</v>
+        <v>194.81670625674201</v>
       </c>
       <c r="G71" s="5">
-        <f t="shared" si="2"/>
         <v>0.878058005296665</v>
       </c>
       <c r="H71" s="5">
-        <f t="shared" si="3"/>
-        <v>254719.480062954</v>
-      </c>
+        <v>254719.48006295401</v>
+      </c>
+    </row>
+    <row r="73" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="E73" s="6"/>
+      <c r="F73" s="6"/>
+      <c r="G73" s="6"/>
+      <c r="H73" s="6"/>
+    </row>
+    <row r="74" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="E74" s="6"/>
+      <c r="F74" s="6"/>
+      <c r="G74" s="6"/>
+      <c r="H74" s="6"/>
+    </row>
+    <row r="75" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="E75" s="6"/>
+      <c r="F75" s="6"/>
+      <c r="G75" s="6"/>
+      <c r="H75" s="6"/>
+    </row>
+    <row r="76" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="G76" s="6"/>
     </row>
   </sheetData>
+  <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:H78"/>
-  <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="14" outlineLevelCol="7"/>
+  <sheetFormatPr defaultColWidth="8.7265625" defaultRowHeight="14" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="8.72727272727273" style="2"/>
-    <col min="2" max="2" width="10.6363636363636" style="2" customWidth="1"/>
-    <col min="3" max="3" width="8.72727272727273" style="2"/>
-    <col min="4" max="4" width="18.2727272727273" style="3" customWidth="1"/>
-    <col min="5" max="5" width="15.0909090909091" style="3" customWidth="1"/>
-    <col min="6" max="6" width="15.9090909090909" style="3" customWidth="1"/>
-    <col min="7" max="7" width="18.2727272727273" style="3" customWidth="1"/>
-    <col min="8" max="8" width="20.4545454545455" style="3" customWidth="1"/>
-    <col min="9" max="16384" width="8.72727272727273" style="1"/>
+    <col min="1" max="1" width="8.7265625" style="2"/>
+    <col min="2" max="2" width="10.6328125" style="2" customWidth="1"/>
+    <col min="3" max="3" width="8.7265625" style="2"/>
+    <col min="4" max="4" width="18.26953125" style="3" customWidth="1"/>
+    <col min="5" max="5" width="15.08984375" style="3" customWidth="1"/>
+    <col min="6" max="6" width="15.90625" style="3" customWidth="1"/>
+    <col min="7" max="7" width="18.26953125" style="3" customWidth="1"/>
+    <col min="8" max="8" width="20.453125" style="3" customWidth="1"/>
+    <col min="9" max="16384" width="8.7265625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" ht="16" spans="1:8">
+    <row r="1" spans="1:8" ht="16" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
@@ -7533,7 +6609,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="2" s="1" customFormat="1" spans="1:8">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" s="4" t="s">
         <v>7</v>
       </c>
@@ -7544,24 +6620,24 @@
         <v>30</v>
       </c>
       <c r="D2" s="5">
-        <v>317.3189366</v>
+        <v>317.31893659999997</v>
       </c>
       <c r="E2" s="5">
-        <v>172.943168</v>
+        <v>172.94316800000001</v>
       </c>
       <c r="F2" s="5">
         <v>111.2891133</v>
       </c>
       <c r="G2" s="5">
         <f t="shared" ref="G2:G65" si="0">D2/E2</f>
-        <v>1.83481625940841</v>
+        <v>1.8348162594084101</v>
       </c>
       <c r="H2" s="5">
         <f t="shared" ref="H2:H65" si="1">D2*F2*PI()</f>
         <v>110942.652491549</v>
       </c>
     </row>
-    <row r="3" s="1" customFormat="1" spans="1:8">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3" s="4" t="s">
         <v>9</v>
       </c>
@@ -7572,24 +6648,24 @@
         <v>30</v>
       </c>
       <c r="D3" s="5">
-        <v>261.972932</v>
+        <v>261.97293200000001</v>
       </c>
       <c r="E3" s="5">
-        <v>160.5429109</v>
+        <v>160.54291090000001</v>
       </c>
       <c r="F3" s="5">
-        <v>108.1264205</v>
+        <v>108.12642049999999</v>
       </c>
       <c r="G3" s="5">
         <f t="shared" si="0"/>
-        <v>1.63179383338315</v>
+        <v>1.6317938333831501</v>
       </c>
       <c r="H3" s="5">
         <f t="shared" si="1"/>
         <v>88989.3673886537</v>
       </c>
     </row>
-    <row r="4" s="1" customFormat="1" spans="1:8">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4" s="4" t="s">
         <v>10</v>
       </c>
@@ -7600,7 +6676,7 @@
         <v>30</v>
       </c>
       <c r="D4" s="5">
-        <v>162.5151384</v>
+        <v>162.51513840000001</v>
       </c>
       <c r="E4" s="5">
         <v>250.417505097087</v>
@@ -7610,14 +6686,14 @@
       </c>
       <c r="G4" s="5">
         <f t="shared" si="0"/>
-        <v>0.648976749197277</v>
+        <v>0.64897674919727699</v>
       </c>
       <c r="H4" s="5">
         <f t="shared" si="1"/>
-        <v>51269.653222363</v>
-      </c>
-    </row>
-    <row r="5" s="1" customFormat="1" spans="1:8">
+        <v>51269.653222362998</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
         <v>11</v>
       </c>
@@ -7631,21 +6707,21 @@
         <v>300.844773236246</v>
       </c>
       <c r="E5" s="5">
-        <v>190.036956666667</v>
+        <v>190.03695666666701</v>
       </c>
       <c r="F5" s="5">
-        <v>89.7014429045307</v>
+        <v>89.701442904530694</v>
       </c>
       <c r="G5" s="5">
         <f t="shared" si="0"/>
-        <v>1.58308561930899</v>
+        <v>1.5830856193089899</v>
       </c>
       <c r="H5" s="5">
         <f t="shared" si="1"/>
-        <v>84779.6798683026</v>
-      </c>
-    </row>
-    <row r="6" s="1" customFormat="1" spans="1:8">
+        <v>84779.679868302599</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
         <v>12</v>
       </c>
@@ -7656,13 +6732,13 @@
         <v>30</v>
       </c>
       <c r="D6" s="5">
-        <v>238.653577985437</v>
+        <v>238.65357798543701</v>
       </c>
       <c r="E6" s="5">
-        <v>227.91118401699</v>
+        <v>227.91118401699001</v>
       </c>
       <c r="F6" s="5">
-        <v>97.28091625</v>
+        <v>97.280916250000004</v>
       </c>
       <c r="G6" s="5">
         <f t="shared" si="0"/>
@@ -7670,10 +6746,10 @@
       </c>
       <c r="H6" s="5">
         <f t="shared" si="1"/>
-        <v>72936.5933653694</v>
-      </c>
-    </row>
-    <row r="7" s="1" customFormat="1" spans="1:8">
+        <v>72936.593365369394</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A7" s="4" t="s">
         <v>13</v>
       </c>
@@ -7684,7 +6760,7 @@
         <v>30</v>
       </c>
       <c r="D7" s="5">
-        <v>290.948661658443</v>
+        <v>290.94866165844297</v>
       </c>
       <c r="E7" s="5">
         <v>168.043833391692</v>
@@ -7694,14 +6770,14 @@
       </c>
       <c r="G7" s="5">
         <f t="shared" si="0"/>
-        <v>1.7313855307042</v>
+        <v>1.7313855307042001</v>
       </c>
       <c r="H7" s="5">
         <f t="shared" si="1"/>
-        <v>103625.756219283</v>
-      </c>
-    </row>
-    <row r="8" s="1" customFormat="1" spans="1:8">
+        <v>103625.75621928299</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A8" s="4" t="s">
         <v>14</v>
       </c>
@@ -7712,10 +6788,10 @@
         <v>60</v>
       </c>
       <c r="D8" s="5">
-        <v>273.608519354839</v>
+        <v>273.60851935483902</v>
       </c>
       <c r="E8" s="5">
-        <v>259.11068361259</v>
+        <v>259.11068361258998</v>
       </c>
       <c r="F8" s="5">
         <v>125.840078311932</v>
@@ -7729,7 +6805,7 @@
         <v>108167.917481974</v>
       </c>
     </row>
-    <row r="9" s="1" customFormat="1" spans="1:8">
+    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A9" s="4" t="s">
         <v>15</v>
       </c>
@@ -7743,21 +6819,21 @@
         <v>280.291873269652</v>
       </c>
       <c r="E9" s="5">
-        <v>180.106337997181</v>
+        <v>180.10633799718099</v>
       </c>
       <c r="F9" s="5">
-        <v>139.301263513937</v>
+        <v>139.30126351393699</v>
       </c>
       <c r="G9" s="5">
         <f t="shared" si="0"/>
-        <v>1.55625768857751</v>
+        <v>1.5562576885775099</v>
       </c>
       <c r="H9" s="5">
         <f t="shared" si="1"/>
         <v>122663.523170017</v>
       </c>
     </row>
-    <row r="10" s="1" customFormat="1" spans="1:8">
+    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A10" s="4" t="s">
         <v>16</v>
       </c>
@@ -7768,24 +6844,24 @@
         <v>60</v>
       </c>
       <c r="D10" s="5">
-        <v>202.687747531207</v>
+        <v>202.68774753120701</v>
       </c>
       <c r="E10" s="5">
-        <v>200.137531435506</v>
+        <v>200.13753143550599</v>
       </c>
       <c r="F10" s="5">
-        <v>104.33923571914</v>
+        <v>104.33923571914001</v>
       </c>
       <c r="G10" s="5">
         <f t="shared" si="0"/>
-        <v>1.01274231813198</v>
+        <v>1.0127423181319799</v>
       </c>
       <c r="H10" s="5">
         <f t="shared" si="1"/>
-        <v>66439.295745999</v>
-      </c>
-    </row>
-    <row r="11" s="1" customFormat="1" spans="1:8">
+        <v>66439.295745998999</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A11" s="4" t="s">
         <v>17</v>
       </c>
@@ -7796,24 +6872,24 @@
         <v>60</v>
       </c>
       <c r="D11" s="5">
-        <v>360.362547845874</v>
+        <v>360.36254784587402</v>
       </c>
       <c r="E11" s="5">
-        <v>268.572025394417</v>
+        <v>268.57202539441698</v>
       </c>
       <c r="F11" s="5">
-        <v>147.922677199636</v>
+        <v>147.92267719963601</v>
       </c>
       <c r="G11" s="5">
         <f t="shared" si="0"/>
-        <v>1.34177246240243</v>
+        <v>1.3417724624024301</v>
       </c>
       <c r="H11" s="5">
         <f t="shared" si="1"/>
-        <v>167465.087179432</v>
-      </c>
-    </row>
-    <row r="12" s="1" customFormat="1" spans="1:8">
+        <v>167465.08717943201</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A12" s="4" t="s">
         <v>18</v>
       </c>
@@ -7827,21 +6903,21 @@
         <v>252.843367475728</v>
       </c>
       <c r="E12" s="5">
-        <v>196.006486274663</v>
+        <v>196.00648627466299</v>
       </c>
       <c r="F12" s="5">
         <v>129.976991199499</v>
       </c>
       <c r="G12" s="5">
         <f t="shared" si="0"/>
-        <v>1.28997449156565</v>
+        <v>1.2899744915656499</v>
       </c>
       <c r="H12" s="5">
         <f t="shared" si="1"/>
-        <v>103244.735949762</v>
-      </c>
-    </row>
-    <row r="13" s="1" customFormat="1" spans="1:8">
+        <v>103244.73594976201</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A13" s="4" t="s">
         <v>19</v>
       </c>
@@ -7852,24 +6928,24 @@
         <v>60</v>
       </c>
       <c r="D13" s="5">
-        <v>347.932452321655</v>
+        <v>347.93245232165498</v>
       </c>
       <c r="E13" s="5">
-        <v>247.369769508935</v>
+        <v>247.36976950893501</v>
       </c>
       <c r="F13" s="5">
-        <v>142.059114682707</v>
+        <v>142.05911468270699</v>
       </c>
       <c r="G13" s="5">
         <f t="shared" si="0"/>
-        <v>1.40652777828249</v>
+        <v>1.4065277782824901</v>
       </c>
       <c r="H13" s="5">
         <f t="shared" si="1"/>
         <v>155279.425150052</v>
       </c>
     </row>
-    <row r="14" s="1" customFormat="1" spans="1:8">
+    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A14" s="4" t="s">
         <v>20</v>
       </c>
@@ -7880,10 +6956,10 @@
         <v>90</v>
       </c>
       <c r="D14" s="5">
-        <v>400.925754951456</v>
+        <v>400.92575495145599</v>
       </c>
       <c r="E14" s="5">
-        <v>327.324309488085</v>
+        <v>327.32430948808502</v>
       </c>
       <c r="F14" s="5">
         <v>171.377923592233</v>
@@ -7894,10 +6970,10 @@
       </c>
       <c r="H14" s="5">
         <f t="shared" si="1"/>
-        <v>215858.276417328</v>
-      </c>
-    </row>
-    <row r="15" s="1" customFormat="1" spans="1:8">
+        <v>215858.27641732799</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A15" s="4" t="s">
         <v>21</v>
       </c>
@@ -7908,24 +6984,24 @@
         <v>90</v>
       </c>
       <c r="D15" s="5">
-        <v>337.296790952461</v>
+        <v>337.29679095246098</v>
       </c>
       <c r="E15" s="5">
-        <v>264.33990778373</v>
+        <v>264.33990778372998</v>
       </c>
       <c r="F15" s="5">
-        <v>125.355081796117</v>
+        <v>125.35508179611701</v>
       </c>
       <c r="G15" s="5">
         <f t="shared" si="0"/>
-        <v>1.27599647658355</v>
+        <v>1.2759964765835501</v>
       </c>
       <c r="H15" s="5">
         <f t="shared" si="1"/>
-        <v>132832.402179932</v>
-      </c>
-    </row>
-    <row r="16" s="1" customFormat="1" spans="1:8">
+        <v>132832.40217993199</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A16" s="4" t="s">
         <v>22</v>
       </c>
@@ -7936,24 +7012,24 @@
         <v>90</v>
       </c>
       <c r="D16" s="5">
-        <v>262.626767723611</v>
+        <v>262.62676772361101</v>
       </c>
       <c r="E16" s="5">
-        <v>333.367284517662</v>
+        <v>333.36728451766197</v>
       </c>
       <c r="F16" s="5">
-        <v>183.094745651725</v>
+        <v>183.09474565172499</v>
       </c>
       <c r="G16" s="5">
         <f t="shared" si="0"/>
-        <v>0.787800062935381</v>
+        <v>0.78780006293538096</v>
       </c>
       <c r="H16" s="5">
         <f t="shared" si="1"/>
-        <v>151065.30875992</v>
-      </c>
-    </row>
-    <row r="17" s="1" customFormat="1" spans="1:8">
+        <v>151065.30875992001</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A17" s="4" t="s">
         <v>23</v>
       </c>
@@ -7970,18 +7046,18 @@
         <v>359.129570609003</v>
       </c>
       <c r="F17" s="5">
-        <v>136.13676971168</v>
+        <v>136.13676971167999</v>
       </c>
       <c r="G17" s="5">
         <f t="shared" si="0"/>
-        <v>0.710416693529224</v>
+        <v>0.71041669352922399</v>
       </c>
       <c r="H17" s="5">
         <f t="shared" si="1"/>
-        <v>109116.30180019</v>
-      </c>
-    </row>
-    <row r="18" s="1" customFormat="1" spans="1:8">
+        <v>109116.30180019001</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A18" s="4" t="s">
         <v>24</v>
       </c>
@@ -7992,24 +7068,24 @@
         <v>90</v>
       </c>
       <c r="D18" s="5">
-        <v>365.698382121462</v>
+        <v>365.69838212146198</v>
       </c>
       <c r="E18" s="5">
-        <v>328.333833949597</v>
+        <v>328.33383394959702</v>
       </c>
       <c r="F18" s="5">
-        <v>188.459064852303</v>
+        <v>188.45906485230299</v>
       </c>
       <c r="G18" s="5">
         <f t="shared" si="0"/>
-        <v>1.11380048081673</v>
+        <v>1.1138004808167301</v>
       </c>
       <c r="H18" s="5">
         <f t="shared" si="1"/>
-        <v>216515.974225247</v>
-      </c>
-    </row>
-    <row r="19" s="1" customFormat="1" spans="1:8">
+        <v>216515.97422524699</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A19" s="4" t="s">
         <v>25</v>
       </c>
@@ -8020,24 +7096,24 @@
         <v>90</v>
       </c>
       <c r="D19" s="5">
-        <v>368.619504652104</v>
+        <v>368.61950465210401</v>
       </c>
       <c r="E19" s="5">
         <v>279.53512753843</v>
       </c>
       <c r="F19" s="5">
-        <v>179.606990887945</v>
+        <v>179.60699088794499</v>
       </c>
       <c r="G19" s="5">
         <f t="shared" si="0"/>
-        <v>1.3186875935706</v>
+        <v>1.3186875935705999</v>
       </c>
       <c r="H19" s="5">
         <f t="shared" si="1"/>
-        <v>207994.293884237</v>
-      </c>
-    </row>
-    <row r="20" s="1" customFormat="1" spans="1:8">
+        <v>207994.29388423701</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A20" s="4" t="s">
         <v>26</v>
       </c>
@@ -8048,13 +7124,13 @@
         <v>150</v>
       </c>
       <c r="D20" s="5">
-        <v>522.62153825705</v>
+        <v>522.62153825705002</v>
       </c>
       <c r="E20" s="5">
-        <v>358.453814343504</v>
+        <v>358.45381434350401</v>
       </c>
       <c r="F20" s="5">
-        <v>203.53831425104</v>
+        <v>203.53831425103999</v>
       </c>
       <c r="G20" s="5">
         <f t="shared" si="0"/>
@@ -8062,10 +7138,10 @@
       </c>
       <c r="H20" s="5">
         <f t="shared" si="1"/>
-        <v>334182.227776318</v>
-      </c>
-    </row>
-    <row r="21" s="1" customFormat="1" spans="1:8">
+        <v>334182.22777631797</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A21" s="4" t="s">
         <v>27</v>
       </c>
@@ -8076,24 +7152,24 @@
         <v>150</v>
       </c>
       <c r="D21" s="5">
-        <v>344.346868042071</v>
+        <v>344.34686804207098</v>
       </c>
       <c r="E21" s="5">
-        <v>327.331937479774</v>
+        <v>327.33193747977401</v>
       </c>
       <c r="F21" s="5">
-        <v>152.491871672735</v>
+        <v>152.49187167273499</v>
       </c>
       <c r="G21" s="5">
         <f t="shared" si="0"/>
-        <v>1.05198066126178</v>
+        <v>1.0519806612617799</v>
       </c>
       <c r="H21" s="5">
         <f t="shared" si="1"/>
-        <v>164965.339411609</v>
-      </c>
-    </row>
-    <row r="22" s="1" customFormat="1" spans="1:8">
+        <v>164965.33941160899</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A22" s="4" t="s">
         <v>28</v>
       </c>
@@ -8104,24 +7180,24 @@
         <v>150</v>
       </c>
       <c r="D22" s="5">
-        <v>395.823943722418</v>
+        <v>395.82394372241799</v>
       </c>
       <c r="E22" s="5">
         <v>333.350709741836</v>
       </c>
       <c r="F22" s="5">
-        <v>174.535303056046</v>
+        <v>174.53530305604599</v>
       </c>
       <c r="G22" s="5">
         <f t="shared" si="0"/>
-        <v>1.18740993240712</v>
+        <v>1.1874099324071199</v>
       </c>
       <c r="H22" s="5">
         <f t="shared" si="1"/>
         <v>217037.720074274</v>
       </c>
     </row>
-    <row r="23" s="1" customFormat="1" spans="1:8">
+    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A23" s="4" t="s">
         <v>29</v>
       </c>
@@ -8132,24 +7208,24 @@
         <v>150</v>
       </c>
       <c r="D23" s="5">
-        <v>415.85780276488</v>
+        <v>415.85780276487998</v>
       </c>
       <c r="E23" s="5">
-        <v>315.11082549599</v>
+        <v>315.11082549599001</v>
       </c>
       <c r="F23" s="5">
         <v>167.761002458843</v>
       </c>
       <c r="G23" s="5">
         <f t="shared" si="0"/>
-        <v>1.31971918803587</v>
+        <v>1.3197191880358701</v>
       </c>
       <c r="H23" s="5">
         <f t="shared" si="1"/>
         <v>219172.337713338</v>
       </c>
     </row>
-    <row r="24" s="1" customFormat="1" spans="1:8">
+    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A24" s="4" t="s">
         <v>30</v>
       </c>
@@ -8160,24 +7236,24 @@
         <v>150</v>
       </c>
       <c r="D24" s="5">
-        <v>382.03881588939</v>
+        <v>382.03881588938998</v>
       </c>
       <c r="E24" s="5">
-        <v>325.70140520111</v>
+        <v>325.70140520110999</v>
       </c>
       <c r="F24" s="5">
-        <v>171.977371619279</v>
+        <v>171.97737161927901</v>
       </c>
       <c r="G24" s="5">
         <f t="shared" si="0"/>
-        <v>1.17297257484503</v>
+        <v>1.1729725748450299</v>
       </c>
       <c r="H24" s="5">
         <f t="shared" si="1"/>
-        <v>206409.019213632</v>
-      </c>
-    </row>
-    <row r="25" s="1" customFormat="1" spans="1:8">
+        <v>206409.01921363201</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A25" s="4" t="s">
         <v>31</v>
       </c>
@@ -8188,24 +7264,24 @@
         <v>150</v>
       </c>
       <c r="D25" s="5">
-        <v>426.115812711255</v>
+        <v>426.11581271125499</v>
       </c>
       <c r="E25" s="5">
-        <v>372.539022608774</v>
+        <v>372.53902260877402</v>
       </c>
       <c r="F25" s="5">
-        <v>172.562715596908</v>
+        <v>172.56271559690799</v>
       </c>
       <c r="G25" s="5">
         <f t="shared" si="0"/>
-        <v>1.14381524310473</v>
+        <v>1.1438152431047299</v>
       </c>
       <c r="H25" s="5">
         <f t="shared" si="1"/>
-        <v>231006.654181582</v>
-      </c>
-    </row>
-    <row r="26" s="1" customFormat="1" spans="1:8">
+        <v>231006.65418158201</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A26" s="4" t="s">
         <v>32</v>
       </c>
@@ -8216,24 +7292,24 @@
         <v>210</v>
       </c>
       <c r="D26" s="5">
-        <v>336.18365052646</v>
+        <v>336.18365052645999</v>
       </c>
       <c r="E26" s="5">
-        <v>217.05505891563</v>
+        <v>217.05505891563001</v>
       </c>
       <c r="F26" s="5">
-        <v>129.729337925612</v>
+        <v>129.72933792561199</v>
       </c>
       <c r="G26" s="5">
         <f t="shared" si="0"/>
-        <v>1.5488404288109</v>
+        <v>1.5488404288108999</v>
       </c>
       <c r="H26" s="5">
         <f t="shared" si="1"/>
-        <v>137013.910962951</v>
-      </c>
-    </row>
-    <row r="27" s="1" customFormat="1" spans="1:8">
+        <v>137013.91096295099</v>
+      </c>
+    </row>
+    <row r="27" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A27" s="4" t="s">
         <v>33</v>
       </c>
@@ -8247,21 +7323,21 @@
         <v>296.746445270668</v>
       </c>
       <c r="E27" s="5">
-        <v>217.680606935863</v>
+        <v>217.68060693586301</v>
       </c>
       <c r="F27" s="5">
-        <v>151.411411356281</v>
+        <v>151.41141135628101</v>
       </c>
       <c r="G27" s="5">
         <f t="shared" si="0"/>
-        <v>1.36321948678736</v>
+        <v>1.3632194867873599</v>
       </c>
       <c r="H27" s="5">
         <f t="shared" si="1"/>
-        <v>141154.265210124</v>
-      </c>
-    </row>
-    <row r="28" s="1" customFormat="1" spans="1:8">
+        <v>141154.26521012399</v>
+      </c>
+    </row>
+    <row r="28" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A28" s="4" t="s">
         <v>34</v>
       </c>
@@ -8272,13 +7348,13 @@
         <v>210</v>
       </c>
       <c r="D28" s="5">
-        <v>379.259895577131</v>
+        <v>379.25989557713098</v>
       </c>
       <c r="E28" s="5">
         <v>214.543403475112</v>
       </c>
       <c r="F28" s="5">
-        <v>182.575535174911</v>
+        <v>182.57553517491101</v>
       </c>
       <c r="G28" s="5">
         <f t="shared" si="0"/>
@@ -8286,10 +7362,10 @@
       </c>
       <c r="H28" s="5">
         <f t="shared" si="1"/>
-        <v>217535.117226597</v>
-      </c>
-    </row>
-    <row r="29" s="1" customFormat="1" spans="1:8">
+        <v>217535.11722659701</v>
+      </c>
+    </row>
+    <row r="29" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A29" s="4" t="s">
         <v>35</v>
       </c>
@@ -8300,7 +7376,7 @@
         <v>210</v>
       </c>
       <c r="D29" s="5">
-        <v>611.8134788364</v>
+        <v>611.81347883640001</v>
       </c>
       <c r="E29" s="5">
         <v>300.365435270251</v>
@@ -8310,14 +7386,14 @@
       </c>
       <c r="G29" s="5">
         <f t="shared" si="0"/>
-        <v>2.03689708266841</v>
+        <v>2.0368970826684101</v>
       </c>
       <c r="H29" s="5">
         <f t="shared" si="1"/>
-        <v>302943.903467257</v>
-      </c>
-    </row>
-    <row r="30" s="1" customFormat="1" spans="1:8">
+        <v>302943.90346725698</v>
+      </c>
+    </row>
+    <row r="30" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A30" s="4" t="s">
         <v>36</v>
       </c>
@@ -8328,13 +7404,13 @@
         <v>210</v>
       </c>
       <c r="D30" s="5">
-        <v>508.171274824496</v>
+        <v>508.17127482449598</v>
       </c>
       <c r="E30" s="5">
         <v>285.20345471994</v>
       </c>
       <c r="F30" s="5">
-        <v>207.994946699029</v>
+        <v>207.99494669902899</v>
       </c>
       <c r="G30" s="5">
         <f t="shared" si="0"/>
@@ -8342,10 +7418,10 @@
       </c>
       <c r="H30" s="5">
         <f t="shared" si="1"/>
-        <v>332057.098471864</v>
-      </c>
-    </row>
-    <row r="31" s="1" customFormat="1" spans="1:8">
+        <v>332057.09847186401</v>
+      </c>
+    </row>
+    <row r="31" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A31" s="4" t="s">
         <v>37</v>
       </c>
@@ -8356,24 +7432,24 @@
         <v>210</v>
       </c>
       <c r="D31" s="5">
-        <v>400.865847080906</v>
+        <v>400.86584708090601</v>
       </c>
       <c r="E31" s="5">
-        <v>245.077517411003</v>
+        <v>245.07751741100299</v>
       </c>
       <c r="F31" s="5">
-        <v>144.622175877023</v>
+        <v>144.62217587702301</v>
       </c>
       <c r="G31" s="5">
         <f t="shared" si="0"/>
-        <v>1.63566960901045</v>
+        <v>1.6356696090104501</v>
       </c>
       <c r="H31" s="5">
         <f t="shared" si="1"/>
         <v>182130.978508637</v>
       </c>
     </row>
-    <row r="32" s="1" customFormat="1" spans="1:8">
+    <row r="32" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A32" s="4" t="s">
         <v>38</v>
       </c>
@@ -8387,10 +7463,10 @@
         <v>344.734818808753</v>
       </c>
       <c r="E32" s="5">
-        <v>303.145652627524</v>
+        <v>303.14565262752399</v>
       </c>
       <c r="F32" s="5">
-        <v>149.212362297735</v>
+        <v>149.21236229773501</v>
       </c>
       <c r="G32" s="5">
         <f t="shared" si="0"/>
@@ -8401,7 +7477,7 @@
         <v>161599.431602433</v>
       </c>
     </row>
-    <row r="33" s="1" customFormat="1" spans="1:8">
+    <row r="33" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A33" s="4" t="s">
         <v>39</v>
       </c>
@@ -8415,21 +7491,21 @@
         <v>348.201279474263</v>
       </c>
       <c r="E33" s="5">
-        <v>485.328481113757</v>
+        <v>485.32848111375699</v>
       </c>
       <c r="F33" s="5">
         <v>163.992114737131</v>
       </c>
       <c r="G33" s="5">
         <f t="shared" si="0"/>
-        <v>0.717454864126648</v>
+        <v>0.71745486412664805</v>
       </c>
       <c r="H33" s="5">
         <f t="shared" si="1"/>
-        <v>179392.053636024</v>
-      </c>
-    </row>
-    <row r="34" s="1" customFormat="1" spans="1:8">
+        <v>179392.05363602401</v>
+      </c>
+    </row>
+    <row r="34" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A34" s="4" t="s">
         <v>40</v>
       </c>
@@ -8443,21 +7519,21 @@
         <v>381.203763428142</v>
       </c>
       <c r="E34" s="5">
-        <v>279.697499890606</v>
+        <v>279.69749989060603</v>
       </c>
       <c r="F34" s="5">
-        <v>152.385399815397</v>
+        <v>152.38539981539699</v>
       </c>
       <c r="G34" s="5">
         <f t="shared" si="0"/>
-        <v>1.36291444713391</v>
+        <v>1.3629144471339101</v>
       </c>
       <c r="H34" s="5">
         <f t="shared" si="1"/>
-        <v>182494.765078049</v>
-      </c>
-    </row>
-    <row r="35" s="1" customFormat="1" spans="1:8">
+        <v>182494.76507804901</v>
+      </c>
+    </row>
+    <row r="35" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A35" s="4" t="s">
         <v>41</v>
       </c>
@@ -8471,21 +7547,21 @@
         <v>352.185105021011</v>
       </c>
       <c r="E35" s="5">
-        <v>222.044048514708</v>
+        <v>222.04404851470801</v>
       </c>
       <c r="F35" s="5">
         <v>128.121198869729</v>
       </c>
       <c r="G35" s="5">
         <f t="shared" si="0"/>
-        <v>1.58610468227741</v>
+        <v>1.5861046822774101</v>
       </c>
       <c r="H35" s="5">
         <f t="shared" si="1"/>
-        <v>141756.130858279</v>
-      </c>
-    </row>
-    <row r="36" s="1" customFormat="1" spans="1:8">
+        <v>141756.13085827901</v>
+      </c>
+    </row>
+    <row r="36" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A36" s="4" t="s">
         <v>42</v>
       </c>
@@ -8496,13 +7572,13 @@
         <v>300</v>
       </c>
       <c r="D36" s="5">
-        <v>340.757048636493</v>
+        <v>340.75704863649298</v>
       </c>
       <c r="E36" s="5">
-        <v>231.920601784694</v>
+        <v>231.92060178469399</v>
       </c>
       <c r="F36" s="5">
-        <v>139.015703283838</v>
+        <v>139.01570328383801</v>
       </c>
       <c r="G36" s="5">
         <f t="shared" si="0"/>
@@ -8510,10 +7586,10 @@
       </c>
       <c r="H36" s="5">
         <f t="shared" si="1"/>
-        <v>148819.068528005</v>
-      </c>
-    </row>
-    <row r="37" s="1" customFormat="1" spans="1:8">
+        <v>148819.06852800501</v>
+      </c>
+    </row>
+    <row r="37" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A37" s="4" t="s">
         <v>43</v>
       </c>
@@ -8530,18 +7606,18 @@
         <v>189.389869027392</v>
       </c>
       <c r="F37" s="5">
-        <v>134.891620579057</v>
+        <v>134.89162057905699</v>
       </c>
       <c r="G37" s="5">
         <f t="shared" si="0"/>
-        <v>1.3027899407744</v>
+        <v>1.3027899407743999</v>
       </c>
       <c r="H37" s="5">
         <f t="shared" si="1"/>
         <v>104560.098881557</v>
       </c>
     </row>
-    <row r="38" s="1" customFormat="1" spans="1:8">
+    <row r="38" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A38" s="4" t="s">
         <v>44</v>
       </c>
@@ -8552,24 +7628,24 @@
         <v>30</v>
       </c>
       <c r="D38" s="5">
-        <v>264.16520211827</v>
+        <v>264.16520211826997</v>
       </c>
       <c r="E38" s="5">
-        <v>307.635205457488</v>
+        <v>307.63520545748798</v>
       </c>
       <c r="F38" s="5">
         <v>129.842860650191</v>
       </c>
       <c r="G38" s="5">
         <f t="shared" si="0"/>
-        <v>0.858696265680733</v>
+        <v>0.85869626568073298</v>
       </c>
       <c r="H38" s="5">
         <f t="shared" si="1"/>
         <v>107756.519718861</v>
       </c>
     </row>
-    <row r="39" s="1" customFormat="1" spans="1:8">
+    <row r="39" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A39" s="4" t="s">
         <v>46</v>
       </c>
@@ -8580,13 +7656,13 @@
         <v>30</v>
       </c>
       <c r="D39" s="5">
-        <v>304.597113045013</v>
+        <v>304.59711304501297</v>
       </c>
       <c r="E39" s="5">
         <v>304.10378011474</v>
       </c>
       <c r="F39" s="5">
-        <v>150.66192168579</v>
+        <v>150.66192168578999</v>
       </c>
       <c r="G39" s="5">
         <f t="shared" si="0"/>
@@ -8594,10 +7670,10 @@
       </c>
       <c r="H39" s="5">
         <f t="shared" si="1"/>
-        <v>144171.414031445</v>
-      </c>
-    </row>
-    <row r="40" s="1" customFormat="1" spans="1:8">
+        <v>144171.41403144499</v>
+      </c>
+    </row>
+    <row r="40" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A40" s="4" t="s">
         <v>47</v>
       </c>
@@ -8608,24 +7684,24 @@
         <v>30</v>
       </c>
       <c r="D40" s="5">
-        <v>224.523230774676</v>
+        <v>224.52323077467599</v>
       </c>
       <c r="E40" s="5">
-        <v>281.951501203479</v>
+        <v>281.95150120347898</v>
       </c>
       <c r="F40" s="5">
         <v>136.921979085761</v>
       </c>
       <c r="G40" s="5">
         <f t="shared" si="0"/>
-        <v>0.796318621522933</v>
+        <v>0.79631862152293298</v>
       </c>
       <c r="H40" s="5">
         <f t="shared" si="1"/>
-        <v>96579.3600599866</v>
-      </c>
-    </row>
-    <row r="41" s="1" customFormat="1" spans="1:8">
+        <v>96579.360059986604</v>
+      </c>
+    </row>
+    <row r="41" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A41" s="4" t="s">
         <v>48</v>
       </c>
@@ -8636,24 +7712,24 @@
         <v>30</v>
       </c>
       <c r="D41" s="5">
-        <v>260.285400718447</v>
+        <v>260.28540071844702</v>
       </c>
       <c r="E41" s="5">
         <v>283.541687339806</v>
       </c>
       <c r="F41" s="5">
-        <v>135.013633796116</v>
+        <v>135.01363379611601</v>
       </c>
       <c r="G41" s="5">
         <f t="shared" si="0"/>
-        <v>0.917979303715267</v>
+        <v>0.91797930371526704</v>
       </c>
       <c r="H41" s="5">
         <f t="shared" si="1"/>
         <v>110402.093370059</v>
       </c>
     </row>
-    <row r="42" s="1" customFormat="1" spans="1:8">
+    <row r="42" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A42" s="4" t="s">
         <v>49</v>
       </c>
@@ -8664,24 +7740,24 @@
         <v>30</v>
       </c>
       <c r="D42" s="5">
-        <v>231.857039544436</v>
+        <v>231.85703954443599</v>
       </c>
       <c r="E42" s="5">
-        <v>274.544936239731</v>
+        <v>274.54493623973099</v>
       </c>
       <c r="F42" s="5">
-        <v>123.123821639283</v>
+        <v>123.12382163928299</v>
       </c>
       <c r="G42" s="5">
         <f t="shared" si="0"/>
-        <v>0.844513990023039</v>
+        <v>0.84451399002303895</v>
       </c>
       <c r="H42" s="5">
         <f t="shared" si="1"/>
-        <v>89683.4374983828</v>
-      </c>
-    </row>
-    <row r="43" s="1" customFormat="1" spans="1:8">
+        <v>89683.437498382802</v>
+      </c>
+    </row>
+    <row r="43" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A43" s="4" t="s">
         <v>50</v>
       </c>
@@ -8692,24 +7768,24 @@
         <v>30</v>
       </c>
       <c r="D43" s="5">
-        <v>296.584884088457</v>
+        <v>296.58488408845699</v>
       </c>
       <c r="E43" s="5">
         <v>300.60054223301</v>
       </c>
       <c r="F43" s="5">
-        <v>134.798179998202</v>
+        <v>134.79817999820199</v>
       </c>
       <c r="G43" s="5">
         <f t="shared" si="0"/>
-        <v>0.986641214567603</v>
+        <v>0.98664121456760301</v>
       </c>
       <c r="H43" s="5">
         <f t="shared" si="1"/>
         <v>125598.054994176</v>
       </c>
     </row>
-    <row r="44" s="1" customFormat="1" spans="1:8">
+    <row r="44" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A44" s="4" t="s">
         <v>51</v>
       </c>
@@ -8723,21 +7799,21 @@
         <v>263.168313230737</v>
       </c>
       <c r="E44" s="5">
-        <v>287.392225883082</v>
+        <v>287.39222588308201</v>
       </c>
       <c r="F44" s="5">
-        <v>153.342109925635</v>
+        <v>153.34210992563499</v>
       </c>
       <c r="G44" s="5">
         <f t="shared" si="0"/>
-        <v>0.915711315509975</v>
+        <v>0.91571131550997498</v>
       </c>
       <c r="H44" s="5">
         <f t="shared" si="1"/>
         <v>126778.294259673</v>
       </c>
     </row>
-    <row r="45" s="1" customFormat="1" spans="1:8">
+    <row r="45" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A45" s="4" t="s">
         <v>52</v>
       </c>
@@ -8748,24 +7824,24 @@
         <v>60</v>
       </c>
       <c r="D45" s="5">
-        <v>307.171026807834</v>
+        <v>307.17102680783398</v>
       </c>
       <c r="E45" s="5">
-        <v>322.878591262136</v>
+        <v>322.87859126213601</v>
       </c>
       <c r="F45" s="5">
         <v>155.17334853532</v>
       </c>
       <c r="G45" s="5">
         <f t="shared" si="0"/>
-        <v>0.951351483562595</v>
+        <v>0.95135148356259502</v>
       </c>
       <c r="H45" s="5">
         <f t="shared" si="1"/>
-        <v>149743.249806834</v>
-      </c>
-    </row>
-    <row r="46" s="1" customFormat="1" spans="1:8">
+        <v>149743.24980683401</v>
+      </c>
+    </row>
+    <row r="46" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A46" s="4" t="s">
         <v>53</v>
       </c>
@@ -8776,24 +7852,24 @@
         <v>60</v>
       </c>
       <c r="D46" s="5">
-        <v>332.14045772286</v>
+        <v>332.14045772285999</v>
       </c>
       <c r="E46" s="5">
-        <v>346.630993049426</v>
+        <v>346.63099304942602</v>
       </c>
       <c r="F46" s="5">
         <v>162.214182700794</v>
       </c>
       <c r="G46" s="5">
         <f t="shared" si="0"/>
-        <v>0.958196077046983</v>
+        <v>0.95819607704698295</v>
       </c>
       <c r="H46" s="5">
         <f t="shared" si="1"/>
-        <v>169262.392498461</v>
-      </c>
-    </row>
-    <row r="47" s="1" customFormat="1" spans="1:8">
+        <v>169262.39249846101</v>
+      </c>
+    </row>
+    <row r="47" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A47" s="4" t="s">
         <v>54</v>
       </c>
@@ -8804,24 +7880,24 @@
         <v>60</v>
       </c>
       <c r="D47" s="5">
-        <v>302.69112143537</v>
+        <v>302.69112143537001</v>
       </c>
       <c r="E47" s="5">
-        <v>328.009368998667</v>
+        <v>328.00936899866701</v>
       </c>
       <c r="F47" s="5">
-        <v>142.013333371407</v>
+        <v>142.01333337140699</v>
       </c>
       <c r="G47" s="5">
         <f t="shared" si="0"/>
-        <v>0.92281242563105</v>
+        <v>0.92281242563105004</v>
       </c>
       <c r="H47" s="5">
         <f t="shared" si="1"/>
         <v>135045.052016217</v>
       </c>
     </row>
-    <row r="48" s="1" customFormat="1" spans="1:8">
+    <row r="48" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A48" s="4" t="s">
         <v>55</v>
       </c>
@@ -8832,13 +7908,13 @@
         <v>60</v>
       </c>
       <c r="D48" s="5">
-        <v>244.287983798544</v>
+        <v>244.28798379854399</v>
       </c>
       <c r="E48" s="5">
         <v>401.097427645631</v>
       </c>
       <c r="F48" s="5">
-        <v>158.86685881068</v>
+        <v>158.86685881067999</v>
       </c>
       <c r="G48" s="5">
         <f t="shared" si="0"/>
@@ -8849,7 +7925,7 @@
         <v>121922.900656817</v>
       </c>
     </row>
-    <row r="49" s="1" customFormat="1" spans="1:8">
+    <row r="49" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A49" s="4" t="s">
         <v>56</v>
       </c>
@@ -8866,18 +7942,18 @@
         <v>344.619108243092</v>
       </c>
       <c r="F49" s="5">
-        <v>143.880692699776</v>
+        <v>143.88069269977601</v>
       </c>
       <c r="G49" s="5">
         <f t="shared" si="0"/>
-        <v>0.841862954092464</v>
+        <v>0.84186295409246403</v>
       </c>
       <c r="H49" s="5">
         <f t="shared" si="1"/>
-        <v>131139.386002125</v>
-      </c>
-    </row>
-    <row r="50" s="1" customFormat="1" spans="1:8">
+        <v>131139.38600212499</v>
+      </c>
+    </row>
+    <row r="50" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A50" s="4" t="s">
         <v>57</v>
       </c>
@@ -8888,7 +7964,7 @@
         <v>90</v>
       </c>
       <c r="D50" s="5">
-        <v>301.830487297735</v>
+        <v>301.83048729773498</v>
       </c>
       <c r="E50" s="5">
         <v>321.117444587379</v>
@@ -8898,14 +7974,14 @@
       </c>
       <c r="G50" s="5">
         <f t="shared" si="0"/>
-        <v>0.939937995849379</v>
+        <v>0.93993799584937898</v>
       </c>
       <c r="H50" s="5">
         <f t="shared" si="1"/>
-        <v>148886.450821856</v>
-      </c>
-    </row>
-    <row r="51" s="1" customFormat="1" spans="1:8">
+        <v>148886.45082185601</v>
+      </c>
+    </row>
+    <row r="51" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A51" s="4" t="s">
         <v>58</v>
       </c>
@@ -8916,24 +7992,24 @@
         <v>90</v>
       </c>
       <c r="D51" s="5">
-        <v>367.584962228387</v>
+        <v>367.58496222838698</v>
       </c>
       <c r="E51" s="5">
         <v>318.99266530282</v>
       </c>
       <c r="F51" s="5">
-        <v>152.879204291879</v>
+        <v>152.87920429187901</v>
       </c>
       <c r="G51" s="5">
         <f t="shared" si="0"/>
-        <v>1.15233045211067</v>
+        <v>1.1523304521106701</v>
       </c>
       <c r="H51" s="5">
         <f t="shared" si="1"/>
         <v>176545.244035207</v>
       </c>
     </row>
-    <row r="52" s="1" customFormat="1" spans="1:8">
+    <row r="52" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A52" s="4" t="s">
         <v>59</v>
       </c>
@@ -8944,24 +8020,24 @@
         <v>90</v>
       </c>
       <c r="D52" s="5">
-        <v>287.31085374072</v>
+        <v>287.31085374072001</v>
       </c>
       <c r="E52" s="5">
         <v>320.283679392728</v>
       </c>
       <c r="F52" s="5">
-        <v>160.139323729298</v>
+        <v>160.13932372929801</v>
       </c>
       <c r="G52" s="5">
         <f t="shared" si="0"/>
-        <v>0.897051183767696</v>
+        <v>0.89705118376769599</v>
       </c>
       <c r="H52" s="5">
         <f t="shared" si="1"/>
-        <v>144543.942287612</v>
-      </c>
-    </row>
-    <row r="53" s="1" customFormat="1" spans="1:8">
+        <v>144543.94228761201</v>
+      </c>
+    </row>
+    <row r="53" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A53" s="4" t="s">
         <v>60</v>
       </c>
@@ -8972,13 +8048,13 @@
         <v>90</v>
       </c>
       <c r="D53" s="5">
-        <v>305.757812530854</v>
+        <v>305.75781253085398</v>
       </c>
       <c r="E53" s="5">
-        <v>346.434880738851</v>
+        <v>346.43488073885101</v>
       </c>
       <c r="F53" s="5">
-        <v>146.997115640941</v>
+        <v>146.99711564094099</v>
       </c>
       <c r="G53" s="5">
         <f t="shared" si="0"/>
@@ -8986,10 +8062,10 @@
       </c>
       <c r="H53" s="5">
         <f t="shared" si="1"/>
-        <v>141200.504532139</v>
-      </c>
-    </row>
-    <row r="54" s="1" customFormat="1" spans="1:8">
+        <v>141200.50453213899</v>
+      </c>
+    </row>
+    <row r="54" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A54" s="4" t="s">
         <v>61</v>
       </c>
@@ -9000,24 +8076,24 @@
         <v>90</v>
       </c>
       <c r="D54" s="5">
-        <v>257.745168338727</v>
+        <v>257.74516833872701</v>
       </c>
       <c r="E54" s="5">
-        <v>379.580174002157</v>
+        <v>379.58017400215698</v>
       </c>
       <c r="F54" s="5">
-        <v>163.168224878641</v>
+        <v>163.16822487864101</v>
       </c>
       <c r="G54" s="5">
         <f t="shared" si="0"/>
-        <v>0.679026951331927</v>
+        <v>0.67902695133192703</v>
       </c>
       <c r="H54" s="5">
         <f t="shared" si="1"/>
-        <v>132122.260144298</v>
-      </c>
-    </row>
-    <row r="55" s="1" customFormat="1" spans="1:8">
+        <v>132122.26014429799</v>
+      </c>
+    </row>
+    <row r="55" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A55" s="4" t="s">
         <v>62</v>
       </c>
@@ -9028,24 +8104,24 @@
         <v>90</v>
       </c>
       <c r="D55" s="5">
-        <v>272.646563151953</v>
+        <v>272.64656315195299</v>
       </c>
       <c r="E55" s="5">
-        <v>337.844271585008</v>
+        <v>337.84427158500802</v>
       </c>
       <c r="F55" s="5">
         <v>167.325824587943</v>
       </c>
       <c r="G55" s="5">
         <f t="shared" si="0"/>
-        <v>0.807018458157725</v>
+        <v>0.80701845815772499</v>
       </c>
       <c r="H55" s="5">
         <f t="shared" si="1"/>
         <v>143322.004689883</v>
       </c>
     </row>
-    <row r="56" s="1" customFormat="1" spans="1:8">
+    <row r="56" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A56" s="4" t="s">
         <v>63</v>
       </c>
@@ -9056,10 +8132,10 @@
         <v>150</v>
       </c>
       <c r="D56" s="5">
-        <v>396.777348283878</v>
+        <v>396.77734828387798</v>
       </c>
       <c r="E56" s="5">
-        <v>408.281854792835</v>
+        <v>408.28185479283502</v>
       </c>
       <c r="F56" s="5">
         <v>144.920868357719</v>
@@ -9070,10 +8146,10 @@
       </c>
       <c r="H56" s="5">
         <f t="shared" si="1"/>
-        <v>180645.717754339</v>
-      </c>
-    </row>
-    <row r="57" s="1" customFormat="1" spans="1:8">
+        <v>180645.71775433901</v>
+      </c>
+    </row>
+    <row r="57" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A57" s="4" t="s">
         <v>64</v>
       </c>
@@ -9084,24 +8160,24 @@
         <v>150</v>
       </c>
       <c r="D57" s="5">
-        <v>415.958152734628</v>
+        <v>415.95815273462802</v>
       </c>
       <c r="E57" s="5">
-        <v>324.545449908306</v>
+        <v>324.54544990830601</v>
       </c>
       <c r="F57" s="5">
         <v>141.4363600863</v>
       </c>
       <c r="G57" s="5">
         <f t="shared" si="0"/>
-        <v>1.28166379424561</v>
+        <v>1.2816637942456099</v>
       </c>
       <c r="H57" s="5">
         <f t="shared" si="1"/>
         <v>184824.944573157</v>
       </c>
     </row>
-    <row r="58" s="1" customFormat="1" spans="1:8">
+    <row r="58" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A58" s="4" t="s">
         <v>65</v>
       </c>
@@ -9112,10 +8188,10 @@
         <v>150</v>
       </c>
       <c r="D58" s="5">
-        <v>324.059147800551</v>
+        <v>324.05914780055099</v>
       </c>
       <c r="E58" s="5">
-        <v>266.837235341004</v>
+        <v>266.83723534100398</v>
       </c>
       <c r="F58" s="5">
         <v>149.766795780894</v>
@@ -9129,7 +8205,7 @@
         <v>152471.859392871</v>
       </c>
     </row>
-    <row r="59" s="1" customFormat="1" spans="1:8">
+    <row r="59" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A59" s="4" t="s">
         <v>66</v>
       </c>
@@ -9140,7 +8216,7 @@
         <v>150</v>
       </c>
       <c r="D59" s="5">
-        <v>394.439770090274</v>
+        <v>394.43977009027401</v>
       </c>
       <c r="E59" s="5">
         <v>342.913017952649</v>
@@ -9157,7 +8233,7 @@
         <v>189266.969248165</v>
       </c>
     </row>
-    <row r="60" s="1" customFormat="1" spans="1:8">
+    <row r="60" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A60" s="4" t="s">
         <v>67</v>
       </c>
@@ -9168,24 +8244,24 @@
         <v>150</v>
       </c>
       <c r="D60" s="5">
-        <v>370.721289398685</v>
+        <v>370.72128939868497</v>
       </c>
       <c r="E60" s="5">
-        <v>331.591503437206</v>
+        <v>331.59150343720597</v>
       </c>
       <c r="F60" s="5">
         <v>139.48020755559</v>
       </c>
       <c r="G60" s="5">
         <f t="shared" si="0"/>
-        <v>1.11800599700495</v>
+        <v>1.1180059970049501</v>
       </c>
       <c r="H60" s="5">
         <f t="shared" si="1"/>
-        <v>162446.36008807</v>
-      </c>
-    </row>
-    <row r="61" s="1" customFormat="1" spans="1:8">
+        <v>162446.36008807001</v>
+      </c>
+    </row>
+    <row r="61" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A61" s="4" t="s">
         <v>68</v>
       </c>
@@ -9196,24 +8272,24 @@
         <v>150</v>
       </c>
       <c r="D61" s="5">
-        <v>283.288765924234</v>
+        <v>283.28876592423399</v>
       </c>
       <c r="E61" s="5">
-        <v>344.51542944032</v>
+        <v>344.51542944032002</v>
       </c>
       <c r="F61" s="5">
-        <v>150.697406225014</v>
+        <v>150.69740622501399</v>
       </c>
       <c r="G61" s="5">
         <f t="shared" si="0"/>
-        <v>0.822281795577193</v>
+        <v>0.82228179557719305</v>
       </c>
       <c r="H61" s="5">
         <f t="shared" si="1"/>
-        <v>134117.362012494</v>
-      </c>
-    </row>
-    <row r="62" s="1" customFormat="1" spans="1:8">
+        <v>134117.36201249401</v>
+      </c>
+    </row>
+    <row r="62" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A62" s="4" t="s">
         <v>69</v>
       </c>
@@ -9224,10 +8300,10 @@
         <v>210</v>
       </c>
       <c r="D62" s="5">
-        <v>306.515369587379</v>
+        <v>306.51536958737898</v>
       </c>
       <c r="E62" s="5">
-        <v>450.059808337379</v>
+        <v>450.05980833737902</v>
       </c>
       <c r="F62" s="5">
         <v>154.544129235437</v>
@@ -9238,10 +8314,10 @@
       </c>
       <c r="H62" s="5">
         <f t="shared" si="1"/>
-        <v>148817.718035965</v>
-      </c>
-    </row>
-    <row r="63" s="1" customFormat="1" spans="1:8">
+        <v>148817.71803596499</v>
+      </c>
+    </row>
+    <row r="63" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A63" s="4" t="s">
         <v>70</v>
       </c>
@@ -9252,24 +8328,24 @@
         <v>210</v>
       </c>
       <c r="D63" s="5">
-        <v>384.317548457563</v>
+        <v>384.31754845756302</v>
       </c>
       <c r="E63" s="5">
-        <v>368.989293102098</v>
+        <v>368.98929310209797</v>
       </c>
       <c r="F63" s="5">
         <v>153.971564727529</v>
       </c>
       <c r="G63" s="5">
         <f t="shared" si="0"/>
-        <v>1.04154119277175</v>
+        <v>1.0415411927717499</v>
       </c>
       <c r="H63" s="5">
         <f t="shared" si="1"/>
-        <v>185900.522907706</v>
-      </c>
-    </row>
-    <row r="64" s="1" customFormat="1" spans="1:8">
+        <v>185900.52290770601</v>
+      </c>
+    </row>
+    <row r="64" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A64" s="4" t="s">
         <v>71</v>
       </c>
@@ -9280,7 +8356,7 @@
         <v>210</v>
       </c>
       <c r="D64" s="5">
-        <v>408.90178111906</v>
+        <v>408.90178111905999</v>
       </c>
       <c r="E64" s="5">
         <v>300.028415521206</v>
@@ -9290,14 +8366,14 @@
       </c>
       <c r="G64" s="5">
         <f t="shared" si="0"/>
-        <v>1.36287684754366</v>
+        <v>1.3628768475436599</v>
       </c>
       <c r="H64" s="5">
         <f t="shared" si="1"/>
         <v>257744.074291094</v>
       </c>
     </row>
-    <row r="65" s="1" customFormat="1" spans="1:8">
+    <row r="65" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A65" s="4" t="s">
         <v>72</v>
       </c>
@@ -9308,13 +8384,13 @@
         <v>210</v>
       </c>
       <c r="D65" s="5">
-        <v>305.136905028394</v>
+        <v>305.13690502839398</v>
       </c>
       <c r="E65" s="5">
-        <v>356.269530848141</v>
+        <v>356.26953084814102</v>
       </c>
       <c r="F65" s="5">
-        <v>181.859400659461</v>
+        <v>181.85940065946099</v>
       </c>
       <c r="G65" s="5">
         <f t="shared" si="0"/>
@@ -9325,7 +8401,7 @@
         <v>174333.305612461</v>
       </c>
     </row>
-    <row r="66" s="1" customFormat="1" spans="1:8">
+    <row r="66" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A66" s="4" t="s">
         <v>73</v>
       </c>
@@ -9336,10 +8412,10 @@
         <v>210</v>
       </c>
       <c r="D66" s="5">
-        <v>431.107103038835</v>
+        <v>431.10710303883502</v>
       </c>
       <c r="E66" s="5">
-        <v>376.940433621359</v>
+        <v>376.94043362135898</v>
       </c>
       <c r="F66" s="5">
         <v>194.201179</v>
@@ -9353,7 +8429,7 @@
         <v>263018.873491965</v>
       </c>
     </row>
-    <row r="67" s="1" customFormat="1" spans="1:8">
+    <row r="67" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A67" s="4" t="s">
         <v>74</v>
       </c>
@@ -9364,24 +8440,24 @@
         <v>210</v>
       </c>
       <c r="D67" s="5">
-        <v>368.308072078389</v>
+        <v>368.30807207838899</v>
       </c>
       <c r="E67" s="5">
-        <v>442.222431751169</v>
+        <v>442.22243175116898</v>
       </c>
       <c r="F67" s="5">
         <v>143.102984016541</v>
       </c>
       <c r="G67" s="5">
         <f t="shared" si="2"/>
-        <v>0.832857054808178</v>
+        <v>0.83285705480817795</v>
       </c>
       <c r="H67" s="5">
         <f t="shared" si="3"/>
-        <v>165580.732611505</v>
-      </c>
-    </row>
-    <row r="68" s="1" customFormat="1" spans="1:8">
+        <v>165580.73261150499</v>
+      </c>
+    </row>
+    <row r="68" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A68" s="4" t="s">
         <v>75</v>
       </c>
@@ -9392,24 +8468,24 @@
         <v>300</v>
       </c>
       <c r="D68" s="5">
-        <v>336.509176496764</v>
+        <v>336.50917649676398</v>
       </c>
       <c r="E68" s="5">
-        <v>302.87974272856</v>
+        <v>302.87974272856002</v>
       </c>
       <c r="F68" s="5">
-        <v>227.88911410801</v>
+        <v>227.88911410801001</v>
       </c>
       <c r="G68" s="5">
         <f t="shared" si="2"/>
-        <v>1.11103229772069</v>
+        <v>1.1110322977206899</v>
       </c>
       <c r="H68" s="5">
         <f t="shared" si="3"/>
-        <v>240918.618772604</v>
-      </c>
-    </row>
-    <row r="69" s="1" customFormat="1" spans="1:8">
+        <v>240918.61877260401</v>
+      </c>
+    </row>
+    <row r="69" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A69" s="4" t="s">
         <v>76</v>
       </c>
@@ -9420,13 +8496,13 @@
         <v>300</v>
       </c>
       <c r="D69" s="5">
-        <v>285.480197334211</v>
+        <v>285.48019733421103</v>
       </c>
       <c r="E69" s="5">
-        <v>315.097777834458</v>
+        <v>315.09777783445799</v>
       </c>
       <c r="F69" s="5">
-        <v>139.46762622182</v>
+        <v>139.46762622182001</v>
       </c>
       <c r="G69" s="5">
         <f t="shared" si="2"/>
@@ -9437,7 +8513,7 @@
         <v>125083.282623996</v>
       </c>
     </row>
-    <row r="70" s="1" customFormat="1" spans="1:8">
+    <row r="70" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A70" s="4" t="s">
         <v>77</v>
       </c>
@@ -9448,24 +8524,24 @@
         <v>300</v>
       </c>
       <c r="D70" s="5">
-        <v>350.880187664192</v>
+        <v>350.88018766419202</v>
       </c>
       <c r="E70" s="5">
         <v>357.25900963735</v>
       </c>
       <c r="F70" s="5">
-        <v>170.890647658481</v>
+        <v>170.89064765848099</v>
       </c>
       <c r="G70" s="5">
         <f t="shared" si="2"/>
-        <v>0.982145105368699</v>
+        <v>0.98214510536869903</v>
       </c>
       <c r="H70" s="5">
         <f t="shared" si="3"/>
         <v>188376.626435791</v>
       </c>
     </row>
-    <row r="71" s="1" customFormat="1" spans="1:8">
+    <row r="71" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A71" s="4" t="s">
         <v>78</v>
       </c>
@@ -9476,24 +8552,24 @@
         <v>300</v>
       </c>
       <c r="D71" s="5">
-        <v>335.972957281553</v>
+        <v>335.97295728155302</v>
       </c>
       <c r="E71" s="5">
-        <v>340.383180162909</v>
+        <v>340.38318016290901</v>
       </c>
       <c r="F71" s="5">
-        <v>138.24855109429</v>
+        <v>138.24855109429001</v>
       </c>
       <c r="G71" s="5">
         <f t="shared" si="2"/>
-        <v>0.987043358372628</v>
+        <v>0.98704335837262802</v>
       </c>
       <c r="H71" s="5">
         <f t="shared" si="3"/>
         <v>145919.987305138</v>
       </c>
     </row>
-    <row r="72" s="1" customFormat="1" spans="1:8">
+    <row r="72" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A72" s="4" t="s">
         <v>79</v>
       </c>
@@ -9504,24 +8580,24 @@
         <v>300</v>
       </c>
       <c r="D72" s="5">
-        <v>355.308331048544</v>
+        <v>355.30833104854401</v>
       </c>
       <c r="E72" s="5">
-        <v>384.547787592233</v>
+        <v>384.54778759223302</v>
       </c>
       <c r="F72" s="5">
         <v>186.601893757282</v>
       </c>
       <c r="G72" s="5">
         <f t="shared" si="2"/>
-        <v>0.923964049496252</v>
+        <v>0.92396404949625199</v>
       </c>
       <c r="H72" s="5">
         <f t="shared" si="3"/>
         <v>208291.386222028</v>
       </c>
     </row>
-    <row r="73" s="1" customFormat="1" spans="1:8">
+    <row r="73" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A73" s="4" t="s">
         <v>80</v>
       </c>
@@ -9532,13 +8608,13 @@
         <v>300</v>
       </c>
       <c r="D73" s="5">
-        <v>328.56052038835</v>
+        <v>328.56052038835003</v>
       </c>
       <c r="E73" s="5">
-        <v>325.149457942752</v>
+        <v>325.14945794275201</v>
       </c>
       <c r="F73" s="5">
-        <v>140.747012721794</v>
+        <v>140.74701272179399</v>
       </c>
       <c r="G73" s="5">
         <f t="shared" si="2"/>
@@ -9546,51 +8622,32 @@
       </c>
       <c r="H73" s="5">
         <f t="shared" si="3"/>
-        <v>145279.533404996</v>
-      </c>
-    </row>
-    <row r="75" s="1" customFormat="1" spans="1:8">
-      <c r="A75" s="2"/>
-      <c r="B75" s="2"/>
-      <c r="C75" s="2"/>
-      <c r="D75" s="3"/>
+        <v>145279.53340499601</v>
+      </c>
+    </row>
+    <row r="75" spans="1:8" x14ac:dyDescent="0.25">
       <c r="E75" s="6"/>
       <c r="F75" s="6"/>
       <c r="G75" s="6"/>
       <c r="H75" s="6"/>
     </row>
-    <row r="76" s="1" customFormat="1" spans="1:8">
-      <c r="A76" s="2"/>
-      <c r="B76" s="2"/>
-      <c r="C76" s="2"/>
-      <c r="D76" s="3"/>
+    <row r="76" spans="1:8" x14ac:dyDescent="0.25">
       <c r="E76" s="6"/>
       <c r="F76" s="6"/>
       <c r="G76" s="6"/>
       <c r="H76" s="6"/>
     </row>
-    <row r="77" s="1" customFormat="1" spans="1:8">
-      <c r="A77" s="2"/>
-      <c r="B77" s="2"/>
-      <c r="C77" s="2"/>
-      <c r="D77" s="3"/>
+    <row r="77" spans="1:8" x14ac:dyDescent="0.25">
       <c r="E77" s="6"/>
       <c r="F77" s="6"/>
       <c r="G77" s="6"/>
       <c r="H77" s="6"/>
     </row>
-    <row r="78" s="1" customFormat="1" spans="1:8">
-      <c r="A78" s="2"/>
-      <c r="B78" s="2"/>
-      <c r="C78" s="2"/>
-      <c r="D78" s="3"/>
-      <c r="E78" s="3"/>
-      <c r="F78" s="3"/>
+    <row r="78" spans="1:8" x14ac:dyDescent="0.25">
       <c r="G78" s="6"/>
-      <c r="H78" s="3"/>
     </row>
   </sheetData>
+  <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <headerFooter/>
 </worksheet>
 </file>